--- a/data/1FEB_25_26/clutch_lineups_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/clutch_lineups_25_26_1FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X589"/>
+  <dimension ref="A1:X609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49942,6 +49942,1686 @@
         </is>
       </c>
     </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>A. MARTINEZ CLARIANA | J. PAUKSTÈ | J. PERIS CRESPO | J. ROUND | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>5</v>
+      </c>
+      <c r="E590" t="n">
+        <v>112</v>
+      </c>
+      <c r="F590" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G590" t="n">
+        <v>3</v>
+      </c>
+      <c r="H590" t="n">
+        <v>2</v>
+      </c>
+      <c r="I590" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J590" t="n">
+        <v>2</v>
+      </c>
+      <c r="K590" t="n">
+        <v>129.31</v>
+      </c>
+      <c r="L590" t="n">
+        <v>100</v>
+      </c>
+      <c r="M590" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="N590" t="n">
+        <v>4</v>
+      </c>
+      <c r="O590" t="n">
+        <v>3</v>
+      </c>
+      <c r="P590" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q590" t="n">
+        <v>3</v>
+      </c>
+      <c r="R590" t="n">
+        <v>4</v>
+      </c>
+      <c r="S590" t="n">
+        <v>0</v>
+      </c>
+      <c r="T590" t="n">
+        <v>0</v>
+      </c>
+      <c r="U590" t="n">
+        <v>2</v>
+      </c>
+      <c r="V590" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W590" t="n">
+        <v>28</v>
+      </c>
+      <c r="X590" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>A. MARTINEZ CLARIANA | J. PERIS CRESPO | J. ROUND | J. VAN ZEGEREN | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>5</v>
+      </c>
+      <c r="E591" t="n">
+        <v>62</v>
+      </c>
+      <c r="F591" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G591" t="n">
+        <v>5</v>
+      </c>
+      <c r="H591" t="n">
+        <v>4</v>
+      </c>
+      <c r="I591" t="n">
+        <v>3</v>
+      </c>
+      <c r="J591" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K591" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L591" t="n">
+        <v>103.09</v>
+      </c>
+      <c r="M591" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="N591" t="n">
+        <v>2</v>
+      </c>
+      <c r="O591" t="n">
+        <v>0</v>
+      </c>
+      <c r="P591" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q591" t="n">
+        <v>0</v>
+      </c>
+      <c r="R591" t="n">
+        <v>2</v>
+      </c>
+      <c r="S591" t="n">
+        <v>2</v>
+      </c>
+      <c r="T591" t="n">
+        <v>1</v>
+      </c>
+      <c r="U591" t="n">
+        <v>0</v>
+      </c>
+      <c r="V591" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W591" t="n">
+        <v>28</v>
+      </c>
+      <c r="X591" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>A. MARTINEZ CLARIANA | J. PERIS CRESPO | J. VAN ZEGEREN | O. LO | T. NASPLER PERAIRE</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>5</v>
+      </c>
+      <c r="E592" t="n">
+        <v>43</v>
+      </c>
+      <c r="F592" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G592" t="n">
+        <v>0</v>
+      </c>
+      <c r="H592" t="n">
+        <v>0</v>
+      </c>
+      <c r="I592" t="n">
+        <v>1</v>
+      </c>
+      <c r="J592" t="n">
+        <v>1</v>
+      </c>
+      <c r="K592" t="n">
+        <v>0</v>
+      </c>
+      <c r="L592" t="n">
+        <v>0</v>
+      </c>
+      <c r="M592" t="n">
+        <v>0</v>
+      </c>
+      <c r="N592" t="n">
+        <v>3</v>
+      </c>
+      <c r="O592" t="n">
+        <v>0</v>
+      </c>
+      <c r="P592" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q592" t="n">
+        <v>2</v>
+      </c>
+      <c r="R592" t="n">
+        <v>1</v>
+      </c>
+      <c r="S592" t="n">
+        <v>0</v>
+      </c>
+      <c r="T592" t="n">
+        <v>0</v>
+      </c>
+      <c r="U592" t="n">
+        <v>0</v>
+      </c>
+      <c r="V592" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W592" t="n">
+        <v>28</v>
+      </c>
+      <c r="X592" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>A. MARTINEZ CLARIANA | J. ROUND | J. VAN ZEGEREN | O. LO | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>5</v>
+      </c>
+      <c r="E593" t="n">
+        <v>61</v>
+      </c>
+      <c r="F593" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G593" t="n">
+        <v>1</v>
+      </c>
+      <c r="H593" t="n">
+        <v>2</v>
+      </c>
+      <c r="I593" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J593" t="n">
+        <v>1</v>
+      </c>
+      <c r="K593" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L593" t="n">
+        <v>200</v>
+      </c>
+      <c r="M593" t="n">
+        <v>-86.36</v>
+      </c>
+      <c r="N593" t="n">
+        <v>1</v>
+      </c>
+      <c r="O593" t="n">
+        <v>2</v>
+      </c>
+      <c r="P593" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q593" t="n">
+        <v>1</v>
+      </c>
+      <c r="R593" t="n">
+        <v>2</v>
+      </c>
+      <c r="S593" t="n">
+        <v>0</v>
+      </c>
+      <c r="T593" t="n">
+        <v>0</v>
+      </c>
+      <c r="U593" t="n">
+        <v>1</v>
+      </c>
+      <c r="V593" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W593" t="n">
+        <v>28</v>
+      </c>
+      <c r="X593" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>J. PERIS CRESPO | J. ROUND | O. LO | T. NASPLER PERAIRE | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>5</v>
+      </c>
+      <c r="E594" t="n">
+        <v>22</v>
+      </c>
+      <c r="F594" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G594" t="n">
+        <v>3</v>
+      </c>
+      <c r="H594" t="n">
+        <v>1</v>
+      </c>
+      <c r="I594" t="n">
+        <v>1</v>
+      </c>
+      <c r="J594" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K594" t="n">
+        <v>300</v>
+      </c>
+      <c r="L594" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M594" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="N594" t="n">
+        <v>1</v>
+      </c>
+      <c r="O594" t="n">
+        <v>0</v>
+      </c>
+      <c r="P594" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q594" t="n">
+        <v>0</v>
+      </c>
+      <c r="R594" t="n">
+        <v>0</v>
+      </c>
+      <c r="S594" t="n">
+        <v>1</v>
+      </c>
+      <c r="T594" t="n">
+        <v>0</v>
+      </c>
+      <c r="U594" t="n">
+        <v>0</v>
+      </c>
+      <c r="V594" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W594" t="n">
+        <v>28</v>
+      </c>
+      <c r="X594" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>A. LIMA BRITO | D. MANCHON CRESPO | J. BELEMENE-DZABATOU | M. DIAZ | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>5</v>
+      </c>
+      <c r="E595" t="n">
+        <v>38</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G595" t="n">
+        <v>2</v>
+      </c>
+      <c r="H595" t="n">
+        <v>2</v>
+      </c>
+      <c r="I595" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J595" t="n">
+        <v>2</v>
+      </c>
+      <c r="K595" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L595" t="n">
+        <v>100</v>
+      </c>
+      <c r="M595" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="N595" t="n">
+        <v>1</v>
+      </c>
+      <c r="O595" t="n">
+        <v>2</v>
+      </c>
+      <c r="P595" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q595" t="n">
+        <v>0</v>
+      </c>
+      <c r="R595" t="n">
+        <v>1</v>
+      </c>
+      <c r="S595" t="n">
+        <v>0</v>
+      </c>
+      <c r="T595" t="n">
+        <v>1</v>
+      </c>
+      <c r="U595" t="n">
+        <v>0</v>
+      </c>
+      <c r="V595" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W595" t="n">
+        <v>28</v>
+      </c>
+      <c r="X595" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>A. LIMA BRITO | J. BELEMENE-DZABATOU | M. DIAZ | P. ALI | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>5</v>
+      </c>
+      <c r="E596" t="n">
+        <v>24</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G596" t="n">
+        <v>2</v>
+      </c>
+      <c r="H596" t="n">
+        <v>3</v>
+      </c>
+      <c r="I596" t="n">
+        <v>2</v>
+      </c>
+      <c r="J596" t="n">
+        <v>1</v>
+      </c>
+      <c r="K596" t="n">
+        <v>100</v>
+      </c>
+      <c r="L596" t="n">
+        <v>300</v>
+      </c>
+      <c r="M596" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N596" t="n">
+        <v>1</v>
+      </c>
+      <c r="O596" t="n">
+        <v>0</v>
+      </c>
+      <c r="P596" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q596" t="n">
+        <v>0</v>
+      </c>
+      <c r="R596" t="n">
+        <v>1</v>
+      </c>
+      <c r="S596" t="n">
+        <v>0</v>
+      </c>
+      <c r="T596" t="n">
+        <v>0</v>
+      </c>
+      <c r="U596" t="n">
+        <v>0</v>
+      </c>
+      <c r="V596" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W596" t="n">
+        <v>28</v>
+      </c>
+      <c r="X596" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>D. MANCHON CRESPO | J. BELEMENE-DZABATOU | J. KASIBABU SHILALA | M. DIAZ | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>5</v>
+      </c>
+      <c r="E597" t="n">
+        <v>83</v>
+      </c>
+      <c r="F597" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G597" t="n">
+        <v>2</v>
+      </c>
+      <c r="H597" t="n">
+        <v>2</v>
+      </c>
+      <c r="I597" t="n">
+        <v>1</v>
+      </c>
+      <c r="J597" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K597" t="n">
+        <v>200</v>
+      </c>
+      <c r="L597" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M597" t="n">
+        <v>130.56</v>
+      </c>
+      <c r="N597" t="n">
+        <v>3</v>
+      </c>
+      <c r="O597" t="n">
+        <v>0</v>
+      </c>
+      <c r="P597" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q597" t="n">
+        <v>2</v>
+      </c>
+      <c r="R597" t="n">
+        <v>4</v>
+      </c>
+      <c r="S597" t="n">
+        <v>2</v>
+      </c>
+      <c r="T597" t="n">
+        <v>0</v>
+      </c>
+      <c r="U597" t="n">
+        <v>2</v>
+      </c>
+      <c r="V597" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W597" t="n">
+        <v>28</v>
+      </c>
+      <c r="X597" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>J. BELEMENE-DZABATOU | J. KASIBABU SHILALA | M. DIAZ | P. ALI | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>5</v>
+      </c>
+      <c r="E598" t="n">
+        <v>155</v>
+      </c>
+      <c r="F598" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G598" t="n">
+        <v>3</v>
+      </c>
+      <c r="H598" t="n">
+        <v>5</v>
+      </c>
+      <c r="I598" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="J598" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K598" t="n">
+        <v>87.20999999999999</v>
+      </c>
+      <c r="L598" t="n">
+        <v>215.52</v>
+      </c>
+      <c r="M598" t="n">
+        <v>-128.31</v>
+      </c>
+      <c r="N598" t="n">
+        <v>4</v>
+      </c>
+      <c r="O598" t="n">
+        <v>1</v>
+      </c>
+      <c r="P598" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q598" t="n">
+        <v>1</v>
+      </c>
+      <c r="R598" t="n">
+        <v>5</v>
+      </c>
+      <c r="S598" t="n">
+        <v>3</v>
+      </c>
+      <c r="T598" t="n">
+        <v>0</v>
+      </c>
+      <c r="U598" t="n">
+        <v>4</v>
+      </c>
+      <c r="V598" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W598" t="n">
+        <v>28</v>
+      </c>
+      <c r="X598" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>A. GARUBA ALARI | C. POLYNICE | I. RIVERA CARROLL | J. LOPEZ SANTANA | K. WEBSTER</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>5</v>
+      </c>
+      <c r="E599" t="n">
+        <v>134</v>
+      </c>
+      <c r="F599" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G599" t="n">
+        <v>7</v>
+      </c>
+      <c r="H599" t="n">
+        <v>4</v>
+      </c>
+      <c r="I599" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="J599" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="K599" t="n">
+        <v>143.44</v>
+      </c>
+      <c r="L599" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="M599" t="n">
+        <v>53.35</v>
+      </c>
+      <c r="N599" t="n">
+        <v>5</v>
+      </c>
+      <c r="O599" t="n">
+        <v>2</v>
+      </c>
+      <c r="P599" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q599" t="n">
+        <v>2</v>
+      </c>
+      <c r="R599" t="n">
+        <v>4</v>
+      </c>
+      <c r="S599" t="n">
+        <v>1</v>
+      </c>
+      <c r="T599" t="n">
+        <v>1</v>
+      </c>
+      <c r="U599" t="n">
+        <v>1</v>
+      </c>
+      <c r="V599" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W599" t="n">
+        <v>28</v>
+      </c>
+      <c r="X599" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>J. GRANGER | L. GIOVANNETTI | O. SILVERIO GRULLON | P. GARINO GULLOTTA | T. MC GREW</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>5</v>
+      </c>
+      <c r="E600" t="n">
+        <v>17</v>
+      </c>
+      <c r="F600" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G600" t="n">
+        <v>2</v>
+      </c>
+      <c r="H600" t="n">
+        <v>0</v>
+      </c>
+      <c r="I600" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J600" t="n">
+        <v>0</v>
+      </c>
+      <c r="K600" t="n">
+        <v>138.89</v>
+      </c>
+      <c r="L600" t="n">
+        <v>0</v>
+      </c>
+      <c r="M600" t="n">
+        <v>0</v>
+      </c>
+      <c r="N600" t="n">
+        <v>2</v>
+      </c>
+      <c r="O600" t="n">
+        <v>1</v>
+      </c>
+      <c r="P600" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q600" t="n">
+        <v>1</v>
+      </c>
+      <c r="R600" t="n">
+        <v>0</v>
+      </c>
+      <c r="S600" t="n">
+        <v>0</v>
+      </c>
+      <c r="T600" t="n">
+        <v>1</v>
+      </c>
+      <c r="U600" t="n">
+        <v>1</v>
+      </c>
+      <c r="V600" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W600" t="n">
+        <v>28</v>
+      </c>
+      <c r="X600" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>J. GRANGER | L. NWOGBO | O. SILVERIO GRULLON | P. GARINO GULLOTTA | T. MC GREW</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>5</v>
+      </c>
+      <c r="E601" t="n">
+        <v>91</v>
+      </c>
+      <c r="F601" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G601" t="n">
+        <v>2</v>
+      </c>
+      <c r="H601" t="n">
+        <v>5</v>
+      </c>
+      <c r="I601" t="n">
+        <v>2</v>
+      </c>
+      <c r="J601" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K601" t="n">
+        <v>100</v>
+      </c>
+      <c r="L601" t="n">
+        <v>128.87</v>
+      </c>
+      <c r="M601" t="n">
+        <v>-28.87</v>
+      </c>
+      <c r="N601" t="n">
+        <v>1</v>
+      </c>
+      <c r="O601" t="n">
+        <v>0</v>
+      </c>
+      <c r="P601" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q601" t="n">
+        <v>0</v>
+      </c>
+      <c r="R601" t="n">
+        <v>3</v>
+      </c>
+      <c r="S601" t="n">
+        <v>2</v>
+      </c>
+      <c r="T601" t="n">
+        <v>0</v>
+      </c>
+      <c r="U601" t="n">
+        <v>0</v>
+      </c>
+      <c r="V601" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W601" t="n">
+        <v>28</v>
+      </c>
+      <c r="X601" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>J. GRANGER | O. SILVERIO GRULLON | P. GARINO GULLOTTA | R. STUMBRIS | T. MC GREW</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>5</v>
+      </c>
+      <c r="E602" t="n">
+        <v>26</v>
+      </c>
+      <c r="F602" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G602" t="n">
+        <v>0</v>
+      </c>
+      <c r="H602" t="n">
+        <v>2</v>
+      </c>
+      <c r="I602" t="n">
+        <v>1</v>
+      </c>
+      <c r="J602" t="n">
+        <v>1</v>
+      </c>
+      <c r="K602" t="n">
+        <v>0</v>
+      </c>
+      <c r="L602" t="n">
+        <v>200</v>
+      </c>
+      <c r="M602" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N602" t="n">
+        <v>1</v>
+      </c>
+      <c r="O602" t="n">
+        <v>0</v>
+      </c>
+      <c r="P602" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q602" t="n">
+        <v>0</v>
+      </c>
+      <c r="R602" t="n">
+        <v>2</v>
+      </c>
+      <c r="S602" t="n">
+        <v>0</v>
+      </c>
+      <c r="T602" t="n">
+        <v>0</v>
+      </c>
+      <c r="U602" t="n">
+        <v>1</v>
+      </c>
+      <c r="V602" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W602" t="n">
+        <v>28</v>
+      </c>
+      <c r="X602" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>A. FAURE RIBES | D. DUSCAK | G. PARHAM II | J. ARIAS GONZALEZ | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>5</v>
+      </c>
+      <c r="E603" t="n">
+        <v>82</v>
+      </c>
+      <c r="F603" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G603" t="n">
+        <v>0</v>
+      </c>
+      <c r="H603" t="n">
+        <v>2</v>
+      </c>
+      <c r="I603" t="n">
+        <v>1</v>
+      </c>
+      <c r="J603" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K603" t="n">
+        <v>0</v>
+      </c>
+      <c r="L603" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="M603" t="n">
+        <v>-106.38</v>
+      </c>
+      <c r="N603" t="n">
+        <v>2</v>
+      </c>
+      <c r="O603" t="n">
+        <v>0</v>
+      </c>
+      <c r="P603" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q603" t="n">
+        <v>1</v>
+      </c>
+      <c r="R603" t="n">
+        <v>2</v>
+      </c>
+      <c r="S603" t="n">
+        <v>2</v>
+      </c>
+      <c r="T603" t="n">
+        <v>0</v>
+      </c>
+      <c r="U603" t="n">
+        <v>1</v>
+      </c>
+      <c r="V603" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W603" t="n">
+        <v>28</v>
+      </c>
+      <c r="X603" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>A. FAURE RIBES | D. DUSCAK | G. PARHAM II | M. TOWNES VILLAR | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>5</v>
+      </c>
+      <c r="E604" t="n">
+        <v>44</v>
+      </c>
+      <c r="F604" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G604" t="n">
+        <v>2</v>
+      </c>
+      <c r="H604" t="n">
+        <v>4</v>
+      </c>
+      <c r="I604" t="n">
+        <v>2</v>
+      </c>
+      <c r="J604" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K604" t="n">
+        <v>100</v>
+      </c>
+      <c r="L604" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="M604" t="n">
+        <v>-112.77</v>
+      </c>
+      <c r="N604" t="n">
+        <v>2</v>
+      </c>
+      <c r="O604" t="n">
+        <v>0</v>
+      </c>
+      <c r="P604" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q604" t="n">
+        <v>0</v>
+      </c>
+      <c r="R604" t="n">
+        <v>1</v>
+      </c>
+      <c r="S604" t="n">
+        <v>2</v>
+      </c>
+      <c r="T604" t="n">
+        <v>0</v>
+      </c>
+      <c r="U604" t="n">
+        <v>0</v>
+      </c>
+      <c r="V604" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W604" t="n">
+        <v>28</v>
+      </c>
+      <c r="X604" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>D. DUSCAK | G. PARHAM II | M. TOWNES VILLAR | R. COSIALLS BORRAS | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>5</v>
+      </c>
+      <c r="E605" t="n">
+        <v>90</v>
+      </c>
+      <c r="F605" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G605" t="n">
+        <v>2</v>
+      </c>
+      <c r="H605" t="n">
+        <v>4</v>
+      </c>
+      <c r="I605" t="n">
+        <v>3</v>
+      </c>
+      <c r="J605" t="n">
+        <v>2</v>
+      </c>
+      <c r="K605" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="L605" t="n">
+        <v>200</v>
+      </c>
+      <c r="M605" t="n">
+        <v>-133.33</v>
+      </c>
+      <c r="N605" t="n">
+        <v>3</v>
+      </c>
+      <c r="O605" t="n">
+        <v>0</v>
+      </c>
+      <c r="P605" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q605" t="n">
+        <v>0</v>
+      </c>
+      <c r="R605" t="n">
+        <v>2</v>
+      </c>
+      <c r="S605" t="n">
+        <v>0</v>
+      </c>
+      <c r="T605" t="n">
+        <v>0</v>
+      </c>
+      <c r="U605" t="n">
+        <v>0</v>
+      </c>
+      <c r="V605" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W605" t="n">
+        <v>28</v>
+      </c>
+      <c r="X605" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>F. NWAOKORIE | J. ARIAS GONZALEZ | M. TOWNES VILLAR | R. COSIALLS BORRAS | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>5</v>
+      </c>
+      <c r="E606" t="n">
+        <v>10</v>
+      </c>
+      <c r="F606" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G606" t="n">
+        <v>2</v>
+      </c>
+      <c r="H606" t="n">
+        <v>0</v>
+      </c>
+      <c r="I606" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="J606" t="n">
+        <v>1</v>
+      </c>
+      <c r="K606" t="n">
+        <v>0</v>
+      </c>
+      <c r="L606" t="n">
+        <v>0</v>
+      </c>
+      <c r="M606" t="n">
+        <v>0</v>
+      </c>
+      <c r="N606" t="n">
+        <v>0</v>
+      </c>
+      <c r="O606" t="n">
+        <v>2</v>
+      </c>
+      <c r="P606" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q606" t="n">
+        <v>1</v>
+      </c>
+      <c r="R606" t="n">
+        <v>1</v>
+      </c>
+      <c r="S606" t="n">
+        <v>0</v>
+      </c>
+      <c r="T606" t="n">
+        <v>0</v>
+      </c>
+      <c r="U606" t="n">
+        <v>0</v>
+      </c>
+      <c r="V606" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W606" t="n">
+        <v>28</v>
+      </c>
+      <c r="X606" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>A. JORDA RODRIGUEZ | D. GEU | J. BONE | K. LARSEN | M. TORRES CUEVAS</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>5</v>
+      </c>
+      <c r="E607" t="n">
+        <v>206</v>
+      </c>
+      <c r="F607" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="G607" t="n">
+        <v>10</v>
+      </c>
+      <c r="H607" t="n">
+        <v>4</v>
+      </c>
+      <c r="I607" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="J607" t="n">
+        <v>6</v>
+      </c>
+      <c r="K607" t="n">
+        <v>173.61</v>
+      </c>
+      <c r="L607" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="M607" t="n">
+        <v>106.94</v>
+      </c>
+      <c r="N607" t="n">
+        <v>5</v>
+      </c>
+      <c r="O607" t="n">
+        <v>4</v>
+      </c>
+      <c r="P607" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q607" t="n">
+        <v>1</v>
+      </c>
+      <c r="R607" t="n">
+        <v>7</v>
+      </c>
+      <c r="S607" t="n">
+        <v>0</v>
+      </c>
+      <c r="T607" t="n">
+        <v>0</v>
+      </c>
+      <c r="U607" t="n">
+        <v>1</v>
+      </c>
+      <c r="V607" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W607" t="n">
+        <v>28</v>
+      </c>
+      <c r="X607" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>A. JORDA RODRIGUEZ | D. GEU | J. BONE | M. TORRES CUEVAS | U. MENDICOTE RUBIO</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>5</v>
+      </c>
+      <c r="E608" t="n">
+        <v>10</v>
+      </c>
+      <c r="F608" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G608" t="n">
+        <v>0</v>
+      </c>
+      <c r="H608" t="n">
+        <v>0</v>
+      </c>
+      <c r="I608" t="n">
+        <v>0</v>
+      </c>
+      <c r="J608" t="n">
+        <v>0</v>
+      </c>
+      <c r="K608" t="n">
+        <v>0</v>
+      </c>
+      <c r="L608" t="n">
+        <v>0</v>
+      </c>
+      <c r="M608" t="n">
+        <v>0</v>
+      </c>
+      <c r="N608" t="n">
+        <v>0</v>
+      </c>
+      <c r="O608" t="n">
+        <v>0</v>
+      </c>
+      <c r="P608" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q608" t="n">
+        <v>0</v>
+      </c>
+      <c r="R608" t="n">
+        <v>0</v>
+      </c>
+      <c r="S608" t="n">
+        <v>0</v>
+      </c>
+      <c r="T608" t="n">
+        <v>0</v>
+      </c>
+      <c r="U608" t="n">
+        <v>0</v>
+      </c>
+      <c r="V608" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W608" t="n">
+        <v>28</v>
+      </c>
+      <c r="X608" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>A. JORDA RODRIGUEZ | J. BONE | J. MWEMA | K. LARSEN | M. TORRES CUEVAS</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>5</v>
+      </c>
+      <c r="E609" t="n">
+        <v>10</v>
+      </c>
+      <c r="F609" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G609" t="n">
+        <v>0</v>
+      </c>
+      <c r="H609" t="n">
+        <v>2</v>
+      </c>
+      <c r="I609" t="n">
+        <v>1</v>
+      </c>
+      <c r="J609" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K609" t="n">
+        <v>0</v>
+      </c>
+      <c r="L609" t="n">
+        <v>0</v>
+      </c>
+      <c r="M609" t="n">
+        <v>0</v>
+      </c>
+      <c r="N609" t="n">
+        <v>1</v>
+      </c>
+      <c r="O609" t="n">
+        <v>0</v>
+      </c>
+      <c r="P609" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q609" t="n">
+        <v>0</v>
+      </c>
+      <c r="R609" t="n">
+        <v>0</v>
+      </c>
+      <c r="S609" t="n">
+        <v>2</v>
+      </c>
+      <c r="T609" t="n">
+        <v>0</v>
+      </c>
+      <c r="U609" t="n">
+        <v>1</v>
+      </c>
+      <c r="V609" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W609" t="n">
+        <v>28</v>
+      </c>
+      <c r="X609" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/1FEB_25_26/clutch_lineups_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/clutch_lineups_25_26_1FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X589"/>
+  <dimension ref="A1:X645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49942,6 +49942,4710 @@
         </is>
       </c>
     </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>A. MARTINEZ CLARIANA | J. PAUKSTÈ | J. PERIS CRESPO | J. ROUND | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>5</v>
+      </c>
+      <c r="E590" t="n">
+        <v>112</v>
+      </c>
+      <c r="F590" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G590" t="n">
+        <v>3</v>
+      </c>
+      <c r="H590" t="n">
+        <v>2</v>
+      </c>
+      <c r="I590" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J590" t="n">
+        <v>2</v>
+      </c>
+      <c r="K590" t="n">
+        <v>129.31</v>
+      </c>
+      <c r="L590" t="n">
+        <v>100</v>
+      </c>
+      <c r="M590" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="N590" t="n">
+        <v>4</v>
+      </c>
+      <c r="O590" t="n">
+        <v>3</v>
+      </c>
+      <c r="P590" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q590" t="n">
+        <v>3</v>
+      </c>
+      <c r="R590" t="n">
+        <v>4</v>
+      </c>
+      <c r="S590" t="n">
+        <v>0</v>
+      </c>
+      <c r="T590" t="n">
+        <v>0</v>
+      </c>
+      <c r="U590" t="n">
+        <v>2</v>
+      </c>
+      <c r="V590" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W590" t="n">
+        <v>28</v>
+      </c>
+      <c r="X590" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>A. MARTINEZ CLARIANA | J. PERIS CRESPO | J. ROUND | J. VAN ZEGEREN | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>5</v>
+      </c>
+      <c r="E591" t="n">
+        <v>62</v>
+      </c>
+      <c r="F591" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G591" t="n">
+        <v>5</v>
+      </c>
+      <c r="H591" t="n">
+        <v>4</v>
+      </c>
+      <c r="I591" t="n">
+        <v>3</v>
+      </c>
+      <c r="J591" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K591" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L591" t="n">
+        <v>103.09</v>
+      </c>
+      <c r="M591" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="N591" t="n">
+        <v>2</v>
+      </c>
+      <c r="O591" t="n">
+        <v>0</v>
+      </c>
+      <c r="P591" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q591" t="n">
+        <v>0</v>
+      </c>
+      <c r="R591" t="n">
+        <v>2</v>
+      </c>
+      <c r="S591" t="n">
+        <v>2</v>
+      </c>
+      <c r="T591" t="n">
+        <v>1</v>
+      </c>
+      <c r="U591" t="n">
+        <v>0</v>
+      </c>
+      <c r="V591" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W591" t="n">
+        <v>28</v>
+      </c>
+      <c r="X591" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>A. MARTINEZ CLARIANA | J. PERIS CRESPO | J. VAN ZEGEREN | O. LO | T. NASPLER PERAIRE</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>5</v>
+      </c>
+      <c r="E592" t="n">
+        <v>43</v>
+      </c>
+      <c r="F592" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G592" t="n">
+        <v>0</v>
+      </c>
+      <c r="H592" t="n">
+        <v>0</v>
+      </c>
+      <c r="I592" t="n">
+        <v>1</v>
+      </c>
+      <c r="J592" t="n">
+        <v>1</v>
+      </c>
+      <c r="K592" t="n">
+        <v>0</v>
+      </c>
+      <c r="L592" t="n">
+        <v>0</v>
+      </c>
+      <c r="M592" t="n">
+        <v>0</v>
+      </c>
+      <c r="N592" t="n">
+        <v>3</v>
+      </c>
+      <c r="O592" t="n">
+        <v>0</v>
+      </c>
+      <c r="P592" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q592" t="n">
+        <v>2</v>
+      </c>
+      <c r="R592" t="n">
+        <v>1</v>
+      </c>
+      <c r="S592" t="n">
+        <v>0</v>
+      </c>
+      <c r="T592" t="n">
+        <v>0</v>
+      </c>
+      <c r="U592" t="n">
+        <v>0</v>
+      </c>
+      <c r="V592" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W592" t="n">
+        <v>28</v>
+      </c>
+      <c r="X592" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>A. MARTINEZ CLARIANA | J. ROUND | J. VAN ZEGEREN | O. LO | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>5</v>
+      </c>
+      <c r="E593" t="n">
+        <v>61</v>
+      </c>
+      <c r="F593" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G593" t="n">
+        <v>1</v>
+      </c>
+      <c r="H593" t="n">
+        <v>2</v>
+      </c>
+      <c r="I593" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J593" t="n">
+        <v>1</v>
+      </c>
+      <c r="K593" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L593" t="n">
+        <v>200</v>
+      </c>
+      <c r="M593" t="n">
+        <v>-86.36</v>
+      </c>
+      <c r="N593" t="n">
+        <v>1</v>
+      </c>
+      <c r="O593" t="n">
+        <v>2</v>
+      </c>
+      <c r="P593" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q593" t="n">
+        <v>1</v>
+      </c>
+      <c r="R593" t="n">
+        <v>2</v>
+      </c>
+      <c r="S593" t="n">
+        <v>0</v>
+      </c>
+      <c r="T593" t="n">
+        <v>0</v>
+      </c>
+      <c r="U593" t="n">
+        <v>1</v>
+      </c>
+      <c r="V593" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W593" t="n">
+        <v>28</v>
+      </c>
+      <c r="X593" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>J. PERIS CRESPO | J. ROUND | O. LO | T. NASPLER PERAIRE | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>5</v>
+      </c>
+      <c r="E594" t="n">
+        <v>22</v>
+      </c>
+      <c r="F594" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G594" t="n">
+        <v>3</v>
+      </c>
+      <c r="H594" t="n">
+        <v>1</v>
+      </c>
+      <c r="I594" t="n">
+        <v>1</v>
+      </c>
+      <c r="J594" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K594" t="n">
+        <v>300</v>
+      </c>
+      <c r="L594" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M594" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="N594" t="n">
+        <v>1</v>
+      </c>
+      <c r="O594" t="n">
+        <v>0</v>
+      </c>
+      <c r="P594" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q594" t="n">
+        <v>0</v>
+      </c>
+      <c r="R594" t="n">
+        <v>0</v>
+      </c>
+      <c r="S594" t="n">
+        <v>1</v>
+      </c>
+      <c r="T594" t="n">
+        <v>0</v>
+      </c>
+      <c r="U594" t="n">
+        <v>0</v>
+      </c>
+      <c r="V594" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W594" t="n">
+        <v>28</v>
+      </c>
+      <c r="X594" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>A. LIMA BRITO | D. MANCHON CRESPO | J. BELEMENE-DZABATOU | M. DIAZ | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>5</v>
+      </c>
+      <c r="E595" t="n">
+        <v>38</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G595" t="n">
+        <v>2</v>
+      </c>
+      <c r="H595" t="n">
+        <v>2</v>
+      </c>
+      <c r="I595" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J595" t="n">
+        <v>2</v>
+      </c>
+      <c r="K595" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L595" t="n">
+        <v>100</v>
+      </c>
+      <c r="M595" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="N595" t="n">
+        <v>1</v>
+      </c>
+      <c r="O595" t="n">
+        <v>2</v>
+      </c>
+      <c r="P595" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q595" t="n">
+        <v>0</v>
+      </c>
+      <c r="R595" t="n">
+        <v>1</v>
+      </c>
+      <c r="S595" t="n">
+        <v>0</v>
+      </c>
+      <c r="T595" t="n">
+        <v>1</v>
+      </c>
+      <c r="U595" t="n">
+        <v>0</v>
+      </c>
+      <c r="V595" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W595" t="n">
+        <v>28</v>
+      </c>
+      <c r="X595" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>A. LIMA BRITO | J. BELEMENE-DZABATOU | M. DIAZ | P. ALI | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>5</v>
+      </c>
+      <c r="E596" t="n">
+        <v>24</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G596" t="n">
+        <v>2</v>
+      </c>
+      <c r="H596" t="n">
+        <v>3</v>
+      </c>
+      <c r="I596" t="n">
+        <v>2</v>
+      </c>
+      <c r="J596" t="n">
+        <v>1</v>
+      </c>
+      <c r="K596" t="n">
+        <v>100</v>
+      </c>
+      <c r="L596" t="n">
+        <v>300</v>
+      </c>
+      <c r="M596" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N596" t="n">
+        <v>1</v>
+      </c>
+      <c r="O596" t="n">
+        <v>0</v>
+      </c>
+      <c r="P596" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q596" t="n">
+        <v>0</v>
+      </c>
+      <c r="R596" t="n">
+        <v>1</v>
+      </c>
+      <c r="S596" t="n">
+        <v>0</v>
+      </c>
+      <c r="T596" t="n">
+        <v>0</v>
+      </c>
+      <c r="U596" t="n">
+        <v>0</v>
+      </c>
+      <c r="V596" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W596" t="n">
+        <v>28</v>
+      </c>
+      <c r="X596" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>D. MANCHON CRESPO | J. BELEMENE-DZABATOU | J. KASIBABU SHILALA | M. DIAZ | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>5</v>
+      </c>
+      <c r="E597" t="n">
+        <v>83</v>
+      </c>
+      <c r="F597" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G597" t="n">
+        <v>2</v>
+      </c>
+      <c r="H597" t="n">
+        <v>2</v>
+      </c>
+      <c r="I597" t="n">
+        <v>1</v>
+      </c>
+      <c r="J597" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K597" t="n">
+        <v>200</v>
+      </c>
+      <c r="L597" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M597" t="n">
+        <v>130.56</v>
+      </c>
+      <c r="N597" t="n">
+        <v>3</v>
+      </c>
+      <c r="O597" t="n">
+        <v>0</v>
+      </c>
+      <c r="P597" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q597" t="n">
+        <v>2</v>
+      </c>
+      <c r="R597" t="n">
+        <v>4</v>
+      </c>
+      <c r="S597" t="n">
+        <v>2</v>
+      </c>
+      <c r="T597" t="n">
+        <v>0</v>
+      </c>
+      <c r="U597" t="n">
+        <v>2</v>
+      </c>
+      <c r="V597" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W597" t="n">
+        <v>28</v>
+      </c>
+      <c r="X597" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>J. BELEMENE-DZABATOU | J. KASIBABU SHILALA | M. DIAZ | P. ALI | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>5</v>
+      </c>
+      <c r="E598" t="n">
+        <v>155</v>
+      </c>
+      <c r="F598" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G598" t="n">
+        <v>3</v>
+      </c>
+      <c r="H598" t="n">
+        <v>5</v>
+      </c>
+      <c r="I598" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="J598" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K598" t="n">
+        <v>87.20999999999999</v>
+      </c>
+      <c r="L598" t="n">
+        <v>215.52</v>
+      </c>
+      <c r="M598" t="n">
+        <v>-128.31</v>
+      </c>
+      <c r="N598" t="n">
+        <v>4</v>
+      </c>
+      <c r="O598" t="n">
+        <v>1</v>
+      </c>
+      <c r="P598" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q598" t="n">
+        <v>1</v>
+      </c>
+      <c r="R598" t="n">
+        <v>5</v>
+      </c>
+      <c r="S598" t="n">
+        <v>3</v>
+      </c>
+      <c r="T598" t="n">
+        <v>0</v>
+      </c>
+      <c r="U598" t="n">
+        <v>4</v>
+      </c>
+      <c r="V598" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W598" t="n">
+        <v>28</v>
+      </c>
+      <c r="X598" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>A. GARUBA ALARI | C. POLYNICE | I. RIVERA CARROLL | J. LOPEZ SANTANA | K. WEBSTER</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>5</v>
+      </c>
+      <c r="E599" t="n">
+        <v>134</v>
+      </c>
+      <c r="F599" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G599" t="n">
+        <v>7</v>
+      </c>
+      <c r="H599" t="n">
+        <v>4</v>
+      </c>
+      <c r="I599" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="J599" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="K599" t="n">
+        <v>143.44</v>
+      </c>
+      <c r="L599" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="M599" t="n">
+        <v>53.35</v>
+      </c>
+      <c r="N599" t="n">
+        <v>5</v>
+      </c>
+      <c r="O599" t="n">
+        <v>2</v>
+      </c>
+      <c r="P599" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q599" t="n">
+        <v>2</v>
+      </c>
+      <c r="R599" t="n">
+        <v>4</v>
+      </c>
+      <c r="S599" t="n">
+        <v>1</v>
+      </c>
+      <c r="T599" t="n">
+        <v>1</v>
+      </c>
+      <c r="U599" t="n">
+        <v>1</v>
+      </c>
+      <c r="V599" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W599" t="n">
+        <v>28</v>
+      </c>
+      <c r="X599" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>J. GRANGER | L. GIOVANNETTI | O. SILVERIO GRULLON | P. GARINO GULLOTTA | T. MC GREW</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>5</v>
+      </c>
+      <c r="E600" t="n">
+        <v>17</v>
+      </c>
+      <c r="F600" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G600" t="n">
+        <v>2</v>
+      </c>
+      <c r="H600" t="n">
+        <v>0</v>
+      </c>
+      <c r="I600" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J600" t="n">
+        <v>0</v>
+      </c>
+      <c r="K600" t="n">
+        <v>138.89</v>
+      </c>
+      <c r="L600" t="n">
+        <v>0</v>
+      </c>
+      <c r="M600" t="n">
+        <v>0</v>
+      </c>
+      <c r="N600" t="n">
+        <v>2</v>
+      </c>
+      <c r="O600" t="n">
+        <v>1</v>
+      </c>
+      <c r="P600" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q600" t="n">
+        <v>1</v>
+      </c>
+      <c r="R600" t="n">
+        <v>0</v>
+      </c>
+      <c r="S600" t="n">
+        <v>0</v>
+      </c>
+      <c r="T600" t="n">
+        <v>1</v>
+      </c>
+      <c r="U600" t="n">
+        <v>1</v>
+      </c>
+      <c r="V600" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W600" t="n">
+        <v>28</v>
+      </c>
+      <c r="X600" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>J. GRANGER | L. NWOGBO | O. SILVERIO GRULLON | P. GARINO GULLOTTA | T. MC GREW</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>5</v>
+      </c>
+      <c r="E601" t="n">
+        <v>91</v>
+      </c>
+      <c r="F601" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G601" t="n">
+        <v>2</v>
+      </c>
+      <c r="H601" t="n">
+        <v>5</v>
+      </c>
+      <c r="I601" t="n">
+        <v>2</v>
+      </c>
+      <c r="J601" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K601" t="n">
+        <v>100</v>
+      </c>
+      <c r="L601" t="n">
+        <v>128.87</v>
+      </c>
+      <c r="M601" t="n">
+        <v>-28.87</v>
+      </c>
+      <c r="N601" t="n">
+        <v>1</v>
+      </c>
+      <c r="O601" t="n">
+        <v>0</v>
+      </c>
+      <c r="P601" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q601" t="n">
+        <v>0</v>
+      </c>
+      <c r="R601" t="n">
+        <v>3</v>
+      </c>
+      <c r="S601" t="n">
+        <v>2</v>
+      </c>
+      <c r="T601" t="n">
+        <v>0</v>
+      </c>
+      <c r="U601" t="n">
+        <v>0</v>
+      </c>
+      <c r="V601" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W601" t="n">
+        <v>28</v>
+      </c>
+      <c r="X601" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>J. GRANGER | O. SILVERIO GRULLON | P. GARINO GULLOTTA | R. STUMBRIS | T. MC GREW</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>5</v>
+      </c>
+      <c r="E602" t="n">
+        <v>26</v>
+      </c>
+      <c r="F602" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G602" t="n">
+        <v>0</v>
+      </c>
+      <c r="H602" t="n">
+        <v>2</v>
+      </c>
+      <c r="I602" t="n">
+        <v>1</v>
+      </c>
+      <c r="J602" t="n">
+        <v>1</v>
+      </c>
+      <c r="K602" t="n">
+        <v>0</v>
+      </c>
+      <c r="L602" t="n">
+        <v>200</v>
+      </c>
+      <c r="M602" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N602" t="n">
+        <v>1</v>
+      </c>
+      <c r="O602" t="n">
+        <v>0</v>
+      </c>
+      <c r="P602" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q602" t="n">
+        <v>0</v>
+      </c>
+      <c r="R602" t="n">
+        <v>2</v>
+      </c>
+      <c r="S602" t="n">
+        <v>0</v>
+      </c>
+      <c r="T602" t="n">
+        <v>0</v>
+      </c>
+      <c r="U602" t="n">
+        <v>1</v>
+      </c>
+      <c r="V602" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W602" t="n">
+        <v>28</v>
+      </c>
+      <c r="X602" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>A. FAURE RIBES | D. DUSCAK | G. PARHAM II | J. ARIAS GONZALEZ | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>5</v>
+      </c>
+      <c r="E603" t="n">
+        <v>82</v>
+      </c>
+      <c r="F603" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G603" t="n">
+        <v>0</v>
+      </c>
+      <c r="H603" t="n">
+        <v>2</v>
+      </c>
+      <c r="I603" t="n">
+        <v>1</v>
+      </c>
+      <c r="J603" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K603" t="n">
+        <v>0</v>
+      </c>
+      <c r="L603" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="M603" t="n">
+        <v>-106.38</v>
+      </c>
+      <c r="N603" t="n">
+        <v>2</v>
+      </c>
+      <c r="O603" t="n">
+        <v>0</v>
+      </c>
+      <c r="P603" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q603" t="n">
+        <v>1</v>
+      </c>
+      <c r="R603" t="n">
+        <v>2</v>
+      </c>
+      <c r="S603" t="n">
+        <v>2</v>
+      </c>
+      <c r="T603" t="n">
+        <v>0</v>
+      </c>
+      <c r="U603" t="n">
+        <v>1</v>
+      </c>
+      <c r="V603" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W603" t="n">
+        <v>28</v>
+      </c>
+      <c r="X603" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>A. FAURE RIBES | D. DUSCAK | G. PARHAM II | M. TOWNES VILLAR | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>5</v>
+      </c>
+      <c r="E604" t="n">
+        <v>44</v>
+      </c>
+      <c r="F604" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G604" t="n">
+        <v>2</v>
+      </c>
+      <c r="H604" t="n">
+        <v>4</v>
+      </c>
+      <c r="I604" t="n">
+        <v>2</v>
+      </c>
+      <c r="J604" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K604" t="n">
+        <v>100</v>
+      </c>
+      <c r="L604" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="M604" t="n">
+        <v>-112.77</v>
+      </c>
+      <c r="N604" t="n">
+        <v>2</v>
+      </c>
+      <c r="O604" t="n">
+        <v>0</v>
+      </c>
+      <c r="P604" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q604" t="n">
+        <v>0</v>
+      </c>
+      <c r="R604" t="n">
+        <v>1</v>
+      </c>
+      <c r="S604" t="n">
+        <v>2</v>
+      </c>
+      <c r="T604" t="n">
+        <v>0</v>
+      </c>
+      <c r="U604" t="n">
+        <v>0</v>
+      </c>
+      <c r="V604" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W604" t="n">
+        <v>28</v>
+      </c>
+      <c r="X604" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>D. DUSCAK | G. PARHAM II | M. TOWNES VILLAR | R. COSIALLS BORRAS | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>5</v>
+      </c>
+      <c r="E605" t="n">
+        <v>90</v>
+      </c>
+      <c r="F605" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G605" t="n">
+        <v>2</v>
+      </c>
+      <c r="H605" t="n">
+        <v>4</v>
+      </c>
+      <c r="I605" t="n">
+        <v>3</v>
+      </c>
+      <c r="J605" t="n">
+        <v>2</v>
+      </c>
+      <c r="K605" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="L605" t="n">
+        <v>200</v>
+      </c>
+      <c r="M605" t="n">
+        <v>-133.33</v>
+      </c>
+      <c r="N605" t="n">
+        <v>3</v>
+      </c>
+      <c r="O605" t="n">
+        <v>0</v>
+      </c>
+      <c r="P605" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q605" t="n">
+        <v>0</v>
+      </c>
+      <c r="R605" t="n">
+        <v>2</v>
+      </c>
+      <c r="S605" t="n">
+        <v>0</v>
+      </c>
+      <c r="T605" t="n">
+        <v>0</v>
+      </c>
+      <c r="U605" t="n">
+        <v>0</v>
+      </c>
+      <c r="V605" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W605" t="n">
+        <v>28</v>
+      </c>
+      <c r="X605" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>F. NWAOKORIE | J. ARIAS GONZALEZ | M. TOWNES VILLAR | R. COSIALLS BORRAS | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>5</v>
+      </c>
+      <c r="E606" t="n">
+        <v>10</v>
+      </c>
+      <c r="F606" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G606" t="n">
+        <v>2</v>
+      </c>
+      <c r="H606" t="n">
+        <v>0</v>
+      </c>
+      <c r="I606" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="J606" t="n">
+        <v>1</v>
+      </c>
+      <c r="K606" t="n">
+        <v>0</v>
+      </c>
+      <c r="L606" t="n">
+        <v>0</v>
+      </c>
+      <c r="M606" t="n">
+        <v>0</v>
+      </c>
+      <c r="N606" t="n">
+        <v>0</v>
+      </c>
+      <c r="O606" t="n">
+        <v>2</v>
+      </c>
+      <c r="P606" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q606" t="n">
+        <v>1</v>
+      </c>
+      <c r="R606" t="n">
+        <v>1</v>
+      </c>
+      <c r="S606" t="n">
+        <v>0</v>
+      </c>
+      <c r="T606" t="n">
+        <v>0</v>
+      </c>
+      <c r="U606" t="n">
+        <v>0</v>
+      </c>
+      <c r="V606" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W606" t="n">
+        <v>28</v>
+      </c>
+      <c r="X606" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>A. JORDA RODRIGUEZ | D. GEU | J. BONE | K. LARSEN | M. TORRES CUEVAS</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>5</v>
+      </c>
+      <c r="E607" t="n">
+        <v>206</v>
+      </c>
+      <c r="F607" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="G607" t="n">
+        <v>10</v>
+      </c>
+      <c r="H607" t="n">
+        <v>4</v>
+      </c>
+      <c r="I607" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="J607" t="n">
+        <v>6</v>
+      </c>
+      <c r="K607" t="n">
+        <v>173.61</v>
+      </c>
+      <c r="L607" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="M607" t="n">
+        <v>106.94</v>
+      </c>
+      <c r="N607" t="n">
+        <v>5</v>
+      </c>
+      <c r="O607" t="n">
+        <v>4</v>
+      </c>
+      <c r="P607" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q607" t="n">
+        <v>1</v>
+      </c>
+      <c r="R607" t="n">
+        <v>7</v>
+      </c>
+      <c r="S607" t="n">
+        <v>0</v>
+      </c>
+      <c r="T607" t="n">
+        <v>0</v>
+      </c>
+      <c r="U607" t="n">
+        <v>1</v>
+      </c>
+      <c r="V607" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W607" t="n">
+        <v>28</v>
+      </c>
+      <c r="X607" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>A. JORDA RODRIGUEZ | D. GEU | J. BONE | M. TORRES CUEVAS | U. MENDICOTE RUBIO</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>5</v>
+      </c>
+      <c r="E608" t="n">
+        <v>10</v>
+      </c>
+      <c r="F608" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G608" t="n">
+        <v>0</v>
+      </c>
+      <c r="H608" t="n">
+        <v>0</v>
+      </c>
+      <c r="I608" t="n">
+        <v>0</v>
+      </c>
+      <c r="J608" t="n">
+        <v>0</v>
+      </c>
+      <c r="K608" t="n">
+        <v>0</v>
+      </c>
+      <c r="L608" t="n">
+        <v>0</v>
+      </c>
+      <c r="M608" t="n">
+        <v>0</v>
+      </c>
+      <c r="N608" t="n">
+        <v>0</v>
+      </c>
+      <c r="O608" t="n">
+        <v>0</v>
+      </c>
+      <c r="P608" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q608" t="n">
+        <v>0</v>
+      </c>
+      <c r="R608" t="n">
+        <v>0</v>
+      </c>
+      <c r="S608" t="n">
+        <v>0</v>
+      </c>
+      <c r="T608" t="n">
+        <v>0</v>
+      </c>
+      <c r="U608" t="n">
+        <v>0</v>
+      </c>
+      <c r="V608" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W608" t="n">
+        <v>28</v>
+      </c>
+      <c r="X608" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>A. JORDA RODRIGUEZ | J. BONE | J. MWEMA | K. LARSEN | M. TORRES CUEVAS</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>5</v>
+      </c>
+      <c r="E609" t="n">
+        <v>10</v>
+      </c>
+      <c r="F609" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G609" t="n">
+        <v>0</v>
+      </c>
+      <c r="H609" t="n">
+        <v>2</v>
+      </c>
+      <c r="I609" t="n">
+        <v>1</v>
+      </c>
+      <c r="J609" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K609" t="n">
+        <v>0</v>
+      </c>
+      <c r="L609" t="n">
+        <v>0</v>
+      </c>
+      <c r="M609" t="n">
+        <v>0</v>
+      </c>
+      <c r="N609" t="n">
+        <v>1</v>
+      </c>
+      <c r="O609" t="n">
+        <v>0</v>
+      </c>
+      <c r="P609" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q609" t="n">
+        <v>0</v>
+      </c>
+      <c r="R609" t="n">
+        <v>0</v>
+      </c>
+      <c r="S609" t="n">
+        <v>2</v>
+      </c>
+      <c r="T609" t="n">
+        <v>0</v>
+      </c>
+      <c r="U609" t="n">
+        <v>1</v>
+      </c>
+      <c r="V609" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W609" t="n">
+        <v>28</v>
+      </c>
+      <c r="X609" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2486513</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>C. DE SOUZA PACHECO | I. DIOP GAYE | J. CREMO | P. JORGENSEN | S. BARRO</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>5</v>
+      </c>
+      <c r="E610" t="n">
+        <v>47</v>
+      </c>
+      <c r="F610" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G610" t="n">
+        <v>0</v>
+      </c>
+      <c r="H610" t="n">
+        <v>4</v>
+      </c>
+      <c r="I610" t="n">
+        <v>2</v>
+      </c>
+      <c r="J610" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K610" t="n">
+        <v>0</v>
+      </c>
+      <c r="L610" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="M610" t="n">
+        <v>-212.77</v>
+      </c>
+      <c r="N610" t="n">
+        <v>2</v>
+      </c>
+      <c r="O610" t="n">
+        <v>0</v>
+      </c>
+      <c r="P610" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q610" t="n">
+        <v>0</v>
+      </c>
+      <c r="R610" t="n">
+        <v>1</v>
+      </c>
+      <c r="S610" t="n">
+        <v>2</v>
+      </c>
+      <c r="T610" t="n">
+        <v>0</v>
+      </c>
+      <c r="U610" t="n">
+        <v>0</v>
+      </c>
+      <c r="V610" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W610" t="n">
+        <v>29</v>
+      </c>
+      <c r="X610" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs LEYMA CORUÑA</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2486513</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>C. DE SOUZA PACHECO | I. DIOP GAYE | J. DIAZ ALEJANO | P. JORGENSEN | S. BARRO</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>5</v>
+      </c>
+      <c r="E611" t="n">
+        <v>37</v>
+      </c>
+      <c r="F611" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G611" t="n">
+        <v>0</v>
+      </c>
+      <c r="H611" t="n">
+        <v>3</v>
+      </c>
+      <c r="I611" t="n">
+        <v>1</v>
+      </c>
+      <c r="J611" t="n">
+        <v>2</v>
+      </c>
+      <c r="K611" t="n">
+        <v>0</v>
+      </c>
+      <c r="L611" t="n">
+        <v>150</v>
+      </c>
+      <c r="M611" t="n">
+        <v>-150</v>
+      </c>
+      <c r="N611" t="n">
+        <v>0</v>
+      </c>
+      <c r="O611" t="n">
+        <v>0</v>
+      </c>
+      <c r="P611" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q611" t="n">
+        <v>0</v>
+      </c>
+      <c r="R611" t="n">
+        <v>2</v>
+      </c>
+      <c r="S611" t="n">
+        <v>0</v>
+      </c>
+      <c r="T611" t="n">
+        <v>0</v>
+      </c>
+      <c r="U611" t="n">
+        <v>0</v>
+      </c>
+      <c r="V611" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W611" t="n">
+        <v>29</v>
+      </c>
+      <c r="X611" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs LEYMA CORUÑA</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2486513</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>A. GALAN POZO | D. DE SOUSA ANJO BRITO | D. KRAVIC | L. WESTERMANN | T. MUNNINGS</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>5</v>
+      </c>
+      <c r="E612" t="n">
+        <v>37</v>
+      </c>
+      <c r="F612" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G612" t="n">
+        <v>3</v>
+      </c>
+      <c r="H612" t="n">
+        <v>0</v>
+      </c>
+      <c r="I612" t="n">
+        <v>2</v>
+      </c>
+      <c r="J612" t="n">
+        <v>1</v>
+      </c>
+      <c r="K612" t="n">
+        <v>150</v>
+      </c>
+      <c r="L612" t="n">
+        <v>0</v>
+      </c>
+      <c r="M612" t="n">
+        <v>150</v>
+      </c>
+      <c r="N612" t="n">
+        <v>2</v>
+      </c>
+      <c r="O612" t="n">
+        <v>0</v>
+      </c>
+      <c r="P612" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q612" t="n">
+        <v>0</v>
+      </c>
+      <c r="R612" t="n">
+        <v>0</v>
+      </c>
+      <c r="S612" t="n">
+        <v>0</v>
+      </c>
+      <c r="T612" t="n">
+        <v>1</v>
+      </c>
+      <c r="U612" t="n">
+        <v>0</v>
+      </c>
+      <c r="V612" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W612" t="n">
+        <v>29</v>
+      </c>
+      <c r="X612" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs LEYMA CORUÑA</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2486513</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>D. DE SOUSA ANJO BRITO | D. KRAVIC | S. QUINTELA SALVADOR | T. MUNNINGS</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>4</v>
+      </c>
+      <c r="E613" t="n">
+        <v>47</v>
+      </c>
+      <c r="F613" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G613" t="n">
+        <v>4</v>
+      </c>
+      <c r="H613" t="n">
+        <v>0</v>
+      </c>
+      <c r="I613" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J613" t="n">
+        <v>2</v>
+      </c>
+      <c r="K613" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="L613" t="n">
+        <v>0</v>
+      </c>
+      <c r="M613" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="N613" t="n">
+        <v>1</v>
+      </c>
+      <c r="O613" t="n">
+        <v>2</v>
+      </c>
+      <c r="P613" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q613" t="n">
+        <v>0</v>
+      </c>
+      <c r="R613" t="n">
+        <v>2</v>
+      </c>
+      <c r="S613" t="n">
+        <v>0</v>
+      </c>
+      <c r="T613" t="n">
+        <v>0</v>
+      </c>
+      <c r="U613" t="n">
+        <v>0</v>
+      </c>
+      <c r="V613" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W613" t="n">
+        <v>29</v>
+      </c>
+      <c r="X613" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs LEYMA CORUÑA</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2486515</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>A. VRABAC | G. KALSCHEUR | I. VAZQUEZ PEREZ | R. DIAS MARQUES LISBOA SANTOS | R. GILL</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>5</v>
+      </c>
+      <c r="E614" t="n">
+        <v>22</v>
+      </c>
+      <c r="F614" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G614" t="n">
+        <v>0</v>
+      </c>
+      <c r="H614" t="n">
+        <v>1</v>
+      </c>
+      <c r="I614" t="n">
+        <v>0</v>
+      </c>
+      <c r="J614" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K614" t="n">
+        <v>0</v>
+      </c>
+      <c r="L614" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M614" t="n">
+        <v>0</v>
+      </c>
+      <c r="N614" t="n">
+        <v>1</v>
+      </c>
+      <c r="O614" t="n">
+        <v>0</v>
+      </c>
+      <c r="P614" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q614" t="n">
+        <v>1</v>
+      </c>
+      <c r="R614" t="n">
+        <v>0</v>
+      </c>
+      <c r="S614" t="n">
+        <v>2</v>
+      </c>
+      <c r="T614" t="n">
+        <v>0</v>
+      </c>
+      <c r="U614" t="n">
+        <v>0</v>
+      </c>
+      <c r="V614" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W614" t="n">
+        <v>29</v>
+      </c>
+      <c r="X614" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2486515</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>A. VRABAC | G. KALSCHEUR | R. DIAS MARQUES LISBOA SANTOS | R. GILL | S. MC DONNELL</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>5</v>
+      </c>
+      <c r="E615" t="n">
+        <v>64</v>
+      </c>
+      <c r="F615" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G615" t="n">
+        <v>4</v>
+      </c>
+      <c r="H615" t="n">
+        <v>8</v>
+      </c>
+      <c r="I615" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J615" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="K615" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L615" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="M615" t="n">
+        <v>-106.38</v>
+      </c>
+      <c r="N615" t="n">
+        <v>2</v>
+      </c>
+      <c r="O615" t="n">
+        <v>4</v>
+      </c>
+      <c r="P615" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q615" t="n">
+        <v>0</v>
+      </c>
+      <c r="R615" t="n">
+        <v>2</v>
+      </c>
+      <c r="S615" t="n">
+        <v>4</v>
+      </c>
+      <c r="T615" t="n">
+        <v>0</v>
+      </c>
+      <c r="U615" t="n">
+        <v>0</v>
+      </c>
+      <c r="V615" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W615" t="n">
+        <v>29</v>
+      </c>
+      <c r="X615" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2486515</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>D. ALDERETE DIAZ | D. LOVE | J. YU | M. LAPORNIK | P. HERNANDEZ MONTENEGRO</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>5</v>
+      </c>
+      <c r="E616" t="n">
+        <v>52</v>
+      </c>
+      <c r="F616" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G616" t="n">
+        <v>1</v>
+      </c>
+      <c r="H616" t="n">
+        <v>4</v>
+      </c>
+      <c r="I616" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J616" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K616" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L616" t="n">
+        <v>138.89</v>
+      </c>
+      <c r="M616" t="n">
+        <v>-25.25</v>
+      </c>
+      <c r="N616" t="n">
+        <v>0</v>
+      </c>
+      <c r="O616" t="n">
+        <v>2</v>
+      </c>
+      <c r="P616" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q616" t="n">
+        <v>0</v>
+      </c>
+      <c r="R616" t="n">
+        <v>3</v>
+      </c>
+      <c r="S616" t="n">
+        <v>2</v>
+      </c>
+      <c r="T616" t="n">
+        <v>0</v>
+      </c>
+      <c r="U616" t="n">
+        <v>1</v>
+      </c>
+      <c r="V616" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W616" t="n">
+        <v>29</v>
+      </c>
+      <c r="X616" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2486515</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>D. ALDERETE DIAZ | D. VAN OOSTRUM | J. YU | M. LAPORNIK | P. HERNANDEZ MONTENEGRO</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>5</v>
+      </c>
+      <c r="E617" t="n">
+        <v>23</v>
+      </c>
+      <c r="F617" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G617" t="n">
+        <v>4</v>
+      </c>
+      <c r="H617" t="n">
+        <v>0</v>
+      </c>
+      <c r="I617" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J617" t="n">
+        <v>0</v>
+      </c>
+      <c r="K617" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="L617" t="n">
+        <v>0</v>
+      </c>
+      <c r="M617" t="n">
+        <v>0</v>
+      </c>
+      <c r="N617" t="n">
+        <v>1</v>
+      </c>
+      <c r="O617" t="n">
+        <v>2</v>
+      </c>
+      <c r="P617" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q617" t="n">
+        <v>0</v>
+      </c>
+      <c r="R617" t="n">
+        <v>0</v>
+      </c>
+      <c r="S617" t="n">
+        <v>0</v>
+      </c>
+      <c r="T617" t="n">
+        <v>0</v>
+      </c>
+      <c r="U617" t="n">
+        <v>0</v>
+      </c>
+      <c r="V617" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W617" t="n">
+        <v>29</v>
+      </c>
+      <c r="X617" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2486515</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>J. YU | M. LAPORNIK | P. HERNANDEZ MONTENEGRO | R. JOHNSON JR</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>4</v>
+      </c>
+      <c r="E618" t="n">
+        <v>11</v>
+      </c>
+      <c r="F618" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G618" t="n">
+        <v>4</v>
+      </c>
+      <c r="H618" t="n">
+        <v>0</v>
+      </c>
+      <c r="I618" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J618" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K618" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="L618" t="n">
+        <v>0</v>
+      </c>
+      <c r="M618" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="N618" t="n">
+        <v>1</v>
+      </c>
+      <c r="O618" t="n">
+        <v>2</v>
+      </c>
+      <c r="P618" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q618" t="n">
+        <v>0</v>
+      </c>
+      <c r="R618" t="n">
+        <v>0</v>
+      </c>
+      <c r="S618" t="n">
+        <v>2</v>
+      </c>
+      <c r="T618" t="n">
+        <v>0</v>
+      </c>
+      <c r="U618" t="n">
+        <v>0</v>
+      </c>
+      <c r="V618" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W618" t="n">
+        <v>29</v>
+      </c>
+      <c r="X618" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2486516</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>D. DUSCAK | G. PARHAM II | M. TOWNES VILLAR | R. COSIALLS BORRAS | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>5</v>
+      </c>
+      <c r="E619" t="n">
+        <v>71</v>
+      </c>
+      <c r="F619" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G619" t="n">
+        <v>0</v>
+      </c>
+      <c r="H619" t="n">
+        <v>3</v>
+      </c>
+      <c r="I619" t="n">
+        <v>1</v>
+      </c>
+      <c r="J619" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K619" t="n">
+        <v>0</v>
+      </c>
+      <c r="L619" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="M619" t="n">
+        <v>-208.33</v>
+      </c>
+      <c r="N619" t="n">
+        <v>1</v>
+      </c>
+      <c r="O619" t="n">
+        <v>0</v>
+      </c>
+      <c r="P619" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q619" t="n">
+        <v>0</v>
+      </c>
+      <c r="R619" t="n">
+        <v>2</v>
+      </c>
+      <c r="S619" t="n">
+        <v>1</v>
+      </c>
+      <c r="T619" t="n">
+        <v>1</v>
+      </c>
+      <c r="U619" t="n">
+        <v>2</v>
+      </c>
+      <c r="V619" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W619" t="n">
+        <v>29</v>
+      </c>
+      <c r="X619" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2486516</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>B. DE BISSCHOP | D. MANCHON CRESPO | J. BELEMENE-DZABATOU | M. DIAZ | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>5</v>
+      </c>
+      <c r="E620" t="n">
+        <v>41</v>
+      </c>
+      <c r="F620" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G620" t="n">
+        <v>3</v>
+      </c>
+      <c r="H620" t="n">
+        <v>0</v>
+      </c>
+      <c r="I620" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J620" t="n">
+        <v>1</v>
+      </c>
+      <c r="K620" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="L620" t="n">
+        <v>0</v>
+      </c>
+      <c r="M620" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="N620" t="n">
+        <v>2</v>
+      </c>
+      <c r="O620" t="n">
+        <v>1</v>
+      </c>
+      <c r="P620" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q620" t="n">
+        <v>2</v>
+      </c>
+      <c r="R620" t="n">
+        <v>1</v>
+      </c>
+      <c r="S620" t="n">
+        <v>0</v>
+      </c>
+      <c r="T620" t="n">
+        <v>0</v>
+      </c>
+      <c r="U620" t="n">
+        <v>0</v>
+      </c>
+      <c r="V620" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W620" t="n">
+        <v>29</v>
+      </c>
+      <c r="X620" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2486516</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>B. DE BISSCHOP | J. BELEMENE-DZABATOU | M. DIAZ | P. ALI | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>5</v>
+      </c>
+      <c r="E621" t="n">
+        <v>30</v>
+      </c>
+      <c r="F621" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G621" t="n">
+        <v>0</v>
+      </c>
+      <c r="H621" t="n">
+        <v>0</v>
+      </c>
+      <c r="I621" t="n">
+        <v>0</v>
+      </c>
+      <c r="J621" t="n">
+        <v>0</v>
+      </c>
+      <c r="K621" t="n">
+        <v>0</v>
+      </c>
+      <c r="L621" t="n">
+        <v>0</v>
+      </c>
+      <c r="M621" t="n">
+        <v>0</v>
+      </c>
+      <c r="N621" t="n">
+        <v>0</v>
+      </c>
+      <c r="O621" t="n">
+        <v>0</v>
+      </c>
+      <c r="P621" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q621" t="n">
+        <v>0</v>
+      </c>
+      <c r="R621" t="n">
+        <v>0</v>
+      </c>
+      <c r="S621" t="n">
+        <v>0</v>
+      </c>
+      <c r="T621" t="n">
+        <v>0</v>
+      </c>
+      <c r="U621" t="n">
+        <v>0</v>
+      </c>
+      <c r="V621" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W621" t="n">
+        <v>29</v>
+      </c>
+      <c r="X621" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>A. MARTINEZ CLARIANA | B. PREPELIC | J. ROUND | J. VAN ZEGEREN | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>5</v>
+      </c>
+      <c r="E622" t="n">
+        <v>51</v>
+      </c>
+      <c r="F622" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G622" t="n">
+        <v>2</v>
+      </c>
+      <c r="H622" t="n">
+        <v>0</v>
+      </c>
+      <c r="I622" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J622" t="n">
+        <v>2</v>
+      </c>
+      <c r="K622" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="L622" t="n">
+        <v>0</v>
+      </c>
+      <c r="M622" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="N622" t="n">
+        <v>0</v>
+      </c>
+      <c r="O622" t="n">
+        <v>2</v>
+      </c>
+      <c r="P622" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q622" t="n">
+        <v>0</v>
+      </c>
+      <c r="R622" t="n">
+        <v>0</v>
+      </c>
+      <c r="S622" t="n">
+        <v>0</v>
+      </c>
+      <c r="T622" t="n">
+        <v>2</v>
+      </c>
+      <c r="U622" t="n">
+        <v>0</v>
+      </c>
+      <c r="V622" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W622" t="n">
+        <v>29</v>
+      </c>
+      <c r="X622" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>A. MARTINEZ CLARIANA | B. PREPELIC | J. ROUND | O. LO | T. NASPLER PERAIRE</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>5</v>
+      </c>
+      <c r="E623" t="n">
+        <v>11</v>
+      </c>
+      <c r="F623" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G623" t="n">
+        <v>2</v>
+      </c>
+      <c r="H623" t="n">
+        <v>0</v>
+      </c>
+      <c r="I623" t="n">
+        <v>1</v>
+      </c>
+      <c r="J623" t="n">
+        <v>1</v>
+      </c>
+      <c r="K623" t="n">
+        <v>200</v>
+      </c>
+      <c r="L623" t="n">
+        <v>0</v>
+      </c>
+      <c r="M623" t="n">
+        <v>200</v>
+      </c>
+      <c r="N623" t="n">
+        <v>1</v>
+      </c>
+      <c r="O623" t="n">
+        <v>0</v>
+      </c>
+      <c r="P623" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q623" t="n">
+        <v>0</v>
+      </c>
+      <c r="R623" t="n">
+        <v>1</v>
+      </c>
+      <c r="S623" t="n">
+        <v>0</v>
+      </c>
+      <c r="T623" t="n">
+        <v>0</v>
+      </c>
+      <c r="U623" t="n">
+        <v>0</v>
+      </c>
+      <c r="V623" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W623" t="n">
+        <v>29</v>
+      </c>
+      <c r="X623" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>A. MARTINEZ CLARIANA | B. PREPELIC | J. VAN ZEGEREN | T. NASPLER PERAIRE | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>5</v>
+      </c>
+      <c r="E624" t="n">
+        <v>35</v>
+      </c>
+      <c r="F624" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G624" t="n">
+        <v>0</v>
+      </c>
+      <c r="H624" t="n">
+        <v>2</v>
+      </c>
+      <c r="I624" t="n">
+        <v>1</v>
+      </c>
+      <c r="J624" t="n">
+        <v>1</v>
+      </c>
+      <c r="K624" t="n">
+        <v>0</v>
+      </c>
+      <c r="L624" t="n">
+        <v>200</v>
+      </c>
+      <c r="M624" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N624" t="n">
+        <v>0</v>
+      </c>
+      <c r="O624" t="n">
+        <v>0</v>
+      </c>
+      <c r="P624" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q624" t="n">
+        <v>0</v>
+      </c>
+      <c r="R624" t="n">
+        <v>1</v>
+      </c>
+      <c r="S624" t="n">
+        <v>0</v>
+      </c>
+      <c r="T624" t="n">
+        <v>0</v>
+      </c>
+      <c r="U624" t="n">
+        <v>0</v>
+      </c>
+      <c r="V624" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W624" t="n">
+        <v>29</v>
+      </c>
+      <c r="X624" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>B. PREPELIC | C. ROGERS | J. PERIS CRESPO | J. VAN ZEGEREN | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>5</v>
+      </c>
+      <c r="E625" t="n">
+        <v>16</v>
+      </c>
+      <c r="F625" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G625" t="n">
+        <v>0</v>
+      </c>
+      <c r="H625" t="n">
+        <v>2</v>
+      </c>
+      <c r="I625" t="n">
+        <v>0</v>
+      </c>
+      <c r="J625" t="n">
+        <v>1</v>
+      </c>
+      <c r="K625" t="n">
+        <v>0</v>
+      </c>
+      <c r="L625" t="n">
+        <v>200</v>
+      </c>
+      <c r="M625" t="n">
+        <v>0</v>
+      </c>
+      <c r="N625" t="n">
+        <v>0</v>
+      </c>
+      <c r="O625" t="n">
+        <v>0</v>
+      </c>
+      <c r="P625" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q625" t="n">
+        <v>0</v>
+      </c>
+      <c r="R625" t="n">
+        <v>1</v>
+      </c>
+      <c r="S625" t="n">
+        <v>0</v>
+      </c>
+      <c r="T625" t="n">
+        <v>0</v>
+      </c>
+      <c r="U625" t="n">
+        <v>0</v>
+      </c>
+      <c r="V625" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W625" t="n">
+        <v>29</v>
+      </c>
+      <c r="X625" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>B. PREPELIC | C. ROGERS | J. VAN ZEGEREN | T. NASPLER PERAIRE | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>5</v>
+      </c>
+      <c r="E626" t="n">
+        <v>80</v>
+      </c>
+      <c r="F626" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G626" t="n">
+        <v>1</v>
+      </c>
+      <c r="H626" t="n">
+        <v>0</v>
+      </c>
+      <c r="I626" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J626" t="n">
+        <v>3</v>
+      </c>
+      <c r="K626" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="L626" t="n">
+        <v>0</v>
+      </c>
+      <c r="M626" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="N626" t="n">
+        <v>2</v>
+      </c>
+      <c r="O626" t="n">
+        <v>2</v>
+      </c>
+      <c r="P626" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q626" t="n">
+        <v>1</v>
+      </c>
+      <c r="R626" t="n">
+        <v>3</v>
+      </c>
+      <c r="S626" t="n">
+        <v>0</v>
+      </c>
+      <c r="T626" t="n">
+        <v>1</v>
+      </c>
+      <c r="U626" t="n">
+        <v>1</v>
+      </c>
+      <c r="V626" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W626" t="n">
+        <v>29</v>
+      </c>
+      <c r="X626" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>C. ROGERS | D. KRISTENSEN | J. PERIS CRESPO | J. ROUND | O. LO</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>5</v>
+      </c>
+      <c r="E627" t="n">
+        <v>100</v>
+      </c>
+      <c r="F627" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G627" t="n">
+        <v>2</v>
+      </c>
+      <c r="H627" t="n">
+        <v>3</v>
+      </c>
+      <c r="I627" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J627" t="n">
+        <v>2</v>
+      </c>
+      <c r="K627" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L627" t="n">
+        <v>150</v>
+      </c>
+      <c r="M627" t="n">
+        <v>77.27</v>
+      </c>
+      <c r="N627" t="n">
+        <v>1</v>
+      </c>
+      <c r="O627" t="n">
+        <v>2</v>
+      </c>
+      <c r="P627" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q627" t="n">
+        <v>2</v>
+      </c>
+      <c r="R627" t="n">
+        <v>3</v>
+      </c>
+      <c r="S627" t="n">
+        <v>0</v>
+      </c>
+      <c r="T627" t="n">
+        <v>0</v>
+      </c>
+      <c r="U627" t="n">
+        <v>1</v>
+      </c>
+      <c r="V627" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W627" t="n">
+        <v>29</v>
+      </c>
+      <c r="X627" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>A. SCARIOLO ARES | B. VAZQUEZ ARRAIZA | J. ARAMBURU LAMY | L. SMITH | O. MATULIONIS</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>5</v>
+      </c>
+      <c r="E628" t="n">
+        <v>17</v>
+      </c>
+      <c r="F628" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G628" t="n">
+        <v>3</v>
+      </c>
+      <c r="H628" t="n">
+        <v>0</v>
+      </c>
+      <c r="I628" t="n">
+        <v>1</v>
+      </c>
+      <c r="J628" t="n">
+        <v>0</v>
+      </c>
+      <c r="K628" t="n">
+        <v>300</v>
+      </c>
+      <c r="L628" t="n">
+        <v>0</v>
+      </c>
+      <c r="M628" t="n">
+        <v>0</v>
+      </c>
+      <c r="N628" t="n">
+        <v>1</v>
+      </c>
+      <c r="O628" t="n">
+        <v>0</v>
+      </c>
+      <c r="P628" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q628" t="n">
+        <v>0</v>
+      </c>
+      <c r="R628" t="n">
+        <v>0</v>
+      </c>
+      <c r="S628" t="n">
+        <v>0</v>
+      </c>
+      <c r="T628" t="n">
+        <v>0</v>
+      </c>
+      <c r="U628" t="n">
+        <v>0</v>
+      </c>
+      <c r="V628" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W628" t="n">
+        <v>29</v>
+      </c>
+      <c r="X628" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>A. SCARIOLO ARES | B. VAZQUEZ ARRAIZA | J. ARAMBURU LAMY | O. MATULIONIS | P. BOMBINO PARADA</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>5</v>
+      </c>
+      <c r="E629" t="n">
+        <v>252</v>
+      </c>
+      <c r="F629" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G629" t="n">
+        <v>2</v>
+      </c>
+      <c r="H629" t="n">
+        <v>7</v>
+      </c>
+      <c r="I629" t="n">
+        <v>8</v>
+      </c>
+      <c r="J629" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="K629" t="n">
+        <v>25</v>
+      </c>
+      <c r="L629" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="M629" t="n">
+        <v>-66.62</v>
+      </c>
+      <c r="N629" t="n">
+        <v>7</v>
+      </c>
+      <c r="O629" t="n">
+        <v>0</v>
+      </c>
+      <c r="P629" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q629" t="n">
+        <v>2</v>
+      </c>
+      <c r="R629" t="n">
+        <v>4</v>
+      </c>
+      <c r="S629" t="n">
+        <v>6</v>
+      </c>
+      <c r="T629" t="n">
+        <v>4</v>
+      </c>
+      <c r="U629" t="n">
+        <v>3</v>
+      </c>
+      <c r="V629" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W629" t="n">
+        <v>29</v>
+      </c>
+      <c r="X629" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>A. SCARIOLO ARES | J. ARAMBURU LAMY | J. BOCCA | O. MATULIONIS | P. BOMBINO PARADA</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>5</v>
+      </c>
+      <c r="E630" t="n">
+        <v>24</v>
+      </c>
+      <c r="F630" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G630" t="n">
+        <v>2</v>
+      </c>
+      <c r="H630" t="n">
+        <v>0</v>
+      </c>
+      <c r="I630" t="n">
+        <v>1</v>
+      </c>
+      <c r="J630" t="n">
+        <v>0</v>
+      </c>
+      <c r="K630" t="n">
+        <v>200</v>
+      </c>
+      <c r="L630" t="n">
+        <v>0</v>
+      </c>
+      <c r="M630" t="n">
+        <v>0</v>
+      </c>
+      <c r="N630" t="n">
+        <v>1</v>
+      </c>
+      <c r="O630" t="n">
+        <v>0</v>
+      </c>
+      <c r="P630" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q630" t="n">
+        <v>0</v>
+      </c>
+      <c r="R630" t="n">
+        <v>0</v>
+      </c>
+      <c r="S630" t="n">
+        <v>0</v>
+      </c>
+      <c r="T630" t="n">
+        <v>0</v>
+      </c>
+      <c r="U630" t="n">
+        <v>0</v>
+      </c>
+      <c r="V630" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W630" t="n">
+        <v>29</v>
+      </c>
+      <c r="X630" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2486514</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>A. GARUBA ALARI | A. MARTIN MARIN | J. LOPEZ SANTANA | K. WEBSTER | S. SVEJCAR</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>5</v>
+      </c>
+      <c r="E631" t="n">
+        <v>5</v>
+      </c>
+      <c r="F631" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G631" t="n">
+        <v>2</v>
+      </c>
+      <c r="H631" t="n">
+        <v>0</v>
+      </c>
+      <c r="I631" t="n">
+        <v>1</v>
+      </c>
+      <c r="J631" t="n">
+        <v>0</v>
+      </c>
+      <c r="K631" t="n">
+        <v>200</v>
+      </c>
+      <c r="L631" t="n">
+        <v>0</v>
+      </c>
+      <c r="M631" t="n">
+        <v>0</v>
+      </c>
+      <c r="N631" t="n">
+        <v>1</v>
+      </c>
+      <c r="O631" t="n">
+        <v>0</v>
+      </c>
+      <c r="P631" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q631" t="n">
+        <v>0</v>
+      </c>
+      <c r="R631" t="n">
+        <v>0</v>
+      </c>
+      <c r="S631" t="n">
+        <v>0</v>
+      </c>
+      <c r="T631" t="n">
+        <v>0</v>
+      </c>
+      <c r="U631" t="n">
+        <v>0</v>
+      </c>
+      <c r="V631" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W631" t="n">
+        <v>29</v>
+      </c>
+      <c r="X631" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA vs GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2486514</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>A. GARUBA ALARI | A. MARTIN MARIN | J. LOPEZ SANTANA | K. WEBSTER | V. FAVERANI TATSCH</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>5</v>
+      </c>
+      <c r="E632" t="n">
+        <v>18</v>
+      </c>
+      <c r="F632" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G632" t="n">
+        <v>2</v>
+      </c>
+      <c r="H632" t="n">
+        <v>4</v>
+      </c>
+      <c r="I632" t="n">
+        <v>2</v>
+      </c>
+      <c r="J632" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K632" t="n">
+        <v>100</v>
+      </c>
+      <c r="L632" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M632" t="n">
+        <v>-127.27</v>
+      </c>
+      <c r="N632" t="n">
+        <v>2</v>
+      </c>
+      <c r="O632" t="n">
+        <v>0</v>
+      </c>
+      <c r="P632" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q632" t="n">
+        <v>0</v>
+      </c>
+      <c r="R632" t="n">
+        <v>0</v>
+      </c>
+      <c r="S632" t="n">
+        <v>4</v>
+      </c>
+      <c r="T632" t="n">
+        <v>0</v>
+      </c>
+      <c r="U632" t="n">
+        <v>0</v>
+      </c>
+      <c r="V632" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W632" t="n">
+        <v>29</v>
+      </c>
+      <c r="X632" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA vs GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2486514</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>A. GARUBA ALARI | A. MARTIN MARIN | K. WEBSTER | S. SVEJCAR | V. FAVERANI TATSCH</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>5</v>
+      </c>
+      <c r="E633" t="n">
+        <v>215</v>
+      </c>
+      <c r="F633" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="G633" t="n">
+        <v>4</v>
+      </c>
+      <c r="H633" t="n">
+        <v>8</v>
+      </c>
+      <c r="I633" t="n">
+        <v>4</v>
+      </c>
+      <c r="J633" t="n">
+        <v>5</v>
+      </c>
+      <c r="K633" t="n">
+        <v>100</v>
+      </c>
+      <c r="L633" t="n">
+        <v>160</v>
+      </c>
+      <c r="M633" t="n">
+        <v>-60</v>
+      </c>
+      <c r="N633" t="n">
+        <v>5</v>
+      </c>
+      <c r="O633" t="n">
+        <v>0</v>
+      </c>
+      <c r="P633" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q633" t="n">
+        <v>1</v>
+      </c>
+      <c r="R633" t="n">
+        <v>7</v>
+      </c>
+      <c r="S633" t="n">
+        <v>0</v>
+      </c>
+      <c r="T633" t="n">
+        <v>2</v>
+      </c>
+      <c r="U633" t="n">
+        <v>4</v>
+      </c>
+      <c r="V633" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W633" t="n">
+        <v>29</v>
+      </c>
+      <c r="X633" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA vs GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2486514</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>A. GARUBA ALARI | J. LOPEZ SANTANA | K. WEBSTER | S. SVEJCAR | V. FAVERANI TATSCH</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>5</v>
+      </c>
+      <c r="E634" t="n">
+        <v>4</v>
+      </c>
+      <c r="F634" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G634" t="n">
+        <v>0</v>
+      </c>
+      <c r="H634" t="n">
+        <v>0</v>
+      </c>
+      <c r="I634" t="n">
+        <v>0</v>
+      </c>
+      <c r="J634" t="n">
+        <v>1</v>
+      </c>
+      <c r="K634" t="n">
+        <v>0</v>
+      </c>
+      <c r="L634" t="n">
+        <v>0</v>
+      </c>
+      <c r="M634" t="n">
+        <v>0</v>
+      </c>
+      <c r="N634" t="n">
+        <v>0</v>
+      </c>
+      <c r="O634" t="n">
+        <v>0</v>
+      </c>
+      <c r="P634" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q634" t="n">
+        <v>0</v>
+      </c>
+      <c r="R634" t="n">
+        <v>0</v>
+      </c>
+      <c r="S634" t="n">
+        <v>0</v>
+      </c>
+      <c r="T634" t="n">
+        <v>1</v>
+      </c>
+      <c r="U634" t="n">
+        <v>0</v>
+      </c>
+      <c r="V634" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W634" t="n">
+        <v>29</v>
+      </c>
+      <c r="X634" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA vs GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2486514</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>A. SOLA IDDRISU | E. VICEDO AYALA | E. WEMBI | F. ZURBRIGGEN | S. LITTLESON</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>5</v>
+      </c>
+      <c r="E635" t="n">
+        <v>47</v>
+      </c>
+      <c r="F635" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G635" t="n">
+        <v>4</v>
+      </c>
+      <c r="H635" t="n">
+        <v>2</v>
+      </c>
+      <c r="I635" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J635" t="n">
+        <v>3</v>
+      </c>
+      <c r="K635" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L635" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="M635" t="n">
+        <v>160.61</v>
+      </c>
+      <c r="N635" t="n">
+        <v>0</v>
+      </c>
+      <c r="O635" t="n">
+        <v>4</v>
+      </c>
+      <c r="P635" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q635" t="n">
+        <v>1</v>
+      </c>
+      <c r="R635" t="n">
+        <v>3</v>
+      </c>
+      <c r="S635" t="n">
+        <v>0</v>
+      </c>
+      <c r="T635" t="n">
+        <v>0</v>
+      </c>
+      <c r="U635" t="n">
+        <v>0</v>
+      </c>
+      <c r="V635" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W635" t="n">
+        <v>29</v>
+      </c>
+      <c r="X635" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA vs GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2486514</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>A. SOLA IDDRISU | E. VICEDO AYALA | F. ZURBRIGGEN | J. LOBO MARTORELL | V. ARTEAGA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>5</v>
+      </c>
+      <c r="E636" t="n">
+        <v>6</v>
+      </c>
+      <c r="F636" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G636" t="n">
+        <v>0</v>
+      </c>
+      <c r="H636" t="n">
+        <v>0</v>
+      </c>
+      <c r="I636" t="n">
+        <v>1</v>
+      </c>
+      <c r="J636" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K636" t="n">
+        <v>0</v>
+      </c>
+      <c r="L636" t="n">
+        <v>0</v>
+      </c>
+      <c r="M636" t="n">
+        <v>0</v>
+      </c>
+      <c r="N636" t="n">
+        <v>1</v>
+      </c>
+      <c r="O636" t="n">
+        <v>0</v>
+      </c>
+      <c r="P636" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q636" t="n">
+        <v>0</v>
+      </c>
+      <c r="R636" t="n">
+        <v>0</v>
+      </c>
+      <c r="S636" t="n">
+        <v>0</v>
+      </c>
+      <c r="T636" t="n">
+        <v>0</v>
+      </c>
+      <c r="U636" t="n">
+        <v>1</v>
+      </c>
+      <c r="V636" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W636" t="n">
+        <v>29</v>
+      </c>
+      <c r="X636" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA vs GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2486514</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>A. SOLA IDDRISU | E. VICEDO AYALA | F. ZURBRIGGEN | S. LITTLESON | V. ARTEAGA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>5</v>
+      </c>
+      <c r="E637" t="n">
+        <v>184</v>
+      </c>
+      <c r="F637" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="G637" t="n">
+        <v>8</v>
+      </c>
+      <c r="H637" t="n">
+        <v>4</v>
+      </c>
+      <c r="I637" t="n">
+        <v>5</v>
+      </c>
+      <c r="J637" t="n">
+        <v>4</v>
+      </c>
+      <c r="K637" t="n">
+        <v>160</v>
+      </c>
+      <c r="L637" t="n">
+        <v>100</v>
+      </c>
+      <c r="M637" t="n">
+        <v>60</v>
+      </c>
+      <c r="N637" t="n">
+        <v>6</v>
+      </c>
+      <c r="O637" t="n">
+        <v>0</v>
+      </c>
+      <c r="P637" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q637" t="n">
+        <v>3</v>
+      </c>
+      <c r="R637" t="n">
+        <v>4</v>
+      </c>
+      <c r="S637" t="n">
+        <v>0</v>
+      </c>
+      <c r="T637" t="n">
+        <v>0</v>
+      </c>
+      <c r="U637" t="n">
+        <v>0</v>
+      </c>
+      <c r="V637" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W637" t="n">
+        <v>29</v>
+      </c>
+      <c r="X637" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA vs GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2486514</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>E. VICEDO AYALA | E. WEMBI | F. ZURBRIGGEN | J. LOBO MARTORELL | S. LITTLESON</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>5</v>
+      </c>
+      <c r="E638" t="n">
+        <v>5</v>
+      </c>
+      <c r="F638" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G638" t="n">
+        <v>0</v>
+      </c>
+      <c r="H638" t="n">
+        <v>2</v>
+      </c>
+      <c r="I638" t="n">
+        <v>0</v>
+      </c>
+      <c r="J638" t="n">
+        <v>1</v>
+      </c>
+      <c r="K638" t="n">
+        <v>0</v>
+      </c>
+      <c r="L638" t="n">
+        <v>200</v>
+      </c>
+      <c r="M638" t="n">
+        <v>0</v>
+      </c>
+      <c r="N638" t="n">
+        <v>0</v>
+      </c>
+      <c r="O638" t="n">
+        <v>0</v>
+      </c>
+      <c r="P638" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q638" t="n">
+        <v>0</v>
+      </c>
+      <c r="R638" t="n">
+        <v>1</v>
+      </c>
+      <c r="S638" t="n">
+        <v>0</v>
+      </c>
+      <c r="T638" t="n">
+        <v>0</v>
+      </c>
+      <c r="U638" t="n">
+        <v>0</v>
+      </c>
+      <c r="V638" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W638" t="n">
+        <v>29</v>
+      </c>
+      <c r="X638" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA vs GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2486511</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>C. DIAZ RODRIGUEZ | I. CRUZ UCEDA | M. CAICEDO SANCHEZ | S. CECCARDI | S. RODRIGUEZ FEBLES</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>5</v>
+      </c>
+      <c r="E639" t="n">
+        <v>7</v>
+      </c>
+      <c r="F639" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G639" t="n">
+        <v>0</v>
+      </c>
+      <c r="H639" t="n">
+        <v>2</v>
+      </c>
+      <c r="I639" t="n">
+        <v>1</v>
+      </c>
+      <c r="J639" t="n">
+        <v>1</v>
+      </c>
+      <c r="K639" t="n">
+        <v>0</v>
+      </c>
+      <c r="L639" t="n">
+        <v>200</v>
+      </c>
+      <c r="M639" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N639" t="n">
+        <v>0</v>
+      </c>
+      <c r="O639" t="n">
+        <v>0</v>
+      </c>
+      <c r="P639" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q639" t="n">
+        <v>0</v>
+      </c>
+      <c r="R639" t="n">
+        <v>1</v>
+      </c>
+      <c r="S639" t="n">
+        <v>0</v>
+      </c>
+      <c r="T639" t="n">
+        <v>0</v>
+      </c>
+      <c r="U639" t="n">
+        <v>0</v>
+      </c>
+      <c r="V639" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W639" t="n">
+        <v>29</v>
+      </c>
+      <c r="X639" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE vs PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2486511</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>C. DIAZ RODRIGUEZ | J. GODSPOWER JOHNSON | M. CAICEDO SANCHEZ | N. HOOVER | S. RODRIGUEZ FEBLES</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>5</v>
+      </c>
+      <c r="E640" t="n">
+        <v>95</v>
+      </c>
+      <c r="F640" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G640" t="n">
+        <v>8</v>
+      </c>
+      <c r="H640" t="n">
+        <v>0</v>
+      </c>
+      <c r="I640" t="n">
+        <v>3</v>
+      </c>
+      <c r="J640" t="n">
+        <v>2</v>
+      </c>
+      <c r="K640" t="n">
+        <v>266.67</v>
+      </c>
+      <c r="L640" t="n">
+        <v>0</v>
+      </c>
+      <c r="M640" t="n">
+        <v>266.67</v>
+      </c>
+      <c r="N640" t="n">
+        <v>4</v>
+      </c>
+      <c r="O640" t="n">
+        <v>0</v>
+      </c>
+      <c r="P640" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q640" t="n">
+        <v>1</v>
+      </c>
+      <c r="R640" t="n">
+        <v>2</v>
+      </c>
+      <c r="S640" t="n">
+        <v>0</v>
+      </c>
+      <c r="T640" t="n">
+        <v>0</v>
+      </c>
+      <c r="U640" t="n">
+        <v>0</v>
+      </c>
+      <c r="V640" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W640" t="n">
+        <v>29</v>
+      </c>
+      <c r="X640" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE vs PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2486511</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>C. DIAZ RODRIGUEZ | M. CAICEDO SANCHEZ | N. MC MULLEN | S. CECCARDI | S. RODRIGUEZ FEBLES</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>5</v>
+      </c>
+      <c r="E641" t="n">
+        <v>15</v>
+      </c>
+      <c r="F641" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G641" t="n">
+        <v>2</v>
+      </c>
+      <c r="H641" t="n">
+        <v>1</v>
+      </c>
+      <c r="I641" t="n">
+        <v>1</v>
+      </c>
+      <c r="J641" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K641" t="n">
+        <v>200</v>
+      </c>
+      <c r="L641" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M641" t="n">
+        <v>-27.27</v>
+      </c>
+      <c r="N641" t="n">
+        <v>1</v>
+      </c>
+      <c r="O641" t="n">
+        <v>0</v>
+      </c>
+      <c r="P641" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q641" t="n">
+        <v>0</v>
+      </c>
+      <c r="R641" t="n">
+        <v>0</v>
+      </c>
+      <c r="S641" t="n">
+        <v>1</v>
+      </c>
+      <c r="T641" t="n">
+        <v>0</v>
+      </c>
+      <c r="U641" t="n">
+        <v>0</v>
+      </c>
+      <c r="V641" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W641" t="n">
+        <v>29</v>
+      </c>
+      <c r="X641" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE vs PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2486511</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>J. GODSPOWER JOHNSON | M. CAICEDO SANCHEZ | N. HOOVER | S. CECCARDI | S. RODRIGUEZ FEBLES</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>5</v>
+      </c>
+      <c r="E642" t="n">
+        <v>37</v>
+      </c>
+      <c r="F642" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G642" t="n">
+        <v>0</v>
+      </c>
+      <c r="H642" t="n">
+        <v>0</v>
+      </c>
+      <c r="I642" t="n">
+        <v>0</v>
+      </c>
+      <c r="J642" t="n">
+        <v>1</v>
+      </c>
+      <c r="K642" t="n">
+        <v>0</v>
+      </c>
+      <c r="L642" t="n">
+        <v>0</v>
+      </c>
+      <c r="M642" t="n">
+        <v>0</v>
+      </c>
+      <c r="N642" t="n">
+        <v>1</v>
+      </c>
+      <c r="O642" t="n">
+        <v>0</v>
+      </c>
+      <c r="P642" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q642" t="n">
+        <v>1</v>
+      </c>
+      <c r="R642" t="n">
+        <v>1</v>
+      </c>
+      <c r="S642" t="n">
+        <v>0</v>
+      </c>
+      <c r="T642" t="n">
+        <v>0</v>
+      </c>
+      <c r="U642" t="n">
+        <v>0</v>
+      </c>
+      <c r="V642" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W642" t="n">
+        <v>29</v>
+      </c>
+      <c r="X642" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE vs PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2486511</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>A. COMENDADOR FEMENIAS | A. URDIAIN LABAYEN | G. DIKE EGUN | H. ATENCIA SUAREZ | J. FELIU ESPEJO</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>5</v>
+      </c>
+      <c r="E643" t="n">
+        <v>7</v>
+      </c>
+      <c r="F643" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G643" t="n">
+        <v>2</v>
+      </c>
+      <c r="H643" t="n">
+        <v>0</v>
+      </c>
+      <c r="I643" t="n">
+        <v>1</v>
+      </c>
+      <c r="J643" t="n">
+        <v>1</v>
+      </c>
+      <c r="K643" t="n">
+        <v>200</v>
+      </c>
+      <c r="L643" t="n">
+        <v>0</v>
+      </c>
+      <c r="M643" t="n">
+        <v>200</v>
+      </c>
+      <c r="N643" t="n">
+        <v>1</v>
+      </c>
+      <c r="O643" t="n">
+        <v>0</v>
+      </c>
+      <c r="P643" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q643" t="n">
+        <v>0</v>
+      </c>
+      <c r="R643" t="n">
+        <v>0</v>
+      </c>
+      <c r="S643" t="n">
+        <v>0</v>
+      </c>
+      <c r="T643" t="n">
+        <v>1</v>
+      </c>
+      <c r="U643" t="n">
+        <v>0</v>
+      </c>
+      <c r="V643" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W643" t="n">
+        <v>29</v>
+      </c>
+      <c r="X643" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE vs PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2486511</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>A. COMENDADOR FEMENIAS | D. SANADZE | G. DIKE EGUN | H. ATENCIA SUAREZ | J. FELIU ESPEJO</t>
+        </is>
+      </c>
+      <c r="D644" t="n">
+        <v>5</v>
+      </c>
+      <c r="E644" t="n">
+        <v>16</v>
+      </c>
+      <c r="F644" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G644" t="n">
+        <v>1</v>
+      </c>
+      <c r="H644" t="n">
+        <v>4</v>
+      </c>
+      <c r="I644" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J644" t="n">
+        <v>2</v>
+      </c>
+      <c r="K644" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L644" t="n">
+        <v>200</v>
+      </c>
+      <c r="M644" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="N644" t="n">
+        <v>0</v>
+      </c>
+      <c r="O644" t="n">
+        <v>1</v>
+      </c>
+      <c r="P644" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q644" t="n">
+        <v>0</v>
+      </c>
+      <c r="R644" t="n">
+        <v>2</v>
+      </c>
+      <c r="S644" t="n">
+        <v>0</v>
+      </c>
+      <c r="T644" t="n">
+        <v>0</v>
+      </c>
+      <c r="U644" t="n">
+        <v>0</v>
+      </c>
+      <c r="V644" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W644" t="n">
+        <v>29</v>
+      </c>
+      <c r="X644" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE vs PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2486511</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>A. IZAW BOLAVIE | D. SANADZE | G. DIKE EGUN | H. ATENCIA SUAREZ | J. FELIU ESPEJO</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>5</v>
+      </c>
+      <c r="E645" t="n">
+        <v>131</v>
+      </c>
+      <c r="F645" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G645" t="n">
+        <v>0</v>
+      </c>
+      <c r="H645" t="n">
+        <v>6</v>
+      </c>
+      <c r="I645" t="n">
+        <v>3</v>
+      </c>
+      <c r="J645" t="n">
+        <v>2</v>
+      </c>
+      <c r="K645" t="n">
+        <v>0</v>
+      </c>
+      <c r="L645" t="n">
+        <v>300</v>
+      </c>
+      <c r="M645" t="n">
+        <v>-300</v>
+      </c>
+      <c r="N645" t="n">
+        <v>3</v>
+      </c>
+      <c r="O645" t="n">
+        <v>0</v>
+      </c>
+      <c r="P645" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q645" t="n">
+        <v>0</v>
+      </c>
+      <c r="R645" t="n">
+        <v>4</v>
+      </c>
+      <c r="S645" t="n">
+        <v>0</v>
+      </c>
+      <c r="T645" t="n">
+        <v>0</v>
+      </c>
+      <c r="U645" t="n">
+        <v>2</v>
+      </c>
+      <c r="V645" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W645" t="n">
+        <v>29</v>
+      </c>
+      <c r="X645" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE vs PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/1FEB_25_26/clutch_lineups_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/clutch_lineups_25_26_1FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X645"/>
+  <dimension ref="A1:X695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54646,6 +54646,4206 @@
         </is>
       </c>
     </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2486525</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>J. POWELL | J. YU | M. LAPORNIK | P. HERNANDEZ MONTENEGRO | R. JOHNSON JR</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>5</v>
+      </c>
+      <c r="E646" t="n">
+        <v>7</v>
+      </c>
+      <c r="F646" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G646" t="n">
+        <v>0</v>
+      </c>
+      <c r="H646" t="n">
+        <v>0</v>
+      </c>
+      <c r="I646" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J646" t="n">
+        <v>1</v>
+      </c>
+      <c r="K646" t="n">
+        <v>0</v>
+      </c>
+      <c r="L646" t="n">
+        <v>0</v>
+      </c>
+      <c r="M646" t="n">
+        <v>0</v>
+      </c>
+      <c r="N646" t="n">
+        <v>1</v>
+      </c>
+      <c r="O646" t="n">
+        <v>2</v>
+      </c>
+      <c r="P646" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q646" t="n">
+        <v>0</v>
+      </c>
+      <c r="R646" t="n">
+        <v>0</v>
+      </c>
+      <c r="S646" t="n">
+        <v>0</v>
+      </c>
+      <c r="T646" t="n">
+        <v>1</v>
+      </c>
+      <c r="U646" t="n">
+        <v>0</v>
+      </c>
+      <c r="V646" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W646" t="n">
+        <v>30</v>
+      </c>
+      <c r="X646" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2486525</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>J. MWEMA | K. LARSEN | S. HOLLANDERS | U. MENDICOTE RUBIO | Y. JOSEPH</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>5</v>
+      </c>
+      <c r="E647" t="n">
+        <v>7</v>
+      </c>
+      <c r="F647" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G647" t="n">
+        <v>0</v>
+      </c>
+      <c r="H647" t="n">
+        <v>0</v>
+      </c>
+      <c r="I647" t="n">
+        <v>1</v>
+      </c>
+      <c r="J647" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K647" t="n">
+        <v>0</v>
+      </c>
+      <c r="L647" t="n">
+        <v>0</v>
+      </c>
+      <c r="M647" t="n">
+        <v>0</v>
+      </c>
+      <c r="N647" t="n">
+        <v>0</v>
+      </c>
+      <c r="O647" t="n">
+        <v>0</v>
+      </c>
+      <c r="P647" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q647" t="n">
+        <v>0</v>
+      </c>
+      <c r="R647" t="n">
+        <v>1</v>
+      </c>
+      <c r="S647" t="n">
+        <v>2</v>
+      </c>
+      <c r="T647" t="n">
+        <v>0</v>
+      </c>
+      <c r="U647" t="n">
+        <v>0</v>
+      </c>
+      <c r="V647" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W647" t="n">
+        <v>30</v>
+      </c>
+      <c r="X647" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2486524</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>A. LIMA BRITO | B. DE BISSCHOP | D. MANCHON CRESPO | G. RENFROE | M. DIAZ</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>5</v>
+      </c>
+      <c r="E648" t="n">
+        <v>15</v>
+      </c>
+      <c r="F648" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G648" t="n">
+        <v>3</v>
+      </c>
+      <c r="H648" t="n">
+        <v>0</v>
+      </c>
+      <c r="I648" t="n">
+        <v>1</v>
+      </c>
+      <c r="J648" t="n">
+        <v>0</v>
+      </c>
+      <c r="K648" t="n">
+        <v>300</v>
+      </c>
+      <c r="L648" t="n">
+        <v>0</v>
+      </c>
+      <c r="M648" t="n">
+        <v>0</v>
+      </c>
+      <c r="N648" t="n">
+        <v>1</v>
+      </c>
+      <c r="O648" t="n">
+        <v>0</v>
+      </c>
+      <c r="P648" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q648" t="n">
+        <v>0</v>
+      </c>
+      <c r="R648" t="n">
+        <v>0</v>
+      </c>
+      <c r="S648" t="n">
+        <v>0</v>
+      </c>
+      <c r="T648" t="n">
+        <v>0</v>
+      </c>
+      <c r="U648" t="n">
+        <v>0</v>
+      </c>
+      <c r="V648" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W648" t="n">
+        <v>30</v>
+      </c>
+      <c r="X648" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2486524</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>A. LIMA BRITO | B. DE BISSCHOP | G. RENFROE | M. DIAZ | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>5</v>
+      </c>
+      <c r="E649" t="n">
+        <v>4</v>
+      </c>
+      <c r="F649" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G649" t="n">
+        <v>0</v>
+      </c>
+      <c r="H649" t="n">
+        <v>0</v>
+      </c>
+      <c r="I649" t="n">
+        <v>1</v>
+      </c>
+      <c r="J649" t="n">
+        <v>0</v>
+      </c>
+      <c r="K649" t="n">
+        <v>0</v>
+      </c>
+      <c r="L649" t="n">
+        <v>0</v>
+      </c>
+      <c r="M649" t="n">
+        <v>0</v>
+      </c>
+      <c r="N649" t="n">
+        <v>0</v>
+      </c>
+      <c r="O649" t="n">
+        <v>0</v>
+      </c>
+      <c r="P649" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q649" t="n">
+        <v>0</v>
+      </c>
+      <c r="R649" t="n">
+        <v>0</v>
+      </c>
+      <c r="S649" t="n">
+        <v>0</v>
+      </c>
+      <c r="T649" t="n">
+        <v>0</v>
+      </c>
+      <c r="U649" t="n">
+        <v>0</v>
+      </c>
+      <c r="V649" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W649" t="n">
+        <v>30</v>
+      </c>
+      <c r="X649" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2486524</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>B. DE BISSCHOP | D. MANCHON CRESPO | G. RENFROE | J. BELEMENE-DZABATOU | M. DIAZ</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>5</v>
+      </c>
+      <c r="E650" t="n">
+        <v>10</v>
+      </c>
+      <c r="F650" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G650" t="n">
+        <v>0</v>
+      </c>
+      <c r="H650" t="n">
+        <v>0</v>
+      </c>
+      <c r="I650" t="n">
+        <v>1</v>
+      </c>
+      <c r="J650" t="n">
+        <v>0</v>
+      </c>
+      <c r="K650" t="n">
+        <v>0</v>
+      </c>
+      <c r="L650" t="n">
+        <v>0</v>
+      </c>
+      <c r="M650" t="n">
+        <v>0</v>
+      </c>
+      <c r="N650" t="n">
+        <v>1</v>
+      </c>
+      <c r="O650" t="n">
+        <v>0</v>
+      </c>
+      <c r="P650" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q650" t="n">
+        <v>0</v>
+      </c>
+      <c r="R650" t="n">
+        <v>0</v>
+      </c>
+      <c r="S650" t="n">
+        <v>0</v>
+      </c>
+      <c r="T650" t="n">
+        <v>0</v>
+      </c>
+      <c r="U650" t="n">
+        <v>0</v>
+      </c>
+      <c r="V650" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W650" t="n">
+        <v>30</v>
+      </c>
+      <c r="X650" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2486524</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>B. DE BISSCHOP | D. MANCHON CRESPO | G. RENFROE | M. DIAZ | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>5</v>
+      </c>
+      <c r="E651" t="n">
+        <v>22</v>
+      </c>
+      <c r="F651" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G651" t="n">
+        <v>0</v>
+      </c>
+      <c r="H651" t="n">
+        <v>2</v>
+      </c>
+      <c r="I651" t="n">
+        <v>0</v>
+      </c>
+      <c r="J651" t="n">
+        <v>1</v>
+      </c>
+      <c r="K651" t="n">
+        <v>0</v>
+      </c>
+      <c r="L651" t="n">
+        <v>200</v>
+      </c>
+      <c r="M651" t="n">
+        <v>0</v>
+      </c>
+      <c r="N651" t="n">
+        <v>0</v>
+      </c>
+      <c r="O651" t="n">
+        <v>0</v>
+      </c>
+      <c r="P651" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q651" t="n">
+        <v>0</v>
+      </c>
+      <c r="R651" t="n">
+        <v>1</v>
+      </c>
+      <c r="S651" t="n">
+        <v>0</v>
+      </c>
+      <c r="T651" t="n">
+        <v>0</v>
+      </c>
+      <c r="U651" t="n">
+        <v>0</v>
+      </c>
+      <c r="V651" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W651" t="n">
+        <v>30</v>
+      </c>
+      <c r="X651" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2486524</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>C. DE SOUZA PACHECO | G. JOU COLL | J. CREMO | P. JORGENSEN | S. MICOVIC</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>5</v>
+      </c>
+      <c r="E652" t="n">
+        <v>32</v>
+      </c>
+      <c r="F652" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G652" t="n">
+        <v>2</v>
+      </c>
+      <c r="H652" t="n">
+        <v>0</v>
+      </c>
+      <c r="I652" t="n">
+        <v>1</v>
+      </c>
+      <c r="J652" t="n">
+        <v>1</v>
+      </c>
+      <c r="K652" t="n">
+        <v>200</v>
+      </c>
+      <c r="L652" t="n">
+        <v>0</v>
+      </c>
+      <c r="M652" t="n">
+        <v>200</v>
+      </c>
+      <c r="N652" t="n">
+        <v>1</v>
+      </c>
+      <c r="O652" t="n">
+        <v>0</v>
+      </c>
+      <c r="P652" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q652" t="n">
+        <v>0</v>
+      </c>
+      <c r="R652" t="n">
+        <v>1</v>
+      </c>
+      <c r="S652" t="n">
+        <v>0</v>
+      </c>
+      <c r="T652" t="n">
+        <v>0</v>
+      </c>
+      <c r="U652" t="n">
+        <v>0</v>
+      </c>
+      <c r="V652" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W652" t="n">
+        <v>30</v>
+      </c>
+      <c r="X652" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2486524</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>C. DE SOUZA PACHECO | I. DIOP GAYE | J. CREMO | P. JORGENSEN | S. MICOVIC</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>5</v>
+      </c>
+      <c r="E653" t="n">
+        <v>4</v>
+      </c>
+      <c r="F653" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G653" t="n">
+        <v>0</v>
+      </c>
+      <c r="H653" t="n">
+        <v>0</v>
+      </c>
+      <c r="I653" t="n">
+        <v>0</v>
+      </c>
+      <c r="J653" t="n">
+        <v>1</v>
+      </c>
+      <c r="K653" t="n">
+        <v>0</v>
+      </c>
+      <c r="L653" t="n">
+        <v>0</v>
+      </c>
+      <c r="M653" t="n">
+        <v>0</v>
+      </c>
+      <c r="N653" t="n">
+        <v>0</v>
+      </c>
+      <c r="O653" t="n">
+        <v>0</v>
+      </c>
+      <c r="P653" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q653" t="n">
+        <v>0</v>
+      </c>
+      <c r="R653" t="n">
+        <v>0</v>
+      </c>
+      <c r="S653" t="n">
+        <v>0</v>
+      </c>
+      <c r="T653" t="n">
+        <v>1</v>
+      </c>
+      <c r="U653" t="n">
+        <v>0</v>
+      </c>
+      <c r="V653" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W653" t="n">
+        <v>30</v>
+      </c>
+      <c r="X653" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2486524</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>C. DE SOUZA PACHECO | J. CREMO | P. JORGENSEN | S. BARRO | S. MICOVIC</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>5</v>
+      </c>
+      <c r="E654" t="n">
+        <v>15</v>
+      </c>
+      <c r="F654" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G654" t="n">
+        <v>0</v>
+      </c>
+      <c r="H654" t="n">
+        <v>3</v>
+      </c>
+      <c r="I654" t="n">
+        <v>0</v>
+      </c>
+      <c r="J654" t="n">
+        <v>1</v>
+      </c>
+      <c r="K654" t="n">
+        <v>0</v>
+      </c>
+      <c r="L654" t="n">
+        <v>300</v>
+      </c>
+      <c r="M654" t="n">
+        <v>0</v>
+      </c>
+      <c r="N654" t="n">
+        <v>0</v>
+      </c>
+      <c r="O654" t="n">
+        <v>0</v>
+      </c>
+      <c r="P654" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q654" t="n">
+        <v>0</v>
+      </c>
+      <c r="R654" t="n">
+        <v>1</v>
+      </c>
+      <c r="S654" t="n">
+        <v>0</v>
+      </c>
+      <c r="T654" t="n">
+        <v>0</v>
+      </c>
+      <c r="U654" t="n">
+        <v>0</v>
+      </c>
+      <c r="V654" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W654" t="n">
+        <v>30</v>
+      </c>
+      <c r="X654" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>A. SOLA IDDRISU | E. VICEDO AYALA | E. WEMBI | F. ZURBRIGGEN | S. LITTLESON</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>5</v>
+      </c>
+      <c r="E655" t="n">
+        <v>7</v>
+      </c>
+      <c r="F655" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G655" t="n">
+        <v>0</v>
+      </c>
+      <c r="H655" t="n">
+        <v>0</v>
+      </c>
+      <c r="I655" t="n">
+        <v>0</v>
+      </c>
+      <c r="J655" t="n">
+        <v>0</v>
+      </c>
+      <c r="K655" t="n">
+        <v>0</v>
+      </c>
+      <c r="L655" t="n">
+        <v>0</v>
+      </c>
+      <c r="M655" t="n">
+        <v>0</v>
+      </c>
+      <c r="N655" t="n">
+        <v>0</v>
+      </c>
+      <c r="O655" t="n">
+        <v>0</v>
+      </c>
+      <c r="P655" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q655" t="n">
+        <v>0</v>
+      </c>
+      <c r="R655" t="n">
+        <v>0</v>
+      </c>
+      <c r="S655" t="n">
+        <v>0</v>
+      </c>
+      <c r="T655" t="n">
+        <v>0</v>
+      </c>
+      <c r="U655" t="n">
+        <v>0</v>
+      </c>
+      <c r="V655" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W655" t="n">
+        <v>30</v>
+      </c>
+      <c r="X655" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>A. SOLA IDDRISU | E. VICEDO AYALA | F. ZURBRIGGEN | S. LITTLESON | V. ARTEAGA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>5</v>
+      </c>
+      <c r="E656" t="n">
+        <v>99</v>
+      </c>
+      <c r="F656" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G656" t="n">
+        <v>1</v>
+      </c>
+      <c r="H656" t="n">
+        <v>2</v>
+      </c>
+      <c r="I656" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="J656" t="n">
+        <v>4</v>
+      </c>
+      <c r="K656" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="L656" t="n">
+        <v>50</v>
+      </c>
+      <c r="M656" t="n">
+        <v>-29.51</v>
+      </c>
+      <c r="N656" t="n">
+        <v>3</v>
+      </c>
+      <c r="O656" t="n">
+        <v>2</v>
+      </c>
+      <c r="P656" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q656" t="n">
+        <v>0</v>
+      </c>
+      <c r="R656" t="n">
+        <v>4</v>
+      </c>
+      <c r="S656" t="n">
+        <v>0</v>
+      </c>
+      <c r="T656" t="n">
+        <v>1</v>
+      </c>
+      <c r="U656" t="n">
+        <v>1</v>
+      </c>
+      <c r="V656" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W656" t="n">
+        <v>30</v>
+      </c>
+      <c r="X656" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>A. SOLA IDDRISU | E. VICEDO AYALA | J. CONE | S. LITTLESON | V. ARTEAGA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>5</v>
+      </c>
+      <c r="E657" t="n">
+        <v>107</v>
+      </c>
+      <c r="F657" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G657" t="n">
+        <v>4</v>
+      </c>
+      <c r="H657" t="n">
+        <v>5</v>
+      </c>
+      <c r="I657" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J657" t="n">
+        <v>3</v>
+      </c>
+      <c r="K657" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="L657" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="M657" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="N657" t="n">
+        <v>3</v>
+      </c>
+      <c r="O657" t="n">
+        <v>2</v>
+      </c>
+      <c r="P657" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q657" t="n">
+        <v>2</v>
+      </c>
+      <c r="R657" t="n">
+        <v>3</v>
+      </c>
+      <c r="S657" t="n">
+        <v>0</v>
+      </c>
+      <c r="T657" t="n">
+        <v>0</v>
+      </c>
+      <c r="U657" t="n">
+        <v>0</v>
+      </c>
+      <c r="V657" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W657" t="n">
+        <v>30</v>
+      </c>
+      <c r="X657" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>A. SOLA IDDRISU | F. ZURBRIGGEN | N. GALETTE | S. LITTLESON | V. ARTEAGA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>5</v>
+      </c>
+      <c r="E658" t="n">
+        <v>48</v>
+      </c>
+      <c r="F658" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G658" t="n">
+        <v>2</v>
+      </c>
+      <c r="H658" t="n">
+        <v>0</v>
+      </c>
+      <c r="I658" t="n">
+        <v>2</v>
+      </c>
+      <c r="J658" t="n">
+        <v>2</v>
+      </c>
+      <c r="K658" t="n">
+        <v>100</v>
+      </c>
+      <c r="L658" t="n">
+        <v>0</v>
+      </c>
+      <c r="M658" t="n">
+        <v>100</v>
+      </c>
+      <c r="N658" t="n">
+        <v>2</v>
+      </c>
+      <c r="O658" t="n">
+        <v>0</v>
+      </c>
+      <c r="P658" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q658" t="n">
+        <v>0</v>
+      </c>
+      <c r="R658" t="n">
+        <v>2</v>
+      </c>
+      <c r="S658" t="n">
+        <v>0</v>
+      </c>
+      <c r="T658" t="n">
+        <v>0</v>
+      </c>
+      <c r="U658" t="n">
+        <v>0</v>
+      </c>
+      <c r="V658" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W658" t="n">
+        <v>30</v>
+      </c>
+      <c r="X658" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>A. SOLA IDDRISU | J. CONE | N. GALETTE | S. LITTLESON | V. ARTEAGA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>5</v>
+      </c>
+      <c r="E659" t="n">
+        <v>10</v>
+      </c>
+      <c r="F659" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G659" t="n">
+        <v>0</v>
+      </c>
+      <c r="H659" t="n">
+        <v>0</v>
+      </c>
+      <c r="I659" t="n">
+        <v>0</v>
+      </c>
+      <c r="J659" t="n">
+        <v>0</v>
+      </c>
+      <c r="K659" t="n">
+        <v>0</v>
+      </c>
+      <c r="L659" t="n">
+        <v>0</v>
+      </c>
+      <c r="M659" t="n">
+        <v>0</v>
+      </c>
+      <c r="N659" t="n">
+        <v>0</v>
+      </c>
+      <c r="O659" t="n">
+        <v>0</v>
+      </c>
+      <c r="P659" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q659" t="n">
+        <v>0</v>
+      </c>
+      <c r="R659" t="n">
+        <v>0</v>
+      </c>
+      <c r="S659" t="n">
+        <v>0</v>
+      </c>
+      <c r="T659" t="n">
+        <v>0</v>
+      </c>
+      <c r="U659" t="n">
+        <v>0</v>
+      </c>
+      <c r="V659" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W659" t="n">
+        <v>30</v>
+      </c>
+      <c r="X659" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>E. VICEDO AYALA | E. WEMBI | F. ZURBRIGGEN | J. LOBO MARTORELL | S. LITTLESON</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>5</v>
+      </c>
+      <c r="E660" t="n">
+        <v>28</v>
+      </c>
+      <c r="F660" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G660" t="n">
+        <v>0</v>
+      </c>
+      <c r="H660" t="n">
+        <v>1</v>
+      </c>
+      <c r="I660" t="n">
+        <v>1</v>
+      </c>
+      <c r="J660" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K660" t="n">
+        <v>0</v>
+      </c>
+      <c r="L660" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="M660" t="n">
+        <v>-53.19</v>
+      </c>
+      <c r="N660" t="n">
+        <v>2</v>
+      </c>
+      <c r="O660" t="n">
+        <v>0</v>
+      </c>
+      <c r="P660" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q660" t="n">
+        <v>1</v>
+      </c>
+      <c r="R660" t="n">
+        <v>0</v>
+      </c>
+      <c r="S660" t="n">
+        <v>2</v>
+      </c>
+      <c r="T660" t="n">
+        <v>1</v>
+      </c>
+      <c r="U660" t="n">
+        <v>0</v>
+      </c>
+      <c r="V660" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W660" t="n">
+        <v>30</v>
+      </c>
+      <c r="X660" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>A. WINTERING | J. VRANKIC | M. ARMUS | M. KAMBA | T. BORG</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>5</v>
+      </c>
+      <c r="E661" t="n">
+        <v>10</v>
+      </c>
+      <c r="F661" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G661" t="n">
+        <v>0</v>
+      </c>
+      <c r="H661" t="n">
+        <v>0</v>
+      </c>
+      <c r="I661" t="n">
+        <v>0</v>
+      </c>
+      <c r="J661" t="n">
+        <v>0</v>
+      </c>
+      <c r="K661" t="n">
+        <v>0</v>
+      </c>
+      <c r="L661" t="n">
+        <v>0</v>
+      </c>
+      <c r="M661" t="n">
+        <v>0</v>
+      </c>
+      <c r="N661" t="n">
+        <v>0</v>
+      </c>
+      <c r="O661" t="n">
+        <v>0</v>
+      </c>
+      <c r="P661" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q661" t="n">
+        <v>0</v>
+      </c>
+      <c r="R661" t="n">
+        <v>0</v>
+      </c>
+      <c r="S661" t="n">
+        <v>0</v>
+      </c>
+      <c r="T661" t="n">
+        <v>0</v>
+      </c>
+      <c r="U661" t="n">
+        <v>0</v>
+      </c>
+      <c r="V661" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W661" t="n">
+        <v>30</v>
+      </c>
+      <c r="X661" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>A. WINTERING | J. VRANKIC | M. ARMUS | T. BORG | X. OROZ URIA</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>5</v>
+      </c>
+      <c r="E662" t="n">
+        <v>48</v>
+      </c>
+      <c r="F662" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G662" t="n">
+        <v>0</v>
+      </c>
+      <c r="H662" t="n">
+        <v>2</v>
+      </c>
+      <c r="I662" t="n">
+        <v>2</v>
+      </c>
+      <c r="J662" t="n">
+        <v>2</v>
+      </c>
+      <c r="K662" t="n">
+        <v>0</v>
+      </c>
+      <c r="L662" t="n">
+        <v>100</v>
+      </c>
+      <c r="M662" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N662" t="n">
+        <v>2</v>
+      </c>
+      <c r="O662" t="n">
+        <v>0</v>
+      </c>
+      <c r="P662" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q662" t="n">
+        <v>0</v>
+      </c>
+      <c r="R662" t="n">
+        <v>2</v>
+      </c>
+      <c r="S662" t="n">
+        <v>0</v>
+      </c>
+      <c r="T662" t="n">
+        <v>0</v>
+      </c>
+      <c r="U662" t="n">
+        <v>0</v>
+      </c>
+      <c r="V662" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W662" t="n">
+        <v>30</v>
+      </c>
+      <c r="X662" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>A. WINTERING | J. VRANKIC | M. KAMBA | T. BORG | V. VUCETIC</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>5</v>
+      </c>
+      <c r="E663" t="n">
+        <v>241</v>
+      </c>
+      <c r="F663" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="G663" t="n">
+        <v>8</v>
+      </c>
+      <c r="H663" t="n">
+        <v>5</v>
+      </c>
+      <c r="I663" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="J663" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="K663" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="L663" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="M663" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="N663" t="n">
+        <v>7</v>
+      </c>
+      <c r="O663" t="n">
+        <v>2</v>
+      </c>
+      <c r="P663" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q663" t="n">
+        <v>1</v>
+      </c>
+      <c r="R663" t="n">
+        <v>8</v>
+      </c>
+      <c r="S663" t="n">
+        <v>4</v>
+      </c>
+      <c r="T663" t="n">
+        <v>1</v>
+      </c>
+      <c r="U663" t="n">
+        <v>3</v>
+      </c>
+      <c r="V663" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W663" t="n">
+        <v>30</v>
+      </c>
+      <c r="X663" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2486523</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>A. FAURE RIBES | D. DUSCAK | G. PARHAM II | M. TOWNES VILLAR | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>5</v>
+      </c>
+      <c r="E664" t="n">
+        <v>70</v>
+      </c>
+      <c r="F664" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G664" t="n">
+        <v>2</v>
+      </c>
+      <c r="H664" t="n">
+        <v>4</v>
+      </c>
+      <c r="I664" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J664" t="n">
+        <v>2</v>
+      </c>
+      <c r="K664" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="L664" t="n">
+        <v>200</v>
+      </c>
+      <c r="M664" t="n">
+        <v>-130.56</v>
+      </c>
+      <c r="N664" t="n">
+        <v>1</v>
+      </c>
+      <c r="O664" t="n">
+        <v>2</v>
+      </c>
+      <c r="P664" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q664" t="n">
+        <v>0</v>
+      </c>
+      <c r="R664" t="n">
+        <v>2</v>
+      </c>
+      <c r="S664" t="n">
+        <v>0</v>
+      </c>
+      <c r="T664" t="n">
+        <v>1</v>
+      </c>
+      <c r="U664" t="n">
+        <v>1</v>
+      </c>
+      <c r="V664" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W664" t="n">
+        <v>30</v>
+      </c>
+      <c r="X664" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2486523</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>D. DUSCAK | D. SHELIST | F. NWAOKORIE | G. PARHAM II | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>5</v>
+      </c>
+      <c r="E665" t="n">
+        <v>111</v>
+      </c>
+      <c r="F665" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G665" t="n">
+        <v>1</v>
+      </c>
+      <c r="H665" t="n">
+        <v>0</v>
+      </c>
+      <c r="I665" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J665" t="n">
+        <v>3</v>
+      </c>
+      <c r="K665" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="L665" t="n">
+        <v>0</v>
+      </c>
+      <c r="M665" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="N665" t="n">
+        <v>2</v>
+      </c>
+      <c r="O665" t="n">
+        <v>1</v>
+      </c>
+      <c r="P665" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q665" t="n">
+        <v>1</v>
+      </c>
+      <c r="R665" t="n">
+        <v>2</v>
+      </c>
+      <c r="S665" t="n">
+        <v>0</v>
+      </c>
+      <c r="T665" t="n">
+        <v>2</v>
+      </c>
+      <c r="U665" t="n">
+        <v>1</v>
+      </c>
+      <c r="V665" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W665" t="n">
+        <v>30</v>
+      </c>
+      <c r="X665" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2486523</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>D. DUSCAK | D. SHELIST | G. PARHAM II | M. TOWNES VILLAR | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>5</v>
+      </c>
+      <c r="E666" t="n">
+        <v>51</v>
+      </c>
+      <c r="F666" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G666" t="n">
+        <v>0</v>
+      </c>
+      <c r="H666" t="n">
+        <v>0</v>
+      </c>
+      <c r="I666" t="n">
+        <v>2</v>
+      </c>
+      <c r="J666" t="n">
+        <v>1</v>
+      </c>
+      <c r="K666" t="n">
+        <v>0</v>
+      </c>
+      <c r="L666" t="n">
+        <v>0</v>
+      </c>
+      <c r="M666" t="n">
+        <v>0</v>
+      </c>
+      <c r="N666" t="n">
+        <v>2</v>
+      </c>
+      <c r="O666" t="n">
+        <v>0</v>
+      </c>
+      <c r="P666" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q666" t="n">
+        <v>0</v>
+      </c>
+      <c r="R666" t="n">
+        <v>1</v>
+      </c>
+      <c r="S666" t="n">
+        <v>0</v>
+      </c>
+      <c r="T666" t="n">
+        <v>0</v>
+      </c>
+      <c r="U666" t="n">
+        <v>0</v>
+      </c>
+      <c r="V666" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W666" t="n">
+        <v>30</v>
+      </c>
+      <c r="X666" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2486523</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>D. SHELIST | F. NWAOKORIE | G. PARHAM II | M. TOWNES VILLAR | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>5</v>
+      </c>
+      <c r="E667" t="n">
+        <v>31</v>
+      </c>
+      <c r="F667" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G667" t="n">
+        <v>0</v>
+      </c>
+      <c r="H667" t="n">
+        <v>2</v>
+      </c>
+      <c r="I667" t="n">
+        <v>1</v>
+      </c>
+      <c r="J667" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K667" t="n">
+        <v>0</v>
+      </c>
+      <c r="L667" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="M667" t="n">
+        <v>-106.38</v>
+      </c>
+      <c r="N667" t="n">
+        <v>0</v>
+      </c>
+      <c r="O667" t="n">
+        <v>0</v>
+      </c>
+      <c r="P667" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q667" t="n">
+        <v>0</v>
+      </c>
+      <c r="R667" t="n">
+        <v>1</v>
+      </c>
+      <c r="S667" t="n">
+        <v>2</v>
+      </c>
+      <c r="T667" t="n">
+        <v>0</v>
+      </c>
+      <c r="U667" t="n">
+        <v>0</v>
+      </c>
+      <c r="V667" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W667" t="n">
+        <v>30</v>
+      </c>
+      <c r="X667" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2486523</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>H. LOPEZ BARRANTES | J. GRANGER | L. GIOVANNETTI | P. GARINO GULLOTTA | T. MC GREW</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>5</v>
+      </c>
+      <c r="E668" t="n">
+        <v>111</v>
+      </c>
+      <c r="F668" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G668" t="n">
+        <v>0</v>
+      </c>
+      <c r="H668" t="n">
+        <v>1</v>
+      </c>
+      <c r="I668" t="n">
+        <v>3</v>
+      </c>
+      <c r="J668" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K668" t="n">
+        <v>0</v>
+      </c>
+      <c r="L668" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="M668" t="n">
+        <v>-40.98</v>
+      </c>
+      <c r="N668" t="n">
+        <v>2</v>
+      </c>
+      <c r="O668" t="n">
+        <v>0</v>
+      </c>
+      <c r="P668" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q668" t="n">
+        <v>1</v>
+      </c>
+      <c r="R668" t="n">
+        <v>2</v>
+      </c>
+      <c r="S668" t="n">
+        <v>1</v>
+      </c>
+      <c r="T668" t="n">
+        <v>1</v>
+      </c>
+      <c r="U668" t="n">
+        <v>1</v>
+      </c>
+      <c r="V668" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W668" t="n">
+        <v>30</v>
+      </c>
+      <c r="X668" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2486523</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>H. LOPEZ BARRANTES | J. GRANGER | P. GARINO GULLOTTA | S. SALIN | T. MC GREW</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>5</v>
+      </c>
+      <c r="E669" t="n">
+        <v>8</v>
+      </c>
+      <c r="F669" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G669" t="n">
+        <v>0</v>
+      </c>
+      <c r="H669" t="n">
+        <v>0</v>
+      </c>
+      <c r="I669" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J669" t="n">
+        <v>0</v>
+      </c>
+      <c r="K669" t="n">
+        <v>0</v>
+      </c>
+      <c r="L669" t="n">
+        <v>0</v>
+      </c>
+      <c r="M669" t="n">
+        <v>0</v>
+      </c>
+      <c r="N669" t="n">
+        <v>0</v>
+      </c>
+      <c r="O669" t="n">
+        <v>2</v>
+      </c>
+      <c r="P669" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q669" t="n">
+        <v>0</v>
+      </c>
+      <c r="R669" t="n">
+        <v>0</v>
+      </c>
+      <c r="S669" t="n">
+        <v>0</v>
+      </c>
+      <c r="T669" t="n">
+        <v>0</v>
+      </c>
+      <c r="U669" t="n">
+        <v>0</v>
+      </c>
+      <c r="V669" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W669" t="n">
+        <v>30</v>
+      </c>
+      <c r="X669" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2486523</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>J. GRANGER | L. GIOVANNETTI | L. NWOGBO | P. GARINO GULLOTTA | T. MC GREW</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>5</v>
+      </c>
+      <c r="E670" t="n">
+        <v>8</v>
+      </c>
+      <c r="F670" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G670" t="n">
+        <v>0</v>
+      </c>
+      <c r="H670" t="n">
+        <v>0</v>
+      </c>
+      <c r="I670" t="n">
+        <v>1</v>
+      </c>
+      <c r="J670" t="n">
+        <v>0</v>
+      </c>
+      <c r="K670" t="n">
+        <v>0</v>
+      </c>
+      <c r="L670" t="n">
+        <v>0</v>
+      </c>
+      <c r="M670" t="n">
+        <v>0</v>
+      </c>
+      <c r="N670" t="n">
+        <v>0</v>
+      </c>
+      <c r="O670" t="n">
+        <v>0</v>
+      </c>
+      <c r="P670" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q670" t="n">
+        <v>0</v>
+      </c>
+      <c r="R670" t="n">
+        <v>0</v>
+      </c>
+      <c r="S670" t="n">
+        <v>0</v>
+      </c>
+      <c r="T670" t="n">
+        <v>0</v>
+      </c>
+      <c r="U670" t="n">
+        <v>0</v>
+      </c>
+      <c r="V670" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W670" t="n">
+        <v>30</v>
+      </c>
+      <c r="X670" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2486523</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>J. GRANGER | L. NWOGBO | P. GARINO GULLOTTA | S. SALIN | T. MC GREW</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>5</v>
+      </c>
+      <c r="E671" t="n">
+        <v>136</v>
+      </c>
+      <c r="F671" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G671" t="n">
+        <v>6</v>
+      </c>
+      <c r="H671" t="n">
+        <v>2</v>
+      </c>
+      <c r="I671" t="n">
+        <v>3</v>
+      </c>
+      <c r="J671" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="K671" t="n">
+        <v>200</v>
+      </c>
+      <c r="L671" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="M671" t="n">
+        <v>165.99</v>
+      </c>
+      <c r="N671" t="n">
+        <v>4</v>
+      </c>
+      <c r="O671" t="n">
+        <v>0</v>
+      </c>
+      <c r="P671" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q671" t="n">
+        <v>1</v>
+      </c>
+      <c r="R671" t="n">
+        <v>3</v>
+      </c>
+      <c r="S671" t="n">
+        <v>2</v>
+      </c>
+      <c r="T671" t="n">
+        <v>2</v>
+      </c>
+      <c r="U671" t="n">
+        <v>0</v>
+      </c>
+      <c r="V671" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W671" t="n">
+        <v>30</v>
+      </c>
+      <c r="X671" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO vs MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2486519</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>A. SCARIOLO ARES | J. BOCCA | L. BRACEY | O. MATULIONIS | S. NIANG BEYE</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>5</v>
+      </c>
+      <c r="E672" t="n">
+        <v>46</v>
+      </c>
+      <c r="F672" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G672" t="n">
+        <v>0</v>
+      </c>
+      <c r="H672" t="n">
+        <v>0</v>
+      </c>
+      <c r="I672" t="n">
+        <v>0</v>
+      </c>
+      <c r="J672" t="n">
+        <v>1</v>
+      </c>
+      <c r="K672" t="n">
+        <v>0</v>
+      </c>
+      <c r="L672" t="n">
+        <v>0</v>
+      </c>
+      <c r="M672" t="n">
+        <v>0</v>
+      </c>
+      <c r="N672" t="n">
+        <v>1</v>
+      </c>
+      <c r="O672" t="n">
+        <v>0</v>
+      </c>
+      <c r="P672" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q672" t="n">
+        <v>1</v>
+      </c>
+      <c r="R672" t="n">
+        <v>1</v>
+      </c>
+      <c r="S672" t="n">
+        <v>0</v>
+      </c>
+      <c r="T672" t="n">
+        <v>0</v>
+      </c>
+      <c r="U672" t="n">
+        <v>0</v>
+      </c>
+      <c r="V672" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W672" t="n">
+        <v>30</v>
+      </c>
+      <c r="X672" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2486519</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>A. SCARIOLO ARES | J. BOCCA | L. CAPALBO | O. MATULIONIS | S. NIANG BEYE</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>5</v>
+      </c>
+      <c r="E673" t="n">
+        <v>6</v>
+      </c>
+      <c r="F673" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G673" t="n">
+        <v>0</v>
+      </c>
+      <c r="H673" t="n">
+        <v>2</v>
+      </c>
+      <c r="I673" t="n">
+        <v>1</v>
+      </c>
+      <c r="J673" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K673" t="n">
+        <v>0</v>
+      </c>
+      <c r="L673" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M673" t="n">
+        <v>-227.27</v>
+      </c>
+      <c r="N673" t="n">
+        <v>0</v>
+      </c>
+      <c r="O673" t="n">
+        <v>0</v>
+      </c>
+      <c r="P673" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q673" t="n">
+        <v>0</v>
+      </c>
+      <c r="R673" t="n">
+        <v>0</v>
+      </c>
+      <c r="S673" t="n">
+        <v>2</v>
+      </c>
+      <c r="T673" t="n">
+        <v>0</v>
+      </c>
+      <c r="U673" t="n">
+        <v>0</v>
+      </c>
+      <c r="V673" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W673" t="n">
+        <v>30</v>
+      </c>
+      <c r="X673" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2486519</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>J. BOCCA | L. BRACEY | L. CAPALBO | L. SMITH | O. MATULIONIS</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>5</v>
+      </c>
+      <c r="E674" t="n">
+        <v>66</v>
+      </c>
+      <c r="F674" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G674" t="n">
+        <v>0</v>
+      </c>
+      <c r="H674" t="n">
+        <v>3</v>
+      </c>
+      <c r="I674" t="n">
+        <v>1</v>
+      </c>
+      <c r="J674" t="n">
+        <v>0</v>
+      </c>
+      <c r="K674" t="n">
+        <v>0</v>
+      </c>
+      <c r="L674" t="n">
+        <v>0</v>
+      </c>
+      <c r="M674" t="n">
+        <v>0</v>
+      </c>
+      <c r="N674" t="n">
+        <v>2</v>
+      </c>
+      <c r="O674" t="n">
+        <v>0</v>
+      </c>
+      <c r="P674" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q674" t="n">
+        <v>1</v>
+      </c>
+      <c r="R674" t="n">
+        <v>2</v>
+      </c>
+      <c r="S674" t="n">
+        <v>0</v>
+      </c>
+      <c r="T674" t="n">
+        <v>0</v>
+      </c>
+      <c r="U674" t="n">
+        <v>2</v>
+      </c>
+      <c r="V674" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W674" t="n">
+        <v>30</v>
+      </c>
+      <c r="X674" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2486519</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>L. BRACEY | L. CAPALBO | L. SMITH | O. MATULIONIS | S. NIANG BEYE</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>5</v>
+      </c>
+      <c r="E675" t="n">
+        <v>161</v>
+      </c>
+      <c r="F675" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G675" t="n">
+        <v>4</v>
+      </c>
+      <c r="H675" t="n">
+        <v>5</v>
+      </c>
+      <c r="I675" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J675" t="n">
+        <v>5</v>
+      </c>
+      <c r="K675" t="n">
+        <v>103.09</v>
+      </c>
+      <c r="L675" t="n">
+        <v>100</v>
+      </c>
+      <c r="M675" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N675" t="n">
+        <v>1</v>
+      </c>
+      <c r="O675" t="n">
+        <v>2</v>
+      </c>
+      <c r="P675" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q675" t="n">
+        <v>1</v>
+      </c>
+      <c r="R675" t="n">
+        <v>4</v>
+      </c>
+      <c r="S675" t="n">
+        <v>0</v>
+      </c>
+      <c r="T675" t="n">
+        <v>1</v>
+      </c>
+      <c r="U675" t="n">
+        <v>0</v>
+      </c>
+      <c r="V675" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W675" t="n">
+        <v>30</v>
+      </c>
+      <c r="X675" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2486519</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>A. GARUBA ALARI | A. MARTIN MARIN | C. POLYNICE | I. RIVERA CARROLL | J. LOPEZ SANTANA</t>
+        </is>
+      </c>
+      <c r="D676" t="n">
+        <v>5</v>
+      </c>
+      <c r="E676" t="n">
+        <v>34</v>
+      </c>
+      <c r="F676" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G676" t="n">
+        <v>0</v>
+      </c>
+      <c r="H676" t="n">
+        <v>0</v>
+      </c>
+      <c r="I676" t="n">
+        <v>1</v>
+      </c>
+      <c r="J676" t="n">
+        <v>0</v>
+      </c>
+      <c r="K676" t="n">
+        <v>0</v>
+      </c>
+      <c r="L676" t="n">
+        <v>0</v>
+      </c>
+      <c r="M676" t="n">
+        <v>0</v>
+      </c>
+      <c r="N676" t="n">
+        <v>1</v>
+      </c>
+      <c r="O676" t="n">
+        <v>0</v>
+      </c>
+      <c r="P676" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q676" t="n">
+        <v>0</v>
+      </c>
+      <c r="R676" t="n">
+        <v>1</v>
+      </c>
+      <c r="S676" t="n">
+        <v>0</v>
+      </c>
+      <c r="T676" t="n">
+        <v>0</v>
+      </c>
+      <c r="U676" t="n">
+        <v>1</v>
+      </c>
+      <c r="V676" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W676" t="n">
+        <v>30</v>
+      </c>
+      <c r="X676" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2486519</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>A. GARUBA ALARI | A. MARTIN MARIN | I. RIVERA CARROLL | K. WEBSTER | S. SVEJCAR</t>
+        </is>
+      </c>
+      <c r="D677" t="n">
+        <v>5</v>
+      </c>
+      <c r="E677" t="n">
+        <v>6</v>
+      </c>
+      <c r="F677" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G677" t="n">
+        <v>0</v>
+      </c>
+      <c r="H677" t="n">
+        <v>0</v>
+      </c>
+      <c r="I677" t="n">
+        <v>1</v>
+      </c>
+      <c r="J677" t="n">
+        <v>1</v>
+      </c>
+      <c r="K677" t="n">
+        <v>0</v>
+      </c>
+      <c r="L677" t="n">
+        <v>0</v>
+      </c>
+      <c r="M677" t="n">
+        <v>0</v>
+      </c>
+      <c r="N677" t="n">
+        <v>0</v>
+      </c>
+      <c r="O677" t="n">
+        <v>0</v>
+      </c>
+      <c r="P677" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q677" t="n">
+        <v>0</v>
+      </c>
+      <c r="R677" t="n">
+        <v>0</v>
+      </c>
+      <c r="S677" t="n">
+        <v>0</v>
+      </c>
+      <c r="T677" t="n">
+        <v>1</v>
+      </c>
+      <c r="U677" t="n">
+        <v>0</v>
+      </c>
+      <c r="V677" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W677" t="n">
+        <v>30</v>
+      </c>
+      <c r="X677" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2486519</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>A. GARUBA ALARI | A. MARTIN MARIN | K. WEBSTER | S. SVEJCAR | V. FAVERANI TATSCH</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>5</v>
+      </c>
+      <c r="E678" t="n">
+        <v>239</v>
+      </c>
+      <c r="F678" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="G678" t="n">
+        <v>10</v>
+      </c>
+      <c r="H678" t="n">
+        <v>4</v>
+      </c>
+      <c r="I678" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="J678" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="K678" t="n">
+        <v>204.92</v>
+      </c>
+      <c r="L678" t="n">
+        <v>81.97</v>
+      </c>
+      <c r="M678" t="n">
+        <v>122.95</v>
+      </c>
+      <c r="N678" t="n">
+        <v>6</v>
+      </c>
+      <c r="O678" t="n">
+        <v>2</v>
+      </c>
+      <c r="P678" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q678" t="n">
+        <v>2</v>
+      </c>
+      <c r="R678" t="n">
+        <v>3</v>
+      </c>
+      <c r="S678" t="n">
+        <v>2</v>
+      </c>
+      <c r="T678" t="n">
+        <v>3</v>
+      </c>
+      <c r="U678" t="n">
+        <v>2</v>
+      </c>
+      <c r="V678" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W678" t="n">
+        <v>30</v>
+      </c>
+      <c r="X678" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>A. MARTINEZ CLARIANA | B. PREPELIC | J. PERIS CRESPO | J. VAN ZEGEREN | T. NASPLER PERAIRE</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>5</v>
+      </c>
+      <c r="E679" t="n">
+        <v>11</v>
+      </c>
+      <c r="F679" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G679" t="n">
+        <v>0</v>
+      </c>
+      <c r="H679" t="n">
+        <v>2</v>
+      </c>
+      <c r="I679" t="n">
+        <v>0</v>
+      </c>
+      <c r="J679" t="n">
+        <v>1</v>
+      </c>
+      <c r="K679" t="n">
+        <v>0</v>
+      </c>
+      <c r="L679" t="n">
+        <v>200</v>
+      </c>
+      <c r="M679" t="n">
+        <v>0</v>
+      </c>
+      <c r="N679" t="n">
+        <v>0</v>
+      </c>
+      <c r="O679" t="n">
+        <v>0</v>
+      </c>
+      <c r="P679" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q679" t="n">
+        <v>0</v>
+      </c>
+      <c r="R679" t="n">
+        <v>1</v>
+      </c>
+      <c r="S679" t="n">
+        <v>0</v>
+      </c>
+      <c r="T679" t="n">
+        <v>0</v>
+      </c>
+      <c r="U679" t="n">
+        <v>0</v>
+      </c>
+      <c r="V679" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W679" t="n">
+        <v>30</v>
+      </c>
+      <c r="X679" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>B. PREPELIC | J. ROUND | O. LO | T. NASPLER PERAIRE | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>5</v>
+      </c>
+      <c r="E680" t="n">
+        <v>91</v>
+      </c>
+      <c r="F680" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G680" t="n">
+        <v>4</v>
+      </c>
+      <c r="H680" t="n">
+        <v>0</v>
+      </c>
+      <c r="I680" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J680" t="n">
+        <v>2</v>
+      </c>
+      <c r="K680" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="L680" t="n">
+        <v>0</v>
+      </c>
+      <c r="M680" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="N680" t="n">
+        <v>2</v>
+      </c>
+      <c r="O680" t="n">
+        <v>2</v>
+      </c>
+      <c r="P680" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q680" t="n">
+        <v>2</v>
+      </c>
+      <c r="R680" t="n">
+        <v>2</v>
+      </c>
+      <c r="S680" t="n">
+        <v>0</v>
+      </c>
+      <c r="T680" t="n">
+        <v>0</v>
+      </c>
+      <c r="U680" t="n">
+        <v>0</v>
+      </c>
+      <c r="V680" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W680" t="n">
+        <v>30</v>
+      </c>
+      <c r="X680" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>C. ROGERS | J. PERIS CRESPO | J. ROUND | O. LO | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>5</v>
+      </c>
+      <c r="E681" t="n">
+        <v>17</v>
+      </c>
+      <c r="F681" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G681" t="n">
+        <v>0</v>
+      </c>
+      <c r="H681" t="n">
+        <v>3</v>
+      </c>
+      <c r="I681" t="n">
+        <v>2</v>
+      </c>
+      <c r="J681" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K681" t="n">
+        <v>0</v>
+      </c>
+      <c r="L681" t="n">
+        <v>394.74</v>
+      </c>
+      <c r="M681" t="n">
+        <v>-394.74</v>
+      </c>
+      <c r="N681" t="n">
+        <v>1</v>
+      </c>
+      <c r="O681" t="n">
+        <v>0</v>
+      </c>
+      <c r="P681" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q681" t="n">
+        <v>0</v>
+      </c>
+      <c r="R681" t="n">
+        <v>0</v>
+      </c>
+      <c r="S681" t="n">
+        <v>4</v>
+      </c>
+      <c r="T681" t="n">
+        <v>0</v>
+      </c>
+      <c r="U681" t="n">
+        <v>1</v>
+      </c>
+      <c r="V681" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W681" t="n">
+        <v>30</v>
+      </c>
+      <c r="X681" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>C. ROGERS | J. PERIS CRESPO | J. VAN ZEGEREN | S. THRASTARSON | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>5</v>
+      </c>
+      <c r="E682" t="n">
+        <v>17</v>
+      </c>
+      <c r="F682" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G682" t="n">
+        <v>3</v>
+      </c>
+      <c r="H682" t="n">
+        <v>1</v>
+      </c>
+      <c r="I682" t="n">
+        <v>1</v>
+      </c>
+      <c r="J682" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K682" t="n">
+        <v>300</v>
+      </c>
+      <c r="L682" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M682" t="n">
+        <v>186.36</v>
+      </c>
+      <c r="N682" t="n">
+        <v>2</v>
+      </c>
+      <c r="O682" t="n">
+        <v>0</v>
+      </c>
+      <c r="P682" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q682" t="n">
+        <v>1</v>
+      </c>
+      <c r="R682" t="n">
+        <v>0</v>
+      </c>
+      <c r="S682" t="n">
+        <v>2</v>
+      </c>
+      <c r="T682" t="n">
+        <v>0</v>
+      </c>
+      <c r="U682" t="n">
+        <v>0</v>
+      </c>
+      <c r="V682" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W682" t="n">
+        <v>30</v>
+      </c>
+      <c r="X682" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>C. ROGERS | J. PERIS CRESPO | O. LO | S. THRASTARSON | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>5</v>
+      </c>
+      <c r="E683" t="n">
+        <v>53</v>
+      </c>
+      <c r="F683" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G683" t="n">
+        <v>2</v>
+      </c>
+      <c r="H683" t="n">
+        <v>1</v>
+      </c>
+      <c r="I683" t="n">
+        <v>2</v>
+      </c>
+      <c r="J683" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K683" t="n">
+        <v>100</v>
+      </c>
+      <c r="L683" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M683" t="n">
+        <v>-13.64</v>
+      </c>
+      <c r="N683" t="n">
+        <v>3</v>
+      </c>
+      <c r="O683" t="n">
+        <v>0</v>
+      </c>
+      <c r="P683" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q683" t="n">
+        <v>1</v>
+      </c>
+      <c r="R683" t="n">
+        <v>1</v>
+      </c>
+      <c r="S683" t="n">
+        <v>2</v>
+      </c>
+      <c r="T683" t="n">
+        <v>0</v>
+      </c>
+      <c r="U683" t="n">
+        <v>1</v>
+      </c>
+      <c r="V683" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W683" t="n">
+        <v>30</v>
+      </c>
+      <c r="X683" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>C. ROGERS | J. VAN ZEGEREN | S. THRASTARSON | T. NASPLER PERAIRE | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>5</v>
+      </c>
+      <c r="E684" t="n">
+        <v>58</v>
+      </c>
+      <c r="F684" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G684" t="n">
+        <v>0</v>
+      </c>
+      <c r="H684" t="n">
+        <v>6</v>
+      </c>
+      <c r="I684" t="n">
+        <v>1</v>
+      </c>
+      <c r="J684" t="n">
+        <v>2</v>
+      </c>
+      <c r="K684" t="n">
+        <v>0</v>
+      </c>
+      <c r="L684" t="n">
+        <v>300</v>
+      </c>
+      <c r="M684" t="n">
+        <v>-300</v>
+      </c>
+      <c r="N684" t="n">
+        <v>1</v>
+      </c>
+      <c r="O684" t="n">
+        <v>0</v>
+      </c>
+      <c r="P684" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q684" t="n">
+        <v>0</v>
+      </c>
+      <c r="R684" t="n">
+        <v>2</v>
+      </c>
+      <c r="S684" t="n">
+        <v>0</v>
+      </c>
+      <c r="T684" t="n">
+        <v>0</v>
+      </c>
+      <c r="U684" t="n">
+        <v>0</v>
+      </c>
+      <c r="V684" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W684" t="n">
+        <v>30</v>
+      </c>
+      <c r="X684" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>C. ROGERS | O. LO | S. THRASTARSON | T. NASPLER PERAIRE | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>5</v>
+      </c>
+      <c r="E685" t="n">
+        <v>34</v>
+      </c>
+      <c r="F685" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G685" t="n">
+        <v>0</v>
+      </c>
+      <c r="H685" t="n">
+        <v>2</v>
+      </c>
+      <c r="I685" t="n">
+        <v>0</v>
+      </c>
+      <c r="J685" t="n">
+        <v>1</v>
+      </c>
+      <c r="K685" t="n">
+        <v>0</v>
+      </c>
+      <c r="L685" t="n">
+        <v>200</v>
+      </c>
+      <c r="M685" t="n">
+        <v>0</v>
+      </c>
+      <c r="N685" t="n">
+        <v>0</v>
+      </c>
+      <c r="O685" t="n">
+        <v>0</v>
+      </c>
+      <c r="P685" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q685" t="n">
+        <v>0</v>
+      </c>
+      <c r="R685" t="n">
+        <v>1</v>
+      </c>
+      <c r="S685" t="n">
+        <v>0</v>
+      </c>
+      <c r="T685" t="n">
+        <v>0</v>
+      </c>
+      <c r="U685" t="n">
+        <v>0</v>
+      </c>
+      <c r="V685" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W685" t="n">
+        <v>30</v>
+      </c>
+      <c r="X685" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>C. DIAZ RODRIGUEZ | I. CRUZ UCEDA | J. GARCIA SANCHEZ | M. CAICEDO SANCHEZ | S. RODRIGUEZ FEBLES</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>5</v>
+      </c>
+      <c r="E686" t="n">
+        <v>34</v>
+      </c>
+      <c r="F686" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G686" t="n">
+        <v>2</v>
+      </c>
+      <c r="H686" t="n">
+        <v>0</v>
+      </c>
+      <c r="I686" t="n">
+        <v>1</v>
+      </c>
+      <c r="J686" t="n">
+        <v>0</v>
+      </c>
+      <c r="K686" t="n">
+        <v>200</v>
+      </c>
+      <c r="L686" t="n">
+        <v>0</v>
+      </c>
+      <c r="M686" t="n">
+        <v>0</v>
+      </c>
+      <c r="N686" t="n">
+        <v>1</v>
+      </c>
+      <c r="O686" t="n">
+        <v>0</v>
+      </c>
+      <c r="P686" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q686" t="n">
+        <v>0</v>
+      </c>
+      <c r="R686" t="n">
+        <v>0</v>
+      </c>
+      <c r="S686" t="n">
+        <v>0</v>
+      </c>
+      <c r="T686" t="n">
+        <v>0</v>
+      </c>
+      <c r="U686" t="n">
+        <v>0</v>
+      </c>
+      <c r="V686" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W686" t="n">
+        <v>30</v>
+      </c>
+      <c r="X686" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>C. DIAZ RODRIGUEZ | I. CRUZ UCEDA | M. CAICEDO SANCHEZ | S. CECCARDI | S. RODRIGUEZ FEBLES</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>5</v>
+      </c>
+      <c r="E687" t="n">
+        <v>33</v>
+      </c>
+      <c r="F687" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G687" t="n">
+        <v>0</v>
+      </c>
+      <c r="H687" t="n">
+        <v>2</v>
+      </c>
+      <c r="I687" t="n">
+        <v>0</v>
+      </c>
+      <c r="J687" t="n">
+        <v>1</v>
+      </c>
+      <c r="K687" t="n">
+        <v>0</v>
+      </c>
+      <c r="L687" t="n">
+        <v>200</v>
+      </c>
+      <c r="M687" t="n">
+        <v>0</v>
+      </c>
+      <c r="N687" t="n">
+        <v>1</v>
+      </c>
+      <c r="O687" t="n">
+        <v>0</v>
+      </c>
+      <c r="P687" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q687" t="n">
+        <v>1</v>
+      </c>
+      <c r="R687" t="n">
+        <v>2</v>
+      </c>
+      <c r="S687" t="n">
+        <v>0</v>
+      </c>
+      <c r="T687" t="n">
+        <v>0</v>
+      </c>
+      <c r="U687" t="n">
+        <v>1</v>
+      </c>
+      <c r="V687" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W687" t="n">
+        <v>30</v>
+      </c>
+      <c r="X687" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>C. DIAZ RODRIGUEZ | J. GARCIA SANCHEZ | J. GODSPOWER JOHNSON | M. CAICEDO SANCHEZ | N. MC MULLEN</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>5</v>
+      </c>
+      <c r="E688" t="n">
+        <v>20</v>
+      </c>
+      <c r="F688" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G688" t="n">
+        <v>1</v>
+      </c>
+      <c r="H688" t="n">
+        <v>0</v>
+      </c>
+      <c r="I688" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J688" t="n">
+        <v>1</v>
+      </c>
+      <c r="K688" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L688" t="n">
+        <v>0</v>
+      </c>
+      <c r="M688" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N688" t="n">
+        <v>0</v>
+      </c>
+      <c r="O688" t="n">
+        <v>2</v>
+      </c>
+      <c r="P688" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q688" t="n">
+        <v>0</v>
+      </c>
+      <c r="R688" t="n">
+        <v>1</v>
+      </c>
+      <c r="S688" t="n">
+        <v>0</v>
+      </c>
+      <c r="T688" t="n">
+        <v>0</v>
+      </c>
+      <c r="U688" t="n">
+        <v>0</v>
+      </c>
+      <c r="V688" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W688" t="n">
+        <v>30</v>
+      </c>
+      <c r="X688" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>C. DIAZ RODRIGUEZ | J. GARCIA SANCHEZ | J. GODSPOWER JOHNSON | S. CECCARDI | S. RODRIGUEZ FEBLES</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>5</v>
+      </c>
+      <c r="E689" t="n">
+        <v>58</v>
+      </c>
+      <c r="F689" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G689" t="n">
+        <v>6</v>
+      </c>
+      <c r="H689" t="n">
+        <v>0</v>
+      </c>
+      <c r="I689" t="n">
+        <v>2</v>
+      </c>
+      <c r="J689" t="n">
+        <v>1</v>
+      </c>
+      <c r="K689" t="n">
+        <v>300</v>
+      </c>
+      <c r="L689" t="n">
+        <v>0</v>
+      </c>
+      <c r="M689" t="n">
+        <v>300</v>
+      </c>
+      <c r="N689" t="n">
+        <v>2</v>
+      </c>
+      <c r="O689" t="n">
+        <v>0</v>
+      </c>
+      <c r="P689" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q689" t="n">
+        <v>0</v>
+      </c>
+      <c r="R689" t="n">
+        <v>1</v>
+      </c>
+      <c r="S689" t="n">
+        <v>0</v>
+      </c>
+      <c r="T689" t="n">
+        <v>0</v>
+      </c>
+      <c r="U689" t="n">
+        <v>0</v>
+      </c>
+      <c r="V689" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W689" t="n">
+        <v>30</v>
+      </c>
+      <c r="X689" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>C. DIAZ RODRIGUEZ | J. GODSPOWER JOHNSON | M. CAICEDO SANCHEZ | S. CECCARDI | S. RODRIGUEZ FEBLES</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>5</v>
+      </c>
+      <c r="E690" t="n">
+        <v>17</v>
+      </c>
+      <c r="F690" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G690" t="n">
+        <v>1</v>
+      </c>
+      <c r="H690" t="n">
+        <v>3</v>
+      </c>
+      <c r="I690" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J690" t="n">
+        <v>1</v>
+      </c>
+      <c r="K690" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L690" t="n">
+        <v>300</v>
+      </c>
+      <c r="M690" t="n">
+        <v>-186.36</v>
+      </c>
+      <c r="N690" t="n">
+        <v>0</v>
+      </c>
+      <c r="O690" t="n">
+        <v>2</v>
+      </c>
+      <c r="P690" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q690" t="n">
+        <v>0</v>
+      </c>
+      <c r="R690" t="n">
+        <v>2</v>
+      </c>
+      <c r="S690" t="n">
+        <v>0</v>
+      </c>
+      <c r="T690" t="n">
+        <v>0</v>
+      </c>
+      <c r="U690" t="n">
+        <v>1</v>
+      </c>
+      <c r="V690" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W690" t="n">
+        <v>30</v>
+      </c>
+      <c r="X690" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>C. DIAZ RODRIGUEZ | J. GODSPOWER JOHNSON | N. HOOVER | S. CECCARDI | S. RODRIGUEZ FEBLES</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>5</v>
+      </c>
+      <c r="E691" t="n">
+        <v>42</v>
+      </c>
+      <c r="F691" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G691" t="n">
+        <v>0</v>
+      </c>
+      <c r="H691" t="n">
+        <v>0</v>
+      </c>
+      <c r="I691" t="n">
+        <v>1</v>
+      </c>
+      <c r="J691" t="n">
+        <v>1</v>
+      </c>
+      <c r="K691" t="n">
+        <v>0</v>
+      </c>
+      <c r="L691" t="n">
+        <v>0</v>
+      </c>
+      <c r="M691" t="n">
+        <v>0</v>
+      </c>
+      <c r="N691" t="n">
+        <v>1</v>
+      </c>
+      <c r="O691" t="n">
+        <v>0</v>
+      </c>
+      <c r="P691" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q691" t="n">
+        <v>0</v>
+      </c>
+      <c r="R691" t="n">
+        <v>0</v>
+      </c>
+      <c r="S691" t="n">
+        <v>0</v>
+      </c>
+      <c r="T691" t="n">
+        <v>1</v>
+      </c>
+      <c r="U691" t="n">
+        <v>0</v>
+      </c>
+      <c r="V691" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W691" t="n">
+        <v>30</v>
+      </c>
+      <c r="X691" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>I. CRUZ UCEDA | J. GARCIA SANCHEZ | J. GODSPOWER JOHNSON | M. CAICEDO SANCHEZ | S. CECCARDI</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>5</v>
+      </c>
+      <c r="E692" t="n">
+        <v>49</v>
+      </c>
+      <c r="F692" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G692" t="n">
+        <v>0</v>
+      </c>
+      <c r="H692" t="n">
+        <v>4</v>
+      </c>
+      <c r="I692" t="n">
+        <v>1</v>
+      </c>
+      <c r="J692" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K692" t="n">
+        <v>0</v>
+      </c>
+      <c r="L692" t="n">
+        <v>454.55</v>
+      </c>
+      <c r="M692" t="n">
+        <v>-454.55</v>
+      </c>
+      <c r="N692" t="n">
+        <v>1</v>
+      </c>
+      <c r="O692" t="n">
+        <v>0</v>
+      </c>
+      <c r="P692" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q692" t="n">
+        <v>0</v>
+      </c>
+      <c r="R692" t="n">
+        <v>2</v>
+      </c>
+      <c r="S692" t="n">
+        <v>2</v>
+      </c>
+      <c r="T692" t="n">
+        <v>0</v>
+      </c>
+      <c r="U692" t="n">
+        <v>2</v>
+      </c>
+      <c r="V692" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W692" t="n">
+        <v>30</v>
+      </c>
+      <c r="X692" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>I. CRUZ UCEDA | M. CAICEDO SANCHEZ | M. STILMA | N. HOOVER</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>4</v>
+      </c>
+      <c r="E693" t="n">
+        <v>11</v>
+      </c>
+      <c r="F693" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G693" t="n">
+        <v>2</v>
+      </c>
+      <c r="H693" t="n">
+        <v>0</v>
+      </c>
+      <c r="I693" t="n">
+        <v>1</v>
+      </c>
+      <c r="J693" t="n">
+        <v>0</v>
+      </c>
+      <c r="K693" t="n">
+        <v>200</v>
+      </c>
+      <c r="L693" t="n">
+        <v>0</v>
+      </c>
+      <c r="M693" t="n">
+        <v>0</v>
+      </c>
+      <c r="N693" t="n">
+        <v>1</v>
+      </c>
+      <c r="O693" t="n">
+        <v>0</v>
+      </c>
+      <c r="P693" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q693" t="n">
+        <v>0</v>
+      </c>
+      <c r="R693" t="n">
+        <v>0</v>
+      </c>
+      <c r="S693" t="n">
+        <v>0</v>
+      </c>
+      <c r="T693" t="n">
+        <v>0</v>
+      </c>
+      <c r="U693" t="n">
+        <v>0</v>
+      </c>
+      <c r="V693" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W693" t="n">
+        <v>30</v>
+      </c>
+      <c r="X693" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>J. GODSPOWER JOHNSON | M. CAICEDO SANCHEZ | N. HOOVER | S. CECCARDI | S. RODRIGUEZ FEBLES</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>5</v>
+      </c>
+      <c r="E694" t="n">
+        <v>3</v>
+      </c>
+      <c r="F694" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G694" t="n">
+        <v>1</v>
+      </c>
+      <c r="H694" t="n">
+        <v>0</v>
+      </c>
+      <c r="I694" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J694" t="n">
+        <v>1</v>
+      </c>
+      <c r="K694" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L694" t="n">
+        <v>0</v>
+      </c>
+      <c r="M694" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N694" t="n">
+        <v>0</v>
+      </c>
+      <c r="O694" t="n">
+        <v>2</v>
+      </c>
+      <c r="P694" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q694" t="n">
+        <v>0</v>
+      </c>
+      <c r="R694" t="n">
+        <v>0</v>
+      </c>
+      <c r="S694" t="n">
+        <v>0</v>
+      </c>
+      <c r="T694" t="n">
+        <v>1</v>
+      </c>
+      <c r="U694" t="n">
+        <v>0</v>
+      </c>
+      <c r="V694" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W694" t="n">
+        <v>30</v>
+      </c>
+      <c r="X694" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>J. GODSPOWER JOHNSON | M. CAICEDO SANCHEZ | P. CORDOBA MURO | S. CECCARDI | S. RODRIGUEZ FEBLES</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>5</v>
+      </c>
+      <c r="E695" t="n">
+        <v>14</v>
+      </c>
+      <c r="F695" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G695" t="n">
+        <v>2</v>
+      </c>
+      <c r="H695" t="n">
+        <v>0</v>
+      </c>
+      <c r="I695" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="J695" t="n">
+        <v>1</v>
+      </c>
+      <c r="K695" t="n">
+        <v>0</v>
+      </c>
+      <c r="L695" t="n">
+        <v>0</v>
+      </c>
+      <c r="M695" t="n">
+        <v>0</v>
+      </c>
+      <c r="N695" t="n">
+        <v>0</v>
+      </c>
+      <c r="O695" t="n">
+        <v>2</v>
+      </c>
+      <c r="P695" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q695" t="n">
+        <v>1</v>
+      </c>
+      <c r="R695" t="n">
+        <v>1</v>
+      </c>
+      <c r="S695" t="n">
+        <v>0</v>
+      </c>
+      <c r="T695" t="n">
+        <v>0</v>
+      </c>
+      <c r="U695" t="n">
+        <v>0</v>
+      </c>
+      <c r="V695" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W695" t="n">
+        <v>30</v>
+      </c>
+      <c r="X695" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/1FEB_25_26/clutch_lineups_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/clutch_lineups_25_26_1FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X695"/>
+  <dimension ref="A1:X756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58846,6 +58846,5130 @@
         </is>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>A. HUELVES GARCIA | A. PARRADO CALABRIA | M. JACKSON | M. NUGU | R. SEOANE RODICIO</t>
+        </is>
+      </c>
+      <c r="D696" t="n">
+        <v>5</v>
+      </c>
+      <c r="E696" t="n">
+        <v>8</v>
+      </c>
+      <c r="F696" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G696" t="n">
+        <v>1</v>
+      </c>
+      <c r="H696" t="n">
+        <v>0</v>
+      </c>
+      <c r="I696" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J696" t="n">
+        <v>1</v>
+      </c>
+      <c r="K696" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L696" t="n">
+        <v>0</v>
+      </c>
+      <c r="M696" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N696" t="n">
+        <v>0</v>
+      </c>
+      <c r="O696" t="n">
+        <v>2</v>
+      </c>
+      <c r="P696" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q696" t="n">
+        <v>0</v>
+      </c>
+      <c r="R696" t="n">
+        <v>1</v>
+      </c>
+      <c r="S696" t="n">
+        <v>0</v>
+      </c>
+      <c r="T696" t="n">
+        <v>0</v>
+      </c>
+      <c r="U696" t="n">
+        <v>0</v>
+      </c>
+      <c r="V696" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W696" t="n">
+        <v>31</v>
+      </c>
+      <c r="X696" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>A. PARRADO CALABRIA | F. TERINS | J. BROWN-FERGUSON | M. JACKSON | M. NUGU</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>5</v>
+      </c>
+      <c r="E697" t="n">
+        <v>16</v>
+      </c>
+      <c r="F697" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G697" t="n">
+        <v>0</v>
+      </c>
+      <c r="H697" t="n">
+        <v>2</v>
+      </c>
+      <c r="I697" t="n">
+        <v>1</v>
+      </c>
+      <c r="J697" t="n">
+        <v>1</v>
+      </c>
+      <c r="K697" t="n">
+        <v>0</v>
+      </c>
+      <c r="L697" t="n">
+        <v>200</v>
+      </c>
+      <c r="M697" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N697" t="n">
+        <v>1</v>
+      </c>
+      <c r="O697" t="n">
+        <v>0</v>
+      </c>
+      <c r="P697" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q697" t="n">
+        <v>0</v>
+      </c>
+      <c r="R697" t="n">
+        <v>2</v>
+      </c>
+      <c r="S697" t="n">
+        <v>0</v>
+      </c>
+      <c r="T697" t="n">
+        <v>0</v>
+      </c>
+      <c r="U697" t="n">
+        <v>1</v>
+      </c>
+      <c r="V697" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W697" t="n">
+        <v>31</v>
+      </c>
+      <c r="X697" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>A. PARRADO CALABRIA | F. TERINS | J. ZIDEK | M. JACKSON | M. NUGU</t>
+        </is>
+      </c>
+      <c r="D698" t="n">
+        <v>5</v>
+      </c>
+      <c r="E698" t="n">
+        <v>138</v>
+      </c>
+      <c r="F698" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G698" t="n">
+        <v>2</v>
+      </c>
+      <c r="H698" t="n">
+        <v>0</v>
+      </c>
+      <c r="I698" t="n">
+        <v>2</v>
+      </c>
+      <c r="J698" t="n">
+        <v>2</v>
+      </c>
+      <c r="K698" t="n">
+        <v>100</v>
+      </c>
+      <c r="L698" t="n">
+        <v>0</v>
+      </c>
+      <c r="M698" t="n">
+        <v>100</v>
+      </c>
+      <c r="N698" t="n">
+        <v>4</v>
+      </c>
+      <c r="O698" t="n">
+        <v>0</v>
+      </c>
+      <c r="P698" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q698" t="n">
+        <v>2</v>
+      </c>
+      <c r="R698" t="n">
+        <v>3</v>
+      </c>
+      <c r="S698" t="n">
+        <v>0</v>
+      </c>
+      <c r="T698" t="n">
+        <v>1</v>
+      </c>
+      <c r="U698" t="n">
+        <v>2</v>
+      </c>
+      <c r="V698" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W698" t="n">
+        <v>31</v>
+      </c>
+      <c r="X698" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>A. PARRADO CALABRIA | J. BROWN-FERGUSON | J. ZIDEK | M. JACKSON | M. NUGU</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>5</v>
+      </c>
+      <c r="E699" t="n">
+        <v>9</v>
+      </c>
+      <c r="F699" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G699" t="n">
+        <v>0</v>
+      </c>
+      <c r="H699" t="n">
+        <v>1</v>
+      </c>
+      <c r="I699" t="n">
+        <v>1</v>
+      </c>
+      <c r="J699" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K699" t="n">
+        <v>0</v>
+      </c>
+      <c r="L699" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M699" t="n">
+        <v>-113.64</v>
+      </c>
+      <c r="N699" t="n">
+        <v>1</v>
+      </c>
+      <c r="O699" t="n">
+        <v>0</v>
+      </c>
+      <c r="P699" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q699" t="n">
+        <v>0</v>
+      </c>
+      <c r="R699" t="n">
+        <v>0</v>
+      </c>
+      <c r="S699" t="n">
+        <v>2</v>
+      </c>
+      <c r="T699" t="n">
+        <v>0</v>
+      </c>
+      <c r="U699" t="n">
+        <v>0</v>
+      </c>
+      <c r="V699" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W699" t="n">
+        <v>31</v>
+      </c>
+      <c r="X699" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>A. PARRADO CALABRIA | J. BROWN-FERGUSON | M. JACKSON | M. NUGU | R. SEOANE RODICIO</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>5</v>
+      </c>
+      <c r="E700" t="n">
+        <v>15</v>
+      </c>
+      <c r="F700" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G700" t="n">
+        <v>0</v>
+      </c>
+      <c r="H700" t="n">
+        <v>0</v>
+      </c>
+      <c r="I700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J700" t="n">
+        <v>0</v>
+      </c>
+      <c r="K700" t="n">
+        <v>0</v>
+      </c>
+      <c r="L700" t="n">
+        <v>0</v>
+      </c>
+      <c r="M700" t="n">
+        <v>0</v>
+      </c>
+      <c r="N700" t="n">
+        <v>0</v>
+      </c>
+      <c r="O700" t="n">
+        <v>0</v>
+      </c>
+      <c r="P700" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q700" t="n">
+        <v>0</v>
+      </c>
+      <c r="R700" t="n">
+        <v>0</v>
+      </c>
+      <c r="S700" t="n">
+        <v>0</v>
+      </c>
+      <c r="T700" t="n">
+        <v>0</v>
+      </c>
+      <c r="U700" t="n">
+        <v>0</v>
+      </c>
+      <c r="V700" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W700" t="n">
+        <v>31</v>
+      </c>
+      <c r="X700" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>A. PARRADO CALABRIA | J. ZIDEK | M. JACKSON | M. NUGU | R. SEOANE RODICIO</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>5</v>
+      </c>
+      <c r="E701" t="n">
+        <v>131</v>
+      </c>
+      <c r="F701" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G701" t="n">
+        <v>9</v>
+      </c>
+      <c r="H701" t="n">
+        <v>6</v>
+      </c>
+      <c r="I701" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="J701" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K701" t="n">
+        <v>153.06</v>
+      </c>
+      <c r="L701" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="M701" t="n">
+        <v>-55.27</v>
+      </c>
+      <c r="N701" t="n">
+        <v>6</v>
+      </c>
+      <c r="O701" t="n">
+        <v>2</v>
+      </c>
+      <c r="P701" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q701" t="n">
+        <v>1</v>
+      </c>
+      <c r="R701" t="n">
+        <v>2</v>
+      </c>
+      <c r="S701" t="n">
+        <v>2</v>
+      </c>
+      <c r="T701" t="n">
+        <v>1</v>
+      </c>
+      <c r="U701" t="n">
+        <v>1</v>
+      </c>
+      <c r="V701" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W701" t="n">
+        <v>31</v>
+      </c>
+      <c r="X701" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>F. TERINS | J. BROWN-FERGUSON | J. ZIDEK | M. JACKSON | M. NUGU</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>5</v>
+      </c>
+      <c r="E702" t="n">
+        <v>5</v>
+      </c>
+      <c r="F702" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G702" t="n">
+        <v>0</v>
+      </c>
+      <c r="H702" t="n">
+        <v>0</v>
+      </c>
+      <c r="I702" t="n">
+        <v>0</v>
+      </c>
+      <c r="J702" t="n">
+        <v>0</v>
+      </c>
+      <c r="K702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L702" t="n">
+        <v>0</v>
+      </c>
+      <c r="M702" t="n">
+        <v>0</v>
+      </c>
+      <c r="N702" t="n">
+        <v>0</v>
+      </c>
+      <c r="O702" t="n">
+        <v>0</v>
+      </c>
+      <c r="P702" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q702" t="n">
+        <v>0</v>
+      </c>
+      <c r="R702" t="n">
+        <v>0</v>
+      </c>
+      <c r="S702" t="n">
+        <v>0</v>
+      </c>
+      <c r="T702" t="n">
+        <v>0</v>
+      </c>
+      <c r="U702" t="n">
+        <v>0</v>
+      </c>
+      <c r="V702" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W702" t="n">
+        <v>31</v>
+      </c>
+      <c r="X702" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>F. TERINS | J. BROWN-FERGUSON | J. ZIDEK | M. JACKSON | R. SEOANE RODICIO</t>
+        </is>
+      </c>
+      <c r="D703" t="n">
+        <v>5</v>
+      </c>
+      <c r="E703" t="n">
+        <v>218</v>
+      </c>
+      <c r="F703" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="G703" t="n">
+        <v>10</v>
+      </c>
+      <c r="H703" t="n">
+        <v>7</v>
+      </c>
+      <c r="I703" t="n">
+        <v>5</v>
+      </c>
+      <c r="J703" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K703" t="n">
+        <v>200</v>
+      </c>
+      <c r="L703" t="n">
+        <v>180.41</v>
+      </c>
+      <c r="M703" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="N703" t="n">
+        <v>6</v>
+      </c>
+      <c r="O703" t="n">
+        <v>0</v>
+      </c>
+      <c r="P703" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q703" t="n">
+        <v>1</v>
+      </c>
+      <c r="R703" t="n">
+        <v>5</v>
+      </c>
+      <c r="S703" t="n">
+        <v>2</v>
+      </c>
+      <c r="T703" t="n">
+        <v>1</v>
+      </c>
+      <c r="U703" t="n">
+        <v>3</v>
+      </c>
+      <c r="V703" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W703" t="n">
+        <v>31</v>
+      </c>
+      <c r="X703" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>J. BROWN-FERGUSON | J. ZIDEK | M. JACKSON | M. NUGU | R. SEOANE RODICIO</t>
+        </is>
+      </c>
+      <c r="D704" t="n">
+        <v>5</v>
+      </c>
+      <c r="E704" t="n">
+        <v>57</v>
+      </c>
+      <c r="F704" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G704" t="n">
+        <v>0</v>
+      </c>
+      <c r="H704" t="n">
+        <v>2</v>
+      </c>
+      <c r="I704" t="n">
+        <v>1</v>
+      </c>
+      <c r="J704" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K704" t="n">
+        <v>0</v>
+      </c>
+      <c r="L704" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M704" t="n">
+        <v>-69.44</v>
+      </c>
+      <c r="N704" t="n">
+        <v>1</v>
+      </c>
+      <c r="O704" t="n">
+        <v>0</v>
+      </c>
+      <c r="P704" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q704" t="n">
+        <v>0</v>
+      </c>
+      <c r="R704" t="n">
+        <v>2</v>
+      </c>
+      <c r="S704" t="n">
+        <v>2</v>
+      </c>
+      <c r="T704" t="n">
+        <v>0</v>
+      </c>
+      <c r="U704" t="n">
+        <v>0</v>
+      </c>
+      <c r="V704" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W704" t="n">
+        <v>31</v>
+      </c>
+      <c r="X704" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>A. BARCELLO | A. GALAN POZO | D. KRAVIC | L. WESTERMANN | T. MUNNINGS</t>
+        </is>
+      </c>
+      <c r="D705" t="n">
+        <v>5</v>
+      </c>
+      <c r="E705" t="n">
+        <v>89</v>
+      </c>
+      <c r="F705" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G705" t="n">
+        <v>4</v>
+      </c>
+      <c r="H705" t="n">
+        <v>4</v>
+      </c>
+      <c r="I705" t="n">
+        <v>2</v>
+      </c>
+      <c r="J705" t="n">
+        <v>4</v>
+      </c>
+      <c r="K705" t="n">
+        <v>200</v>
+      </c>
+      <c r="L705" t="n">
+        <v>100</v>
+      </c>
+      <c r="M705" t="n">
+        <v>100</v>
+      </c>
+      <c r="N705" t="n">
+        <v>2</v>
+      </c>
+      <c r="O705" t="n">
+        <v>0</v>
+      </c>
+      <c r="P705" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q705" t="n">
+        <v>1</v>
+      </c>
+      <c r="R705" t="n">
+        <v>4</v>
+      </c>
+      <c r="S705" t="n">
+        <v>0</v>
+      </c>
+      <c r="T705" t="n">
+        <v>0</v>
+      </c>
+      <c r="U705" t="n">
+        <v>0</v>
+      </c>
+      <c r="V705" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W705" t="n">
+        <v>31</v>
+      </c>
+      <c r="X705" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>A. BARCELLO | D. DE SOUSA ANJO BRITO | F. DOS ANJOS DE PAULA | S. QUINTELA SALVADOR | Y. BARRUETA</t>
+        </is>
+      </c>
+      <c r="D706" t="n">
+        <v>5</v>
+      </c>
+      <c r="E706" t="n">
+        <v>8</v>
+      </c>
+      <c r="F706" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G706" t="n">
+        <v>0</v>
+      </c>
+      <c r="H706" t="n">
+        <v>1</v>
+      </c>
+      <c r="I706" t="n">
+        <v>1</v>
+      </c>
+      <c r="J706" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K706" t="n">
+        <v>0</v>
+      </c>
+      <c r="L706" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M706" t="n">
+        <v>-113.64</v>
+      </c>
+      <c r="N706" t="n">
+        <v>1</v>
+      </c>
+      <c r="O706" t="n">
+        <v>0</v>
+      </c>
+      <c r="P706" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q706" t="n">
+        <v>0</v>
+      </c>
+      <c r="R706" t="n">
+        <v>0</v>
+      </c>
+      <c r="S706" t="n">
+        <v>2</v>
+      </c>
+      <c r="T706" t="n">
+        <v>0</v>
+      </c>
+      <c r="U706" t="n">
+        <v>0</v>
+      </c>
+      <c r="V706" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W706" t="n">
+        <v>31</v>
+      </c>
+      <c r="X706" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>A. BARCELLO | D. KRAVIC | L. WESTERMANN | R. ANDERSSON | Y. BARRUETA</t>
+        </is>
+      </c>
+      <c r="D707" t="n">
+        <v>5</v>
+      </c>
+      <c r="E707" t="n">
+        <v>122</v>
+      </c>
+      <c r="F707" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="G707" t="n">
+        <v>0</v>
+      </c>
+      <c r="H707" t="n">
+        <v>2</v>
+      </c>
+      <c r="I707" t="n">
+        <v>1</v>
+      </c>
+      <c r="J707" t="n">
+        <v>1</v>
+      </c>
+      <c r="K707" t="n">
+        <v>0</v>
+      </c>
+      <c r="L707" t="n">
+        <v>200</v>
+      </c>
+      <c r="M707" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N707" t="n">
+        <v>3</v>
+      </c>
+      <c r="O707" t="n">
+        <v>0</v>
+      </c>
+      <c r="P707" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q707" t="n">
+        <v>2</v>
+      </c>
+      <c r="R707" t="n">
+        <v>3</v>
+      </c>
+      <c r="S707" t="n">
+        <v>0</v>
+      </c>
+      <c r="T707" t="n">
+        <v>0</v>
+      </c>
+      <c r="U707" t="n">
+        <v>2</v>
+      </c>
+      <c r="V707" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W707" t="n">
+        <v>31</v>
+      </c>
+      <c r="X707" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>A. BARCELLO | D. KRAVIC | R. ANDERSSON | S. QUINTELA SALVADOR | Y. BARRUETA</t>
+        </is>
+      </c>
+      <c r="D708" t="n">
+        <v>5</v>
+      </c>
+      <c r="E708" t="n">
+        <v>16</v>
+      </c>
+      <c r="F708" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G708" t="n">
+        <v>0</v>
+      </c>
+      <c r="H708" t="n">
+        <v>0</v>
+      </c>
+      <c r="I708" t="n">
+        <v>1</v>
+      </c>
+      <c r="J708" t="n">
+        <v>1</v>
+      </c>
+      <c r="K708" t="n">
+        <v>0</v>
+      </c>
+      <c r="L708" t="n">
+        <v>0</v>
+      </c>
+      <c r="M708" t="n">
+        <v>0</v>
+      </c>
+      <c r="N708" t="n">
+        <v>0</v>
+      </c>
+      <c r="O708" t="n">
+        <v>0</v>
+      </c>
+      <c r="P708" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q708" t="n">
+        <v>0</v>
+      </c>
+      <c r="R708" t="n">
+        <v>1</v>
+      </c>
+      <c r="S708" t="n">
+        <v>0</v>
+      </c>
+      <c r="T708" t="n">
+        <v>0</v>
+      </c>
+      <c r="U708" t="n">
+        <v>0</v>
+      </c>
+      <c r="V708" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W708" t="n">
+        <v>31</v>
+      </c>
+      <c r="X708" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>A. BARCELLO | F. DOS ANJOS DE PAULA | L. WESTERMANN | R. ANDERSSON | T. MUNNINGS</t>
+        </is>
+      </c>
+      <c r="D709" t="n">
+        <v>5</v>
+      </c>
+      <c r="E709" t="n">
+        <v>257</v>
+      </c>
+      <c r="F709" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="G709" t="n">
+        <v>9</v>
+      </c>
+      <c r="H709" t="n">
+        <v>10</v>
+      </c>
+      <c r="I709" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="J709" t="n">
+        <v>6</v>
+      </c>
+      <c r="K709" t="n">
+        <v>189.08</v>
+      </c>
+      <c r="L709" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="M709" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="N709" t="n">
+        <v>5</v>
+      </c>
+      <c r="O709" t="n">
+        <v>4</v>
+      </c>
+      <c r="P709" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q709" t="n">
+        <v>3</v>
+      </c>
+      <c r="R709" t="n">
+        <v>7</v>
+      </c>
+      <c r="S709" t="n">
+        <v>0</v>
+      </c>
+      <c r="T709" t="n">
+        <v>0</v>
+      </c>
+      <c r="U709" t="n">
+        <v>1</v>
+      </c>
+      <c r="V709" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W709" t="n">
+        <v>31</v>
+      </c>
+      <c r="X709" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>A. BARCELLO | F. DOS ANJOS DE PAULA | L. WESTERMANN | R. ANDERSSON | Y. BARRUETA</t>
+        </is>
+      </c>
+      <c r="D710" t="n">
+        <v>5</v>
+      </c>
+      <c r="E710" t="n">
+        <v>3</v>
+      </c>
+      <c r="F710" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G710" t="n">
+        <v>0</v>
+      </c>
+      <c r="H710" t="n">
+        <v>2</v>
+      </c>
+      <c r="I710" t="n">
+        <v>0</v>
+      </c>
+      <c r="J710" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K710" t="n">
+        <v>0</v>
+      </c>
+      <c r="L710" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M710" t="n">
+        <v>0</v>
+      </c>
+      <c r="N710" t="n">
+        <v>0</v>
+      </c>
+      <c r="O710" t="n">
+        <v>0</v>
+      </c>
+      <c r="P710" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q710" t="n">
+        <v>0</v>
+      </c>
+      <c r="R710" t="n">
+        <v>0</v>
+      </c>
+      <c r="S710" t="n">
+        <v>2</v>
+      </c>
+      <c r="T710" t="n">
+        <v>0</v>
+      </c>
+      <c r="U710" t="n">
+        <v>0</v>
+      </c>
+      <c r="V710" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W710" t="n">
+        <v>31</v>
+      </c>
+      <c r="X710" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>A. BARCELLO | F. DOS ANJOS DE PAULA | L. WESTERMANN | T. MUNNINGS | Y. BARRUETA</t>
+        </is>
+      </c>
+      <c r="D711" t="n">
+        <v>5</v>
+      </c>
+      <c r="E711" t="n">
+        <v>38</v>
+      </c>
+      <c r="F711" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G711" t="n">
+        <v>0</v>
+      </c>
+      <c r="H711" t="n">
+        <v>0</v>
+      </c>
+      <c r="I711" t="n">
+        <v>2</v>
+      </c>
+      <c r="J711" t="n">
+        <v>0</v>
+      </c>
+      <c r="K711" t="n">
+        <v>0</v>
+      </c>
+      <c r="L711" t="n">
+        <v>0</v>
+      </c>
+      <c r="M711" t="n">
+        <v>0</v>
+      </c>
+      <c r="N711" t="n">
+        <v>2</v>
+      </c>
+      <c r="O711" t="n">
+        <v>0</v>
+      </c>
+      <c r="P711" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q711" t="n">
+        <v>0</v>
+      </c>
+      <c r="R711" t="n">
+        <v>0</v>
+      </c>
+      <c r="S711" t="n">
+        <v>0</v>
+      </c>
+      <c r="T711" t="n">
+        <v>0</v>
+      </c>
+      <c r="U711" t="n">
+        <v>0</v>
+      </c>
+      <c r="V711" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W711" t="n">
+        <v>31</v>
+      </c>
+      <c r="X711" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>D. DE SOUSA ANJO BRITO | D. KRAVIC | R. ANDERSSON | S. QUINTELA SALVADOR | T. MUNNINGS</t>
+        </is>
+      </c>
+      <c r="D712" t="n">
+        <v>5</v>
+      </c>
+      <c r="E712" t="n">
+        <v>39</v>
+      </c>
+      <c r="F712" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G712" t="n">
+        <v>2</v>
+      </c>
+      <c r="H712" t="n">
+        <v>3</v>
+      </c>
+      <c r="I712" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J712" t="n">
+        <v>1</v>
+      </c>
+      <c r="K712" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L712" t="n">
+        <v>300</v>
+      </c>
+      <c r="M712" t="n">
+        <v>-72.73</v>
+      </c>
+      <c r="N712" t="n">
+        <v>0</v>
+      </c>
+      <c r="O712" t="n">
+        <v>2</v>
+      </c>
+      <c r="P712" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q712" t="n">
+        <v>0</v>
+      </c>
+      <c r="R712" t="n">
+        <v>2</v>
+      </c>
+      <c r="S712" t="n">
+        <v>0</v>
+      </c>
+      <c r="T712" t="n">
+        <v>0</v>
+      </c>
+      <c r="U712" t="n">
+        <v>1</v>
+      </c>
+      <c r="V712" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W712" t="n">
+        <v>31</v>
+      </c>
+      <c r="X712" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>D. DE SOUSA ANJO BRITO | F. DOS ANJOS DE PAULA | L. WESTERMANN | S. QUINTELA SALVADOR | T. MUNNINGS</t>
+        </is>
+      </c>
+      <c r="D713" t="n">
+        <v>5</v>
+      </c>
+      <c r="E713" t="n">
+        <v>16</v>
+      </c>
+      <c r="F713" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G713" t="n">
+        <v>2</v>
+      </c>
+      <c r="H713" t="n">
+        <v>0</v>
+      </c>
+      <c r="I713" t="n">
+        <v>1</v>
+      </c>
+      <c r="J713" t="n">
+        <v>1</v>
+      </c>
+      <c r="K713" t="n">
+        <v>200</v>
+      </c>
+      <c r="L713" t="n">
+        <v>0</v>
+      </c>
+      <c r="M713" t="n">
+        <v>200</v>
+      </c>
+      <c r="N713" t="n">
+        <v>2</v>
+      </c>
+      <c r="O713" t="n">
+        <v>0</v>
+      </c>
+      <c r="P713" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q713" t="n">
+        <v>1</v>
+      </c>
+      <c r="R713" t="n">
+        <v>1</v>
+      </c>
+      <c r="S713" t="n">
+        <v>0</v>
+      </c>
+      <c r="T713" t="n">
+        <v>0</v>
+      </c>
+      <c r="U713" t="n">
+        <v>0</v>
+      </c>
+      <c r="V713" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W713" t="n">
+        <v>31</v>
+      </c>
+      <c r="X713" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>D. DE SOUSA ANJO BRITO | F. DOS ANJOS DE PAULA | R. ANDERSSON | S. QUINTELA SALVADOR | Y. BARRUETA</t>
+        </is>
+      </c>
+      <c r="D714" t="n">
+        <v>5</v>
+      </c>
+      <c r="E714" t="n">
+        <v>9</v>
+      </c>
+      <c r="F714" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G714" t="n">
+        <v>1</v>
+      </c>
+      <c r="H714" t="n">
+        <v>0</v>
+      </c>
+      <c r="I714" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J714" t="n">
+        <v>1</v>
+      </c>
+      <c r="K714" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L714" t="n">
+        <v>0</v>
+      </c>
+      <c r="M714" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N714" t="n">
+        <v>0</v>
+      </c>
+      <c r="O714" t="n">
+        <v>2</v>
+      </c>
+      <c r="P714" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q714" t="n">
+        <v>0</v>
+      </c>
+      <c r="R714" t="n">
+        <v>1</v>
+      </c>
+      <c r="S714" t="n">
+        <v>0</v>
+      </c>
+      <c r="T714" t="n">
+        <v>0</v>
+      </c>
+      <c r="U714" t="n">
+        <v>0</v>
+      </c>
+      <c r="V714" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W714" t="n">
+        <v>31</v>
+      </c>
+      <c r="X714" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO vs GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2486534</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>D. SARAIVA SEIXAS | I. VAZQUEZ PEREZ | R. DIAS MARQUES LISBOA SANTOS | R. GILL | S. MC DONNELL</t>
+        </is>
+      </c>
+      <c r="D715" t="n">
+        <v>5</v>
+      </c>
+      <c r="E715" t="n">
+        <v>72</v>
+      </c>
+      <c r="F715" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G715" t="n">
+        <v>5</v>
+      </c>
+      <c r="H715" t="n">
+        <v>3</v>
+      </c>
+      <c r="I715" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J715" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K715" t="n">
+        <v>284.09</v>
+      </c>
+      <c r="L715" t="n">
+        <v>170.45</v>
+      </c>
+      <c r="M715" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N715" t="n">
+        <v>2</v>
+      </c>
+      <c r="O715" t="n">
+        <v>4</v>
+      </c>
+      <c r="P715" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q715" t="n">
+        <v>2</v>
+      </c>
+      <c r="R715" t="n">
+        <v>1</v>
+      </c>
+      <c r="S715" t="n">
+        <v>4</v>
+      </c>
+      <c r="T715" t="n">
+        <v>1</v>
+      </c>
+      <c r="U715" t="n">
+        <v>2</v>
+      </c>
+      <c r="V715" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W715" t="n">
+        <v>31</v>
+      </c>
+      <c r="X715" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2486534</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>A. MUÑOZ BORCHERS | A. WINTERING | I. JAKOVICS | M. KAMBA | V. VUCETIC</t>
+        </is>
+      </c>
+      <c r="D716" t="n">
+        <v>5</v>
+      </c>
+      <c r="E716" t="n">
+        <v>14</v>
+      </c>
+      <c r="F716" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G716" t="n">
+        <v>0</v>
+      </c>
+      <c r="H716" t="n">
+        <v>2</v>
+      </c>
+      <c r="I716" t="n">
+        <v>0</v>
+      </c>
+      <c r="J716" t="n">
+        <v>1</v>
+      </c>
+      <c r="K716" t="n">
+        <v>0</v>
+      </c>
+      <c r="L716" t="n">
+        <v>200</v>
+      </c>
+      <c r="M716" t="n">
+        <v>0</v>
+      </c>
+      <c r="N716" t="n">
+        <v>0</v>
+      </c>
+      <c r="O716" t="n">
+        <v>0</v>
+      </c>
+      <c r="P716" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q716" t="n">
+        <v>0</v>
+      </c>
+      <c r="R716" t="n">
+        <v>2</v>
+      </c>
+      <c r="S716" t="n">
+        <v>0</v>
+      </c>
+      <c r="T716" t="n">
+        <v>0</v>
+      </c>
+      <c r="U716" t="n">
+        <v>1</v>
+      </c>
+      <c r="V716" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W716" t="n">
+        <v>31</v>
+      </c>
+      <c r="X716" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2486534</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>A. WINTERING | I. JAKOVICS | J. VRANKIC | M. KAMBA | V. VUCETIC</t>
+        </is>
+      </c>
+      <c r="D717" t="n">
+        <v>5</v>
+      </c>
+      <c r="E717" t="n">
+        <v>44</v>
+      </c>
+      <c r="F717" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G717" t="n">
+        <v>1</v>
+      </c>
+      <c r="H717" t="n">
+        <v>3</v>
+      </c>
+      <c r="I717" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J717" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K717" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L717" t="n">
+        <v>394.74</v>
+      </c>
+      <c r="M717" t="n">
+        <v>-281.1</v>
+      </c>
+      <c r="N717" t="n">
+        <v>1</v>
+      </c>
+      <c r="O717" t="n">
+        <v>2</v>
+      </c>
+      <c r="P717" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q717" t="n">
+        <v>2</v>
+      </c>
+      <c r="R717" t="n">
+        <v>0</v>
+      </c>
+      <c r="S717" t="n">
+        <v>4</v>
+      </c>
+      <c r="T717" t="n">
+        <v>0</v>
+      </c>
+      <c r="U717" t="n">
+        <v>1</v>
+      </c>
+      <c r="V717" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W717" t="n">
+        <v>31</v>
+      </c>
+      <c r="X717" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2486534</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>I. JAKOVICS | J. VRANKIC | M. KAMBA | V. VUCETIC | X. OROZ URIA</t>
+        </is>
+      </c>
+      <c r="D718" t="n">
+        <v>5</v>
+      </c>
+      <c r="E718" t="n">
+        <v>14</v>
+      </c>
+      <c r="F718" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G718" t="n">
+        <v>2</v>
+      </c>
+      <c r="H718" t="n">
+        <v>0</v>
+      </c>
+      <c r="I718" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J718" t="n">
+        <v>0</v>
+      </c>
+      <c r="K718" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L718" t="n">
+        <v>0</v>
+      </c>
+      <c r="M718" t="n">
+        <v>0</v>
+      </c>
+      <c r="N718" t="n">
+        <v>0</v>
+      </c>
+      <c r="O718" t="n">
+        <v>2</v>
+      </c>
+      <c r="P718" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q718" t="n">
+        <v>0</v>
+      </c>
+      <c r="R718" t="n">
+        <v>0</v>
+      </c>
+      <c r="S718" t="n">
+        <v>0</v>
+      </c>
+      <c r="T718" t="n">
+        <v>0</v>
+      </c>
+      <c r="U718" t="n">
+        <v>0</v>
+      </c>
+      <c r="V718" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W718" t="n">
+        <v>31</v>
+      </c>
+      <c r="X718" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2486529</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>B. VAZQUEZ ARRAIZA | J. ARAMBURU LAMY | L. BRACEY | L. CAPALBO | O. MATULIONIS</t>
+        </is>
+      </c>
+      <c r="D719" t="n">
+        <v>5</v>
+      </c>
+      <c r="E719" t="n">
+        <v>46</v>
+      </c>
+      <c r="F719" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G719" t="n">
+        <v>2</v>
+      </c>
+      <c r="H719" t="n">
+        <v>2</v>
+      </c>
+      <c r="I719" t="n">
+        <v>2</v>
+      </c>
+      <c r="J719" t="n">
+        <v>1</v>
+      </c>
+      <c r="K719" t="n">
+        <v>100</v>
+      </c>
+      <c r="L719" t="n">
+        <v>200</v>
+      </c>
+      <c r="M719" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N719" t="n">
+        <v>2</v>
+      </c>
+      <c r="O719" t="n">
+        <v>0</v>
+      </c>
+      <c r="P719" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q719" t="n">
+        <v>0</v>
+      </c>
+      <c r="R719" t="n">
+        <v>1</v>
+      </c>
+      <c r="S719" t="n">
+        <v>0</v>
+      </c>
+      <c r="T719" t="n">
+        <v>0</v>
+      </c>
+      <c r="U719" t="n">
+        <v>0</v>
+      </c>
+      <c r="V719" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W719" t="n">
+        <v>31</v>
+      </c>
+      <c r="X719" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2486529</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>B. VAZQUEZ ARRAIZA | J. ARAMBURU LAMY | L. CAPALBO | O. MATULIONIS | P. BOMBINO PARADA</t>
+        </is>
+      </c>
+      <c r="D720" t="n">
+        <v>5</v>
+      </c>
+      <c r="E720" t="n">
+        <v>75</v>
+      </c>
+      <c r="F720" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G720" t="n">
+        <v>0</v>
+      </c>
+      <c r="H720" t="n">
+        <v>1</v>
+      </c>
+      <c r="I720" t="n">
+        <v>2</v>
+      </c>
+      <c r="J720" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K720" t="n">
+        <v>0</v>
+      </c>
+      <c r="L720" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M720" t="n">
+        <v>-113.64</v>
+      </c>
+      <c r="N720" t="n">
+        <v>2</v>
+      </c>
+      <c r="O720" t="n">
+        <v>0</v>
+      </c>
+      <c r="P720" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q720" t="n">
+        <v>1</v>
+      </c>
+      <c r="R720" t="n">
+        <v>0</v>
+      </c>
+      <c r="S720" t="n">
+        <v>2</v>
+      </c>
+      <c r="T720" t="n">
+        <v>0</v>
+      </c>
+      <c r="U720" t="n">
+        <v>0</v>
+      </c>
+      <c r="V720" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W720" t="n">
+        <v>31</v>
+      </c>
+      <c r="X720" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2486529</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>B. VAZQUEZ ARRAIZA | L. CAPALBO | O. MATULIONIS | P. BOMBINO PARADA | S. NIANG BEYE</t>
+        </is>
+      </c>
+      <c r="D721" t="n">
+        <v>5</v>
+      </c>
+      <c r="E721" t="n">
+        <v>36</v>
+      </c>
+      <c r="F721" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G721" t="n">
+        <v>0</v>
+      </c>
+      <c r="H721" t="n">
+        <v>2</v>
+      </c>
+      <c r="I721" t="n">
+        <v>1</v>
+      </c>
+      <c r="J721" t="n">
+        <v>1</v>
+      </c>
+      <c r="K721" t="n">
+        <v>0</v>
+      </c>
+      <c r="L721" t="n">
+        <v>200</v>
+      </c>
+      <c r="M721" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N721" t="n">
+        <v>1</v>
+      </c>
+      <c r="O721" t="n">
+        <v>0</v>
+      </c>
+      <c r="P721" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q721" t="n">
+        <v>0</v>
+      </c>
+      <c r="R721" t="n">
+        <v>3</v>
+      </c>
+      <c r="S721" t="n">
+        <v>0</v>
+      </c>
+      <c r="T721" t="n">
+        <v>0</v>
+      </c>
+      <c r="U721" t="n">
+        <v>2</v>
+      </c>
+      <c r="V721" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W721" t="n">
+        <v>31</v>
+      </c>
+      <c r="X721" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2486529</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>J. ARAMBURU LAMY | L. BRACEY | L. CAPALBO | O. MATULIONIS | S. NIANG BEYE</t>
+        </is>
+      </c>
+      <c r="D722" t="n">
+        <v>5</v>
+      </c>
+      <c r="E722" t="n">
+        <v>31</v>
+      </c>
+      <c r="F722" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G722" t="n">
+        <v>0</v>
+      </c>
+      <c r="H722" t="n">
+        <v>1</v>
+      </c>
+      <c r="I722" t="n">
+        <v>1</v>
+      </c>
+      <c r="J722" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K722" t="n">
+        <v>0</v>
+      </c>
+      <c r="L722" t="n">
+        <v>0</v>
+      </c>
+      <c r="M722" t="n">
+        <v>0</v>
+      </c>
+      <c r="N722" t="n">
+        <v>1</v>
+      </c>
+      <c r="O722" t="n">
+        <v>0</v>
+      </c>
+      <c r="P722" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q722" t="n">
+        <v>0</v>
+      </c>
+      <c r="R722" t="n">
+        <v>0</v>
+      </c>
+      <c r="S722" t="n">
+        <v>2</v>
+      </c>
+      <c r="T722" t="n">
+        <v>0</v>
+      </c>
+      <c r="U722" t="n">
+        <v>1</v>
+      </c>
+      <c r="V722" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W722" t="n">
+        <v>31</v>
+      </c>
+      <c r="X722" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2486529</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>G. KORSANTIA | G. MAIZA APECECHEA | J. NICOLAU ALEDON | J. TATE | M. MOTOS CABODEVILLA</t>
+        </is>
+      </c>
+      <c r="D723" t="n">
+        <v>5</v>
+      </c>
+      <c r="E723" t="n">
+        <v>36</v>
+      </c>
+      <c r="F723" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G723" t="n">
+        <v>2</v>
+      </c>
+      <c r="H723" t="n">
+        <v>0</v>
+      </c>
+      <c r="I723" t="n">
+        <v>1</v>
+      </c>
+      <c r="J723" t="n">
+        <v>1</v>
+      </c>
+      <c r="K723" t="n">
+        <v>200</v>
+      </c>
+      <c r="L723" t="n">
+        <v>0</v>
+      </c>
+      <c r="M723" t="n">
+        <v>200</v>
+      </c>
+      <c r="N723" t="n">
+        <v>3</v>
+      </c>
+      <c r="O723" t="n">
+        <v>0</v>
+      </c>
+      <c r="P723" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q723" t="n">
+        <v>2</v>
+      </c>
+      <c r="R723" t="n">
+        <v>1</v>
+      </c>
+      <c r="S723" t="n">
+        <v>0</v>
+      </c>
+      <c r="T723" t="n">
+        <v>0</v>
+      </c>
+      <c r="U723" t="n">
+        <v>0</v>
+      </c>
+      <c r="V723" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W723" t="n">
+        <v>31</v>
+      </c>
+      <c r="X723" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2486529</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>G. KORSANTIA | G. MAIZA APECECHEA | J. NICOLAU ALEDON | J. TATE | O. HANZLIK</t>
+        </is>
+      </c>
+      <c r="D724" t="n">
+        <v>5</v>
+      </c>
+      <c r="E724" t="n">
+        <v>75</v>
+      </c>
+      <c r="F724" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G724" t="n">
+        <v>1</v>
+      </c>
+      <c r="H724" t="n">
+        <v>0</v>
+      </c>
+      <c r="I724" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J724" t="n">
+        <v>2</v>
+      </c>
+      <c r="K724" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L724" t="n">
+        <v>0</v>
+      </c>
+      <c r="M724" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N724" t="n">
+        <v>0</v>
+      </c>
+      <c r="O724" t="n">
+        <v>2</v>
+      </c>
+      <c r="P724" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q724" t="n">
+        <v>0</v>
+      </c>
+      <c r="R724" t="n">
+        <v>2</v>
+      </c>
+      <c r="S724" t="n">
+        <v>0</v>
+      </c>
+      <c r="T724" t="n">
+        <v>1</v>
+      </c>
+      <c r="U724" t="n">
+        <v>1</v>
+      </c>
+      <c r="V724" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W724" t="n">
+        <v>31</v>
+      </c>
+      <c r="X724" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2486529</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>G. MAIZA APECECHEA | J. NICOLAU ALEDON | J. TATE | M. ANSORREGUI DEBA | O. HANZLIK</t>
+        </is>
+      </c>
+      <c r="D725" t="n">
+        <v>5</v>
+      </c>
+      <c r="E725" t="n">
+        <v>31</v>
+      </c>
+      <c r="F725" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G725" t="n">
+        <v>1</v>
+      </c>
+      <c r="H725" t="n">
+        <v>0</v>
+      </c>
+      <c r="I725" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="J725" t="n">
+        <v>1</v>
+      </c>
+      <c r="K725" t="n">
+        <v>0</v>
+      </c>
+      <c r="L725" t="n">
+        <v>0</v>
+      </c>
+      <c r="M725" t="n">
+        <v>0</v>
+      </c>
+      <c r="N725" t="n">
+        <v>0</v>
+      </c>
+      <c r="O725" t="n">
+        <v>2</v>
+      </c>
+      <c r="P725" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q725" t="n">
+        <v>1</v>
+      </c>
+      <c r="R725" t="n">
+        <v>1</v>
+      </c>
+      <c r="S725" t="n">
+        <v>0</v>
+      </c>
+      <c r="T725" t="n">
+        <v>0</v>
+      </c>
+      <c r="U725" t="n">
+        <v>0</v>
+      </c>
+      <c r="V725" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W725" t="n">
+        <v>31</v>
+      </c>
+      <c r="X725" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2486529</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>G. MAIZA APECECHEA | J. TATE | M. ANSORREGUI DEBA | M. MOTOS CABODEVILLA | O. HANZLIK</t>
+        </is>
+      </c>
+      <c r="D726" t="n">
+        <v>5</v>
+      </c>
+      <c r="E726" t="n">
+        <v>46</v>
+      </c>
+      <c r="F726" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G726" t="n">
+        <v>2</v>
+      </c>
+      <c r="H726" t="n">
+        <v>2</v>
+      </c>
+      <c r="I726" t="n">
+        <v>1</v>
+      </c>
+      <c r="J726" t="n">
+        <v>2</v>
+      </c>
+      <c r="K726" t="n">
+        <v>200</v>
+      </c>
+      <c r="L726" t="n">
+        <v>100</v>
+      </c>
+      <c r="M726" t="n">
+        <v>100</v>
+      </c>
+      <c r="N726" t="n">
+        <v>1</v>
+      </c>
+      <c r="O726" t="n">
+        <v>0</v>
+      </c>
+      <c r="P726" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q726" t="n">
+        <v>0</v>
+      </c>
+      <c r="R726" t="n">
+        <v>2</v>
+      </c>
+      <c r="S726" t="n">
+        <v>0</v>
+      </c>
+      <c r="T726" t="n">
+        <v>0</v>
+      </c>
+      <c r="U726" t="n">
+        <v>0</v>
+      </c>
+      <c r="V726" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W726" t="n">
+        <v>31</v>
+      </c>
+      <c r="X726" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA vs FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2486536</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>B. DE BISSCHOP | G. RENFROE | M. DIAZ | P. RIGOT | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D727" t="n">
+        <v>5</v>
+      </c>
+      <c r="E727" t="n">
+        <v>16</v>
+      </c>
+      <c r="F727" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G727" t="n">
+        <v>2</v>
+      </c>
+      <c r="H727" t="n">
+        <v>0</v>
+      </c>
+      <c r="I727" t="n">
+        <v>1</v>
+      </c>
+      <c r="J727" t="n">
+        <v>0</v>
+      </c>
+      <c r="K727" t="n">
+        <v>200</v>
+      </c>
+      <c r="L727" t="n">
+        <v>0</v>
+      </c>
+      <c r="M727" t="n">
+        <v>0</v>
+      </c>
+      <c r="N727" t="n">
+        <v>1</v>
+      </c>
+      <c r="O727" t="n">
+        <v>0</v>
+      </c>
+      <c r="P727" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q727" t="n">
+        <v>0</v>
+      </c>
+      <c r="R727" t="n">
+        <v>0</v>
+      </c>
+      <c r="S727" t="n">
+        <v>0</v>
+      </c>
+      <c r="T727" t="n">
+        <v>0</v>
+      </c>
+      <c r="U727" t="n">
+        <v>0</v>
+      </c>
+      <c r="V727" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W727" t="n">
+        <v>31</v>
+      </c>
+      <c r="X727" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2486536</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>D. VAN OOSTRUM | J. POWELL | J. YU | M. LAPORNIK | P. HERNANDEZ MONTENEGRO</t>
+        </is>
+      </c>
+      <c r="D728" t="n">
+        <v>5</v>
+      </c>
+      <c r="E728" t="n">
+        <v>16</v>
+      </c>
+      <c r="F728" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G728" t="n">
+        <v>0</v>
+      </c>
+      <c r="H728" t="n">
+        <v>2</v>
+      </c>
+      <c r="I728" t="n">
+        <v>0</v>
+      </c>
+      <c r="J728" t="n">
+        <v>1</v>
+      </c>
+      <c r="K728" t="n">
+        <v>0</v>
+      </c>
+      <c r="L728" t="n">
+        <v>200</v>
+      </c>
+      <c r="M728" t="n">
+        <v>0</v>
+      </c>
+      <c r="N728" t="n">
+        <v>0</v>
+      </c>
+      <c r="O728" t="n">
+        <v>0</v>
+      </c>
+      <c r="P728" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q728" t="n">
+        <v>0</v>
+      </c>
+      <c r="R728" t="n">
+        <v>1</v>
+      </c>
+      <c r="S728" t="n">
+        <v>0</v>
+      </c>
+      <c r="T728" t="n">
+        <v>0</v>
+      </c>
+      <c r="U728" t="n">
+        <v>0</v>
+      </c>
+      <c r="V728" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W728" t="n">
+        <v>31</v>
+      </c>
+      <c r="X728" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA vs GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2486543</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>C. ROGERS | J. PERIS CRESPO | J. VAN ZEGEREN | S. THRASTARSON | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D729" t="n">
+        <v>5</v>
+      </c>
+      <c r="E729" t="n">
+        <v>15</v>
+      </c>
+      <c r="F729" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G729" t="n">
+        <v>0</v>
+      </c>
+      <c r="H729" t="n">
+        <v>3</v>
+      </c>
+      <c r="I729" t="n">
+        <v>1</v>
+      </c>
+      <c r="J729" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K729" t="n">
+        <v>0</v>
+      </c>
+      <c r="L729" t="n">
+        <v>394.74</v>
+      </c>
+      <c r="M729" t="n">
+        <v>-394.74</v>
+      </c>
+      <c r="N729" t="n">
+        <v>1</v>
+      </c>
+      <c r="O729" t="n">
+        <v>0</v>
+      </c>
+      <c r="P729" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q729" t="n">
+        <v>0</v>
+      </c>
+      <c r="R729" t="n">
+        <v>0</v>
+      </c>
+      <c r="S729" t="n">
+        <v>4</v>
+      </c>
+      <c r="T729" t="n">
+        <v>0</v>
+      </c>
+      <c r="U729" t="n">
+        <v>1</v>
+      </c>
+      <c r="V729" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W729" t="n">
+        <v>32</v>
+      </c>
+      <c r="X729" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2486543</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>C. ROGERS | J. ROUND | J. VAN ZEGEREN | S. THRASTARSON | T. NASPLER PERAIRE</t>
+        </is>
+      </c>
+      <c r="D730" t="n">
+        <v>5</v>
+      </c>
+      <c r="E730" t="n">
+        <v>83</v>
+      </c>
+      <c r="F730" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G730" t="n">
+        <v>2</v>
+      </c>
+      <c r="H730" t="n">
+        <v>0</v>
+      </c>
+      <c r="I730" t="n">
+        <v>1</v>
+      </c>
+      <c r="J730" t="n">
+        <v>2</v>
+      </c>
+      <c r="K730" t="n">
+        <v>200</v>
+      </c>
+      <c r="L730" t="n">
+        <v>0</v>
+      </c>
+      <c r="M730" t="n">
+        <v>200</v>
+      </c>
+      <c r="N730" t="n">
+        <v>2</v>
+      </c>
+      <c r="O730" t="n">
+        <v>0</v>
+      </c>
+      <c r="P730" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q730" t="n">
+        <v>1</v>
+      </c>
+      <c r="R730" t="n">
+        <v>1</v>
+      </c>
+      <c r="S730" t="n">
+        <v>0</v>
+      </c>
+      <c r="T730" t="n">
+        <v>2</v>
+      </c>
+      <c r="U730" t="n">
+        <v>1</v>
+      </c>
+      <c r="V730" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W730" t="n">
+        <v>32</v>
+      </c>
+      <c r="X730" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2486543</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>C. ROGERS | J. ROUND | J. VAN ZEGEREN | S. THRASTARSON | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D731" t="n">
+        <v>5</v>
+      </c>
+      <c r="E731" t="n">
+        <v>61</v>
+      </c>
+      <c r="F731" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G731" t="n">
+        <v>2</v>
+      </c>
+      <c r="H731" t="n">
+        <v>1</v>
+      </c>
+      <c r="I731" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J731" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K731" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="L731" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M731" t="n">
+        <v>-44.19</v>
+      </c>
+      <c r="N731" t="n">
+        <v>4</v>
+      </c>
+      <c r="O731" t="n">
+        <v>2</v>
+      </c>
+      <c r="P731" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q731" t="n">
+        <v>2</v>
+      </c>
+      <c r="R731" t="n">
+        <v>2</v>
+      </c>
+      <c r="S731" t="n">
+        <v>2</v>
+      </c>
+      <c r="T731" t="n">
+        <v>0</v>
+      </c>
+      <c r="U731" t="n">
+        <v>2</v>
+      </c>
+      <c r="V731" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W731" t="n">
+        <v>32</v>
+      </c>
+      <c r="X731" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2486543</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>C. ROGERS | J. VAN ZEGEREN | S. THRASTARSON | T. NASPLER PERAIRE | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D732" t="n">
+        <v>5</v>
+      </c>
+      <c r="E732" t="n">
+        <v>129</v>
+      </c>
+      <c r="F732" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G732" t="n">
+        <v>9</v>
+      </c>
+      <c r="H732" t="n">
+        <v>5</v>
+      </c>
+      <c r="I732" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="J732" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K732" t="n">
+        <v>261.63</v>
+      </c>
+      <c r="L732" t="n">
+        <v>173.61</v>
+      </c>
+      <c r="M732" t="n">
+        <v>88.02</v>
+      </c>
+      <c r="N732" t="n">
+        <v>4</v>
+      </c>
+      <c r="O732" t="n">
+        <v>1</v>
+      </c>
+      <c r="P732" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q732" t="n">
+        <v>1</v>
+      </c>
+      <c r="R732" t="n">
+        <v>2</v>
+      </c>
+      <c r="S732" t="n">
+        <v>2</v>
+      </c>
+      <c r="T732" t="n">
+        <v>0</v>
+      </c>
+      <c r="U732" t="n">
+        <v>0</v>
+      </c>
+      <c r="V732" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W732" t="n">
+        <v>32</v>
+      </c>
+      <c r="X732" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2486543</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>J. PERIS CRESPO | J. ROUND | J. VAN ZEGEREN | S. THRASTARSON | T. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D733" t="n">
+        <v>5</v>
+      </c>
+      <c r="E733" t="n">
+        <v>6</v>
+      </c>
+      <c r="F733" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G733" t="n">
+        <v>0</v>
+      </c>
+      <c r="H733" t="n">
+        <v>2</v>
+      </c>
+      <c r="I733" t="n">
+        <v>0</v>
+      </c>
+      <c r="J733" t="n">
+        <v>1</v>
+      </c>
+      <c r="K733" t="n">
+        <v>0</v>
+      </c>
+      <c r="L733" t="n">
+        <v>200</v>
+      </c>
+      <c r="M733" t="n">
+        <v>0</v>
+      </c>
+      <c r="N733" t="n">
+        <v>0</v>
+      </c>
+      <c r="O733" t="n">
+        <v>0</v>
+      </c>
+      <c r="P733" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q733" t="n">
+        <v>0</v>
+      </c>
+      <c r="R733" t="n">
+        <v>1</v>
+      </c>
+      <c r="S733" t="n">
+        <v>0</v>
+      </c>
+      <c r="T733" t="n">
+        <v>0</v>
+      </c>
+      <c r="U733" t="n">
+        <v>0</v>
+      </c>
+      <c r="V733" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W733" t="n">
+        <v>32</v>
+      </c>
+      <c r="X733" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2486543</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>B. DE LA LLAMA RUIZ | J. POWELL | J. YU | M. LAPORNIK | P. HERNANDEZ MONTENEGRO</t>
+        </is>
+      </c>
+      <c r="D734" t="n">
+        <v>5</v>
+      </c>
+      <c r="E734" t="n">
+        <v>83</v>
+      </c>
+      <c r="F734" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G734" t="n">
+        <v>0</v>
+      </c>
+      <c r="H734" t="n">
+        <v>2</v>
+      </c>
+      <c r="I734" t="n">
+        <v>2</v>
+      </c>
+      <c r="J734" t="n">
+        <v>1</v>
+      </c>
+      <c r="K734" t="n">
+        <v>0</v>
+      </c>
+      <c r="L734" t="n">
+        <v>200</v>
+      </c>
+      <c r="M734" t="n">
+        <v>-200</v>
+      </c>
+      <c r="N734" t="n">
+        <v>1</v>
+      </c>
+      <c r="O734" t="n">
+        <v>0</v>
+      </c>
+      <c r="P734" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q734" t="n">
+        <v>1</v>
+      </c>
+      <c r="R734" t="n">
+        <v>2</v>
+      </c>
+      <c r="S734" t="n">
+        <v>0</v>
+      </c>
+      <c r="T734" t="n">
+        <v>0</v>
+      </c>
+      <c r="U734" t="n">
+        <v>1</v>
+      </c>
+      <c r="V734" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W734" t="n">
+        <v>32</v>
+      </c>
+      <c r="X734" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2486543</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>D. ALDERETE DIAZ | G. KANDE KIELI | J. POWELL | M. LAPORNIK | P. HERNANDEZ MONTENEGRO</t>
+        </is>
+      </c>
+      <c r="D735" t="n">
+        <v>5</v>
+      </c>
+      <c r="E735" t="n">
+        <v>15</v>
+      </c>
+      <c r="F735" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G735" t="n">
+        <v>3</v>
+      </c>
+      <c r="H735" t="n">
+        <v>0</v>
+      </c>
+      <c r="I735" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J735" t="n">
+        <v>1</v>
+      </c>
+      <c r="K735" t="n">
+        <v>394.74</v>
+      </c>
+      <c r="L735" t="n">
+        <v>0</v>
+      </c>
+      <c r="M735" t="n">
+        <v>394.74</v>
+      </c>
+      <c r="N735" t="n">
+        <v>0</v>
+      </c>
+      <c r="O735" t="n">
+        <v>4</v>
+      </c>
+      <c r="P735" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q735" t="n">
+        <v>1</v>
+      </c>
+      <c r="R735" t="n">
+        <v>1</v>
+      </c>
+      <c r="S735" t="n">
+        <v>0</v>
+      </c>
+      <c r="T735" t="n">
+        <v>0</v>
+      </c>
+      <c r="U735" t="n">
+        <v>0</v>
+      </c>
+      <c r="V735" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W735" t="n">
+        <v>32</v>
+      </c>
+      <c r="X735" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2486543</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>D. LOVE | J. POWELL | J. YU | M. LAPORNIK | P. HERNANDEZ MONTENEGRO</t>
+        </is>
+      </c>
+      <c r="D736" t="n">
+        <v>5</v>
+      </c>
+      <c r="E736" t="n">
+        <v>196</v>
+      </c>
+      <c r="F736" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="G736" t="n">
+        <v>8</v>
+      </c>
+      <c r="H736" t="n">
+        <v>11</v>
+      </c>
+      <c r="I736" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="J736" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="K736" t="n">
+        <v>168.07</v>
+      </c>
+      <c r="L736" t="n">
+        <v>174.05</v>
+      </c>
+      <c r="M736" t="n">
+        <v>-5.98</v>
+      </c>
+      <c r="N736" t="n">
+        <v>5</v>
+      </c>
+      <c r="O736" t="n">
+        <v>4</v>
+      </c>
+      <c r="P736" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q736" t="n">
+        <v>2</v>
+      </c>
+      <c r="R736" t="n">
+        <v>8</v>
+      </c>
+      <c r="S736" t="n">
+        <v>3</v>
+      </c>
+      <c r="T736" t="n">
+        <v>0</v>
+      </c>
+      <c r="U736" t="n">
+        <v>3</v>
+      </c>
+      <c r="V736" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W736" t="n">
+        <v>32</v>
+      </c>
+      <c r="X736" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA vs CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2486537</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>C. OKANU | D. SARAIVA SEIXAS | M. FERNANDEZ CARBALLO | R. DIAS MARQUES LISBOA SANTOS | S. MC DONNELL</t>
+        </is>
+      </c>
+      <c r="D737" t="n">
+        <v>5</v>
+      </c>
+      <c r="E737" t="n">
+        <v>34</v>
+      </c>
+      <c r="F737" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G737" t="n">
+        <v>4</v>
+      </c>
+      <c r="H737" t="n">
+        <v>5</v>
+      </c>
+      <c r="I737" t="n">
+        <v>3</v>
+      </c>
+      <c r="J737" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K737" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="L737" t="n">
+        <v>304.88</v>
+      </c>
+      <c r="M737" t="n">
+        <v>-171.54</v>
+      </c>
+      <c r="N737" t="n">
+        <v>3</v>
+      </c>
+      <c r="O737" t="n">
+        <v>0</v>
+      </c>
+      <c r="P737" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q737" t="n">
+        <v>0</v>
+      </c>
+      <c r="R737" t="n">
+        <v>0</v>
+      </c>
+      <c r="S737" t="n">
+        <v>6</v>
+      </c>
+      <c r="T737" t="n">
+        <v>0</v>
+      </c>
+      <c r="U737" t="n">
+        <v>1</v>
+      </c>
+      <c r="V737" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W737" t="n">
+        <v>32</v>
+      </c>
+      <c r="X737" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2486537</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>C. OKANU | I. VAZQUEZ PEREZ | M. FERNANDEZ CARBALLO | S. MC DONNELL</t>
+        </is>
+      </c>
+      <c r="D738" t="n">
+        <v>4</v>
+      </c>
+      <c r="E738" t="n">
+        <v>9</v>
+      </c>
+      <c r="F738" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G738" t="n">
+        <v>0</v>
+      </c>
+      <c r="H738" t="n">
+        <v>1</v>
+      </c>
+      <c r="I738" t="n">
+        <v>0</v>
+      </c>
+      <c r="J738" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K738" t="n">
+        <v>0</v>
+      </c>
+      <c r="L738" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M738" t="n">
+        <v>0</v>
+      </c>
+      <c r="N738" t="n">
+        <v>0</v>
+      </c>
+      <c r="O738" t="n">
+        <v>0</v>
+      </c>
+      <c r="P738" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q738" t="n">
+        <v>0</v>
+      </c>
+      <c r="R738" t="n">
+        <v>0</v>
+      </c>
+      <c r="S738" t="n">
+        <v>1</v>
+      </c>
+      <c r="T738" t="n">
+        <v>0</v>
+      </c>
+      <c r="U738" t="n">
+        <v>0</v>
+      </c>
+      <c r="V738" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W738" t="n">
+        <v>32</v>
+      </c>
+      <c r="X738" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2486537</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>C. OKANU | M. IGLESIAS FERNANDEZ | R. GILL | S. MC DONNELL</t>
+        </is>
+      </c>
+      <c r="D739" t="n">
+        <v>4</v>
+      </c>
+      <c r="E739" t="n">
+        <v>6</v>
+      </c>
+      <c r="F739" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G739" t="n">
+        <v>1</v>
+      </c>
+      <c r="H739" t="n">
+        <v>0</v>
+      </c>
+      <c r="I739" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J739" t="n">
+        <v>0</v>
+      </c>
+      <c r="K739" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L739" t="n">
+        <v>0</v>
+      </c>
+      <c r="M739" t="n">
+        <v>0</v>
+      </c>
+      <c r="N739" t="n">
+        <v>0</v>
+      </c>
+      <c r="O739" t="n">
+        <v>2</v>
+      </c>
+      <c r="P739" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q739" t="n">
+        <v>0</v>
+      </c>
+      <c r="R739" t="n">
+        <v>0</v>
+      </c>
+      <c r="S739" t="n">
+        <v>0</v>
+      </c>
+      <c r="T739" t="n">
+        <v>0</v>
+      </c>
+      <c r="U739" t="n">
+        <v>0</v>
+      </c>
+      <c r="V739" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W739" t="n">
+        <v>32</v>
+      </c>
+      <c r="X739" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2486537</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>D. SARAIVA SEIXAS | G. KALSCHEUR | R. DIAS MARQUES LISBOA SANTOS | R. GILL | S. MC DONNELL</t>
+        </is>
+      </c>
+      <c r="D740" t="n">
+        <v>5</v>
+      </c>
+      <c r="E740" t="n">
+        <v>193</v>
+      </c>
+      <c r="F740" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="G740" t="n">
+        <v>7</v>
+      </c>
+      <c r="H740" t="n">
+        <v>5</v>
+      </c>
+      <c r="I740" t="n">
+        <v>5</v>
+      </c>
+      <c r="J740" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="K740" t="n">
+        <v>140</v>
+      </c>
+      <c r="L740" t="n">
+        <v>105.04</v>
+      </c>
+      <c r="M740" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="N740" t="n">
+        <v>3</v>
+      </c>
+      <c r="O740" t="n">
+        <v>0</v>
+      </c>
+      <c r="P740" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q740" t="n">
+        <v>0</v>
+      </c>
+      <c r="R740" t="n">
+        <v>3</v>
+      </c>
+      <c r="S740" t="n">
+        <v>4</v>
+      </c>
+      <c r="T740" t="n">
+        <v>1</v>
+      </c>
+      <c r="U740" t="n">
+        <v>1</v>
+      </c>
+      <c r="V740" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W740" t="n">
+        <v>32</v>
+      </c>
+      <c r="X740" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2486537</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>D. SARAIVA SEIXAS | M. FERNANDEZ CARBALLO | R. DIAS MARQUES LISBOA SANTOS | R. GILL | S. MC DONNELL</t>
+        </is>
+      </c>
+      <c r="D741" t="n">
+        <v>5</v>
+      </c>
+      <c r="E741" t="n">
+        <v>50</v>
+      </c>
+      <c r="F741" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G741" t="n">
+        <v>0</v>
+      </c>
+      <c r="H741" t="n">
+        <v>2</v>
+      </c>
+      <c r="I741" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J741" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K741" t="n">
+        <v>0</v>
+      </c>
+      <c r="L741" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="M741" t="n">
+        <v>-86.20999999999999</v>
+      </c>
+      <c r="N741" t="n">
+        <v>1</v>
+      </c>
+      <c r="O741" t="n">
+        <v>2</v>
+      </c>
+      <c r="P741" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q741" t="n">
+        <v>0</v>
+      </c>
+      <c r="R741" t="n">
+        <v>1</v>
+      </c>
+      <c r="S741" t="n">
+        <v>3</v>
+      </c>
+      <c r="T741" t="n">
+        <v>0</v>
+      </c>
+      <c r="U741" t="n">
+        <v>0</v>
+      </c>
+      <c r="V741" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W741" t="n">
+        <v>32</v>
+      </c>
+      <c r="X741" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2486537</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>A. SOLA IDDRISU | E. VICEDO AYALA | E. WEMBI | F. ZURBRIGGEN | N. GALETTE</t>
+        </is>
+      </c>
+      <c r="D742" t="n">
+        <v>5</v>
+      </c>
+      <c r="E742" t="n">
+        <v>6</v>
+      </c>
+      <c r="F742" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G742" t="n">
+        <v>0</v>
+      </c>
+      <c r="H742" t="n">
+        <v>1</v>
+      </c>
+      <c r="I742" t="n">
+        <v>0</v>
+      </c>
+      <c r="J742" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K742" t="n">
+        <v>0</v>
+      </c>
+      <c r="L742" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M742" t="n">
+        <v>0</v>
+      </c>
+      <c r="N742" t="n">
+        <v>0</v>
+      </c>
+      <c r="O742" t="n">
+        <v>0</v>
+      </c>
+      <c r="P742" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q742" t="n">
+        <v>0</v>
+      </c>
+      <c r="R742" t="n">
+        <v>0</v>
+      </c>
+      <c r="S742" t="n">
+        <v>2</v>
+      </c>
+      <c r="T742" t="n">
+        <v>0</v>
+      </c>
+      <c r="U742" t="n">
+        <v>0</v>
+      </c>
+      <c r="V742" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W742" t="n">
+        <v>32</v>
+      </c>
+      <c r="X742" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2486537</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>A. SOLA IDDRISU | E. VICEDO AYALA | E. WEMBI | F. ZURBRIGGEN | S. LITTLESON</t>
+        </is>
+      </c>
+      <c r="D743" t="n">
+        <v>5</v>
+      </c>
+      <c r="E743" t="n">
+        <v>286</v>
+      </c>
+      <c r="F743" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="G743" t="n">
+        <v>13</v>
+      </c>
+      <c r="H743" t="n">
+        <v>11</v>
+      </c>
+      <c r="I743" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="J743" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="K743" t="n">
+        <v>141.92</v>
+      </c>
+      <c r="L743" t="n">
+        <v>111.34</v>
+      </c>
+      <c r="M743" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="N743" t="n">
+        <v>4</v>
+      </c>
+      <c r="O743" t="n">
+        <v>14</v>
+      </c>
+      <c r="P743" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q743" t="n">
+        <v>2</v>
+      </c>
+      <c r="R743" t="n">
+        <v>7</v>
+      </c>
+      <c r="S743" t="n">
+        <v>2</v>
+      </c>
+      <c r="T743" t="n">
+        <v>2</v>
+      </c>
+      <c r="U743" t="n">
+        <v>0</v>
+      </c>
+      <c r="V743" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W743" t="n">
+        <v>32</v>
+      </c>
+      <c r="X743" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO vs HESTIA MENORCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2486538</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>E. POLANCO TAVAREZ | J. BONE | K. LARSEN | S. HOLLANDERS | U. MENDICOTE RUBIO</t>
+        </is>
+      </c>
+      <c r="D744" t="n">
+        <v>5</v>
+      </c>
+      <c r="E744" t="n">
+        <v>185</v>
+      </c>
+      <c r="F744" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="G744" t="n">
+        <v>1</v>
+      </c>
+      <c r="H744" t="n">
+        <v>4</v>
+      </c>
+      <c r="I744" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="J744" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="K744" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="L744" t="n">
+        <v>84.03</v>
+      </c>
+      <c r="M744" t="n">
+        <v>-69.5</v>
+      </c>
+      <c r="N744" t="n">
+        <v>8</v>
+      </c>
+      <c r="O744" t="n">
+        <v>2</v>
+      </c>
+      <c r="P744" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q744" t="n">
+        <v>3</v>
+      </c>
+      <c r="R744" t="n">
+        <v>3</v>
+      </c>
+      <c r="S744" t="n">
+        <v>4</v>
+      </c>
+      <c r="T744" t="n">
+        <v>1</v>
+      </c>
+      <c r="U744" t="n">
+        <v>1</v>
+      </c>
+      <c r="V744" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W744" t="n">
+        <v>32</v>
+      </c>
+      <c r="X744" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2486538</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>A. IZAW BOLAVIE | A. URDIAIN LABAYEN | D. SANADZE | H. ATENCIA SUAREZ | J. CARRALERO MARTIN</t>
+        </is>
+      </c>
+      <c r="D745" t="n">
+        <v>5</v>
+      </c>
+      <c r="E745" t="n">
+        <v>89</v>
+      </c>
+      <c r="F745" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G745" t="n">
+        <v>0</v>
+      </c>
+      <c r="H745" t="n">
+        <v>0</v>
+      </c>
+      <c r="I745" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J745" t="n">
+        <v>2</v>
+      </c>
+      <c r="K745" t="n">
+        <v>0</v>
+      </c>
+      <c r="L745" t="n">
+        <v>0</v>
+      </c>
+      <c r="M745" t="n">
+        <v>0</v>
+      </c>
+      <c r="N745" t="n">
+        <v>1</v>
+      </c>
+      <c r="O745" t="n">
+        <v>2</v>
+      </c>
+      <c r="P745" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q745" t="n">
+        <v>1</v>
+      </c>
+      <c r="R745" t="n">
+        <v>4</v>
+      </c>
+      <c r="S745" t="n">
+        <v>0</v>
+      </c>
+      <c r="T745" t="n">
+        <v>0</v>
+      </c>
+      <c r="U745" t="n">
+        <v>2</v>
+      </c>
+      <c r="V745" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W745" t="n">
+        <v>32</v>
+      </c>
+      <c r="X745" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2486538</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>A. URDIAIN LABAYEN | D. SANADZE | H. ATENCIA SUAREZ | J. CARRALERO MARTIN | J. ROBERTS</t>
+        </is>
+      </c>
+      <c r="D746" t="n">
+        <v>5</v>
+      </c>
+      <c r="E746" t="n">
+        <v>96</v>
+      </c>
+      <c r="F746" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G746" t="n">
+        <v>4</v>
+      </c>
+      <c r="H746" t="n">
+        <v>1</v>
+      </c>
+      <c r="I746" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J746" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="K746" t="n">
+        <v>103.09</v>
+      </c>
+      <c r="L746" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="M746" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="N746" t="n">
+        <v>2</v>
+      </c>
+      <c r="O746" t="n">
+        <v>2</v>
+      </c>
+      <c r="P746" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q746" t="n">
+        <v>0</v>
+      </c>
+      <c r="R746" t="n">
+        <v>4</v>
+      </c>
+      <c r="S746" t="n">
+        <v>2</v>
+      </c>
+      <c r="T746" t="n">
+        <v>1</v>
+      </c>
+      <c r="U746" t="n">
+        <v>1</v>
+      </c>
+      <c r="V746" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W746" t="n">
+        <v>32</v>
+      </c>
+      <c r="X746" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE vs PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2486541</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>B. DE BISSCHOP | D. MANCHON CRESPO | G. RENFROE | J. BELEMENE-DZABATOU | P. ALI</t>
+        </is>
+      </c>
+      <c r="D747" t="n">
+        <v>5</v>
+      </c>
+      <c r="E747" t="n">
+        <v>24</v>
+      </c>
+      <c r="F747" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G747" t="n">
+        <v>0</v>
+      </c>
+      <c r="H747" t="n">
+        <v>0</v>
+      </c>
+      <c r="I747" t="n">
+        <v>1</v>
+      </c>
+      <c r="J747" t="n">
+        <v>1</v>
+      </c>
+      <c r="K747" t="n">
+        <v>0</v>
+      </c>
+      <c r="L747" t="n">
+        <v>0</v>
+      </c>
+      <c r="M747" t="n">
+        <v>0</v>
+      </c>
+      <c r="N747" t="n">
+        <v>0</v>
+      </c>
+      <c r="O747" t="n">
+        <v>0</v>
+      </c>
+      <c r="P747" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q747" t="n">
+        <v>0</v>
+      </c>
+      <c r="R747" t="n">
+        <v>1</v>
+      </c>
+      <c r="S747" t="n">
+        <v>0</v>
+      </c>
+      <c r="T747" t="n">
+        <v>0</v>
+      </c>
+      <c r="U747" t="n">
+        <v>0</v>
+      </c>
+      <c r="V747" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W747" t="n">
+        <v>32</v>
+      </c>
+      <c r="X747" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2486541</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>B. DE BISSCHOP | D. MANCHON CRESPO | J. KASIBABU SHILALA | M. DIAZ | P. ALI</t>
+        </is>
+      </c>
+      <c r="D748" t="n">
+        <v>5</v>
+      </c>
+      <c r="E748" t="n">
+        <v>15</v>
+      </c>
+      <c r="F748" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G748" t="n">
+        <v>2</v>
+      </c>
+      <c r="H748" t="n">
+        <v>0</v>
+      </c>
+      <c r="I748" t="n">
+        <v>1</v>
+      </c>
+      <c r="J748" t="n">
+        <v>0</v>
+      </c>
+      <c r="K748" t="n">
+        <v>200</v>
+      </c>
+      <c r="L748" t="n">
+        <v>0</v>
+      </c>
+      <c r="M748" t="n">
+        <v>0</v>
+      </c>
+      <c r="N748" t="n">
+        <v>1</v>
+      </c>
+      <c r="O748" t="n">
+        <v>0</v>
+      </c>
+      <c r="P748" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q748" t="n">
+        <v>0</v>
+      </c>
+      <c r="R748" t="n">
+        <v>0</v>
+      </c>
+      <c r="S748" t="n">
+        <v>0</v>
+      </c>
+      <c r="T748" t="n">
+        <v>0</v>
+      </c>
+      <c r="U748" t="n">
+        <v>0</v>
+      </c>
+      <c r="V748" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W748" t="n">
+        <v>32</v>
+      </c>
+      <c r="X748" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2486541</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>A. GARUBA ALARI | A. MARTIN MARIN | C. POLYNICE | I. RIVERA CARROLL | J. LOPEZ SANTANA</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>5</v>
+      </c>
+      <c r="E749" t="n">
+        <v>39</v>
+      </c>
+      <c r="F749" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G749" t="n">
+        <v>0</v>
+      </c>
+      <c r="H749" t="n">
+        <v>2</v>
+      </c>
+      <c r="I749" t="n">
+        <v>1</v>
+      </c>
+      <c r="J749" t="n">
+        <v>2</v>
+      </c>
+      <c r="K749" t="n">
+        <v>0</v>
+      </c>
+      <c r="L749" t="n">
+        <v>100</v>
+      </c>
+      <c r="M749" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N749" t="n">
+        <v>1</v>
+      </c>
+      <c r="O749" t="n">
+        <v>0</v>
+      </c>
+      <c r="P749" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q749" t="n">
+        <v>0</v>
+      </c>
+      <c r="R749" t="n">
+        <v>1</v>
+      </c>
+      <c r="S749" t="n">
+        <v>0</v>
+      </c>
+      <c r="T749" t="n">
+        <v>1</v>
+      </c>
+      <c r="U749" t="n">
+        <v>0</v>
+      </c>
+      <c r="V749" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W749" t="n">
+        <v>32</v>
+      </c>
+      <c r="X749" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2486540</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>A. GALAN POZO | D. DE SOUSA ANJO BRITO | F. DOS ANJOS DE PAULA | S. QUINTELA SALVADOR | T. MUNNINGS</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>5</v>
+      </c>
+      <c r="E750" t="n">
+        <v>9</v>
+      </c>
+      <c r="F750" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G750" t="n">
+        <v>3</v>
+      </c>
+      <c r="H750" t="n">
+        <v>0</v>
+      </c>
+      <c r="I750" t="n">
+        <v>1</v>
+      </c>
+      <c r="J750" t="n">
+        <v>0</v>
+      </c>
+      <c r="K750" t="n">
+        <v>300</v>
+      </c>
+      <c r="L750" t="n">
+        <v>0</v>
+      </c>
+      <c r="M750" t="n">
+        <v>0</v>
+      </c>
+      <c r="N750" t="n">
+        <v>1</v>
+      </c>
+      <c r="O750" t="n">
+        <v>0</v>
+      </c>
+      <c r="P750" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q750" t="n">
+        <v>0</v>
+      </c>
+      <c r="R750" t="n">
+        <v>0</v>
+      </c>
+      <c r="S750" t="n">
+        <v>0</v>
+      </c>
+      <c r="T750" t="n">
+        <v>0</v>
+      </c>
+      <c r="U750" t="n">
+        <v>0</v>
+      </c>
+      <c r="V750" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W750" t="n">
+        <v>32</v>
+      </c>
+      <c r="X750" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES vs MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2486540</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>J. GRANGER | M. NIANG | P. GARINO GULLOTTA | R. STUMBRIS | S. GARCIA CALVO</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>5</v>
+      </c>
+      <c r="E751" t="n">
+        <v>9</v>
+      </c>
+      <c r="F751" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G751" t="n">
+        <v>0</v>
+      </c>
+      <c r="H751" t="n">
+        <v>3</v>
+      </c>
+      <c r="I751" t="n">
+        <v>0</v>
+      </c>
+      <c r="J751" t="n">
+        <v>1</v>
+      </c>
+      <c r="K751" t="n">
+        <v>0</v>
+      </c>
+      <c r="L751" t="n">
+        <v>300</v>
+      </c>
+      <c r="M751" t="n">
+        <v>0</v>
+      </c>
+      <c r="N751" t="n">
+        <v>0</v>
+      </c>
+      <c r="O751" t="n">
+        <v>0</v>
+      </c>
+      <c r="P751" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q751" t="n">
+        <v>0</v>
+      </c>
+      <c r="R751" t="n">
+        <v>1</v>
+      </c>
+      <c r="S751" t="n">
+        <v>0</v>
+      </c>
+      <c r="T751" t="n">
+        <v>0</v>
+      </c>
+      <c r="U751" t="n">
+        <v>0</v>
+      </c>
+      <c r="V751" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W751" t="n">
+        <v>32</v>
+      </c>
+      <c r="X751" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES vs MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2486544</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>F. TERINS | J. BROWN-FERGUSON | J. ZIDEK | M. JACKSON | M. NUGU</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>5</v>
+      </c>
+      <c r="E752" t="n">
+        <v>85</v>
+      </c>
+      <c r="F752" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G752" t="n">
+        <v>4</v>
+      </c>
+      <c r="H752" t="n">
+        <v>0</v>
+      </c>
+      <c r="I752" t="n">
+        <v>1</v>
+      </c>
+      <c r="J752" t="n">
+        <v>2</v>
+      </c>
+      <c r="K752" t="n">
+        <v>400</v>
+      </c>
+      <c r="L752" t="n">
+        <v>0</v>
+      </c>
+      <c r="M752" t="n">
+        <v>400</v>
+      </c>
+      <c r="N752" t="n">
+        <v>2</v>
+      </c>
+      <c r="O752" t="n">
+        <v>0</v>
+      </c>
+      <c r="P752" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q752" t="n">
+        <v>1</v>
+      </c>
+      <c r="R752" t="n">
+        <v>1</v>
+      </c>
+      <c r="S752" t="n">
+        <v>0</v>
+      </c>
+      <c r="T752" t="n">
+        <v>1</v>
+      </c>
+      <c r="U752" t="n">
+        <v>0</v>
+      </c>
+      <c r="V752" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W752" t="n">
+        <v>32</v>
+      </c>
+      <c r="X752" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2486544</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>F. TERINS | J. BROWN-FERGUSON | J. ZIDEK | M. NUGU | R. SEOANE RODICIO</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>5</v>
+      </c>
+      <c r="E753" t="n">
+        <v>75</v>
+      </c>
+      <c r="F753" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G753" t="n">
+        <v>5</v>
+      </c>
+      <c r="H753" t="n">
+        <v>0</v>
+      </c>
+      <c r="I753" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="J753" t="n">
+        <v>3</v>
+      </c>
+      <c r="K753" t="n">
+        <v>115.74</v>
+      </c>
+      <c r="L753" t="n">
+        <v>0</v>
+      </c>
+      <c r="M753" t="n">
+        <v>115.74</v>
+      </c>
+      <c r="N753" t="n">
+        <v>3</v>
+      </c>
+      <c r="O753" t="n">
+        <v>3</v>
+      </c>
+      <c r="P753" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q753" t="n">
+        <v>0</v>
+      </c>
+      <c r="R753" t="n">
+        <v>3</v>
+      </c>
+      <c r="S753" t="n">
+        <v>0</v>
+      </c>
+      <c r="T753" t="n">
+        <v>1</v>
+      </c>
+      <c r="U753" t="n">
+        <v>1</v>
+      </c>
+      <c r="V753" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W753" t="n">
+        <v>32</v>
+      </c>
+      <c r="X753" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2486544</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>C. DIAZ RODRIGUEZ | I. CRUZ UCEDA | J. GODSPOWER JOHNSON | M. CAICEDO SANCHEZ | N. HOOVER</t>
+        </is>
+      </c>
+      <c r="D754" t="n">
+        <v>5</v>
+      </c>
+      <c r="E754" t="n">
+        <v>22</v>
+      </c>
+      <c r="F754" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G754" t="n">
+        <v>0</v>
+      </c>
+      <c r="H754" t="n">
+        <v>4</v>
+      </c>
+      <c r="I754" t="n">
+        <v>1</v>
+      </c>
+      <c r="J754" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K754" t="n">
+        <v>0</v>
+      </c>
+      <c r="L754" t="n">
+        <v>163.93</v>
+      </c>
+      <c r="M754" t="n">
+        <v>-163.93</v>
+      </c>
+      <c r="N754" t="n">
+        <v>0</v>
+      </c>
+      <c r="O754" t="n">
+        <v>0</v>
+      </c>
+      <c r="P754" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q754" t="n">
+        <v>0</v>
+      </c>
+      <c r="R754" t="n">
+        <v>2</v>
+      </c>
+      <c r="S754" t="n">
+        <v>1</v>
+      </c>
+      <c r="T754" t="n">
+        <v>0</v>
+      </c>
+      <c r="U754" t="n">
+        <v>0</v>
+      </c>
+      <c r="V754" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W754" t="n">
+        <v>32</v>
+      </c>
+      <c r="X754" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2486544</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>C. DIAZ RODRIGUEZ | I. CRUZ UCEDA | M. CAICEDO SANCHEZ | M. STILMA | N. HOOVER</t>
+        </is>
+      </c>
+      <c r="D755" t="n">
+        <v>5</v>
+      </c>
+      <c r="E755" t="n">
+        <v>53</v>
+      </c>
+      <c r="F755" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G755" t="n">
+        <v>0</v>
+      </c>
+      <c r="H755" t="n">
+        <v>1</v>
+      </c>
+      <c r="I755" t="n">
+        <v>2</v>
+      </c>
+      <c r="J755" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K755" t="n">
+        <v>0</v>
+      </c>
+      <c r="L755" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="M755" t="n">
+        <v>-53.19</v>
+      </c>
+      <c r="N755" t="n">
+        <v>3</v>
+      </c>
+      <c r="O755" t="n">
+        <v>0</v>
+      </c>
+      <c r="P755" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q755" t="n">
+        <v>1</v>
+      </c>
+      <c r="R755" t="n">
+        <v>1</v>
+      </c>
+      <c r="S755" t="n">
+        <v>2</v>
+      </c>
+      <c r="T755" t="n">
+        <v>0</v>
+      </c>
+      <c r="U755" t="n">
+        <v>0</v>
+      </c>
+      <c r="V755" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W755" t="n">
+        <v>32</v>
+      </c>
+      <c r="X755" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2486544</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>I. CRUZ UCEDA | J. GARCIA SANCHEZ | P. CORDOBA MURO | S. CECCARDI | S. RODRIGUEZ FEBLES</t>
+        </is>
+      </c>
+      <c r="D756" t="n">
+        <v>5</v>
+      </c>
+      <c r="E756" t="n">
+        <v>85</v>
+      </c>
+      <c r="F756" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G756" t="n">
+        <v>0</v>
+      </c>
+      <c r="H756" t="n">
+        <v>4</v>
+      </c>
+      <c r="I756" t="n">
+        <v>2</v>
+      </c>
+      <c r="J756" t="n">
+        <v>1</v>
+      </c>
+      <c r="K756" t="n">
+        <v>0</v>
+      </c>
+      <c r="L756" t="n">
+        <v>400</v>
+      </c>
+      <c r="M756" t="n">
+        <v>-400</v>
+      </c>
+      <c r="N756" t="n">
+        <v>1</v>
+      </c>
+      <c r="O756" t="n">
+        <v>0</v>
+      </c>
+      <c r="P756" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q756" t="n">
+        <v>0</v>
+      </c>
+      <c r="R756" t="n">
+        <v>2</v>
+      </c>
+      <c r="S756" t="n">
+        <v>0</v>
+      </c>
+      <c r="T756" t="n">
+        <v>0</v>
+      </c>
+      <c r="U756" t="n">
+        <v>1</v>
+      </c>
+      <c r="V756" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W756" t="n">
+        <v>32</v>
+      </c>
+      <c r="X756" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS vs MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/1FEB_25_26/clutch_lineups_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/clutch_lineups_25_26_1FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X773"/>
+  <dimension ref="A1:X782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65398,6 +65398,762 @@
         </is>
       </c>
     </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2486560</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>B. DE BISSCHOP | D. MANCHON CRESPO | G. RENFROE | J. BELEMENE-DZABATOU | P. ALI</t>
+        </is>
+      </c>
+      <c r="D774" t="n">
+        <v>5</v>
+      </c>
+      <c r="E774" t="n">
+        <v>5</v>
+      </c>
+      <c r="F774" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G774" t="n">
+        <v>3</v>
+      </c>
+      <c r="H774" t="n">
+        <v>0</v>
+      </c>
+      <c r="I774" t="n">
+        <v>1</v>
+      </c>
+      <c r="J774" t="n">
+        <v>0</v>
+      </c>
+      <c r="K774" t="n">
+        <v>300</v>
+      </c>
+      <c r="L774" t="n">
+        <v>0</v>
+      </c>
+      <c r="M774" t="n">
+        <v>0</v>
+      </c>
+      <c r="N774" t="n">
+        <v>1</v>
+      </c>
+      <c r="O774" t="n">
+        <v>0</v>
+      </c>
+      <c r="P774" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q774" t="n">
+        <v>0</v>
+      </c>
+      <c r="R774" t="n">
+        <v>0</v>
+      </c>
+      <c r="S774" t="n">
+        <v>0</v>
+      </c>
+      <c r="T774" t="n">
+        <v>0</v>
+      </c>
+      <c r="U774" t="n">
+        <v>0</v>
+      </c>
+      <c r="V774" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W774" t="n">
+        <v>34</v>
+      </c>
+      <c r="X774" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2486560</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>B. DE BISSCHOP | G. RENFROE | J. KASIBABU SHILALA | P. ALI | V. ALVES BENITE</t>
+        </is>
+      </c>
+      <c r="D775" t="n">
+        <v>5</v>
+      </c>
+      <c r="E775" t="n">
+        <v>119</v>
+      </c>
+      <c r="F775" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G775" t="n">
+        <v>4</v>
+      </c>
+      <c r="H775" t="n">
+        <v>8</v>
+      </c>
+      <c r="I775" t="n">
+        <v>2</v>
+      </c>
+      <c r="J775" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="K775" t="n">
+        <v>200</v>
+      </c>
+      <c r="L775" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M775" t="n">
+        <v>-27.27</v>
+      </c>
+      <c r="N775" t="n">
+        <v>4</v>
+      </c>
+      <c r="O775" t="n">
+        <v>0</v>
+      </c>
+      <c r="P775" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q775" t="n">
+        <v>2</v>
+      </c>
+      <c r="R775" t="n">
+        <v>1</v>
+      </c>
+      <c r="S775" t="n">
+        <v>8</v>
+      </c>
+      <c r="T775" t="n">
+        <v>0</v>
+      </c>
+      <c r="U775" t="n">
+        <v>1</v>
+      </c>
+      <c r="V775" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W775" t="n">
+        <v>34</v>
+      </c>
+      <c r="X775" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2486560</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>A. GONZÁLEZ PÉREZ | J. GRANGER | O. SILVERIO GRULLON | R. STUMBRIS | S. SALIN</t>
+        </is>
+      </c>
+      <c r="D776" t="n">
+        <v>5</v>
+      </c>
+      <c r="E776" t="n">
+        <v>5</v>
+      </c>
+      <c r="F776" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G776" t="n">
+        <v>0</v>
+      </c>
+      <c r="H776" t="n">
+        <v>3</v>
+      </c>
+      <c r="I776" t="n">
+        <v>0</v>
+      </c>
+      <c r="J776" t="n">
+        <v>1</v>
+      </c>
+      <c r="K776" t="n">
+        <v>0</v>
+      </c>
+      <c r="L776" t="n">
+        <v>300</v>
+      </c>
+      <c r="M776" t="n">
+        <v>0</v>
+      </c>
+      <c r="N776" t="n">
+        <v>0</v>
+      </c>
+      <c r="O776" t="n">
+        <v>0</v>
+      </c>
+      <c r="P776" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q776" t="n">
+        <v>0</v>
+      </c>
+      <c r="R776" t="n">
+        <v>1</v>
+      </c>
+      <c r="S776" t="n">
+        <v>0</v>
+      </c>
+      <c r="T776" t="n">
+        <v>0</v>
+      </c>
+      <c r="U776" t="n">
+        <v>0</v>
+      </c>
+      <c r="V776" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W776" t="n">
+        <v>34</v>
+      </c>
+      <c r="X776" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2486560</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>H. LOPEZ BARRANTES | J. GRANGER | O. SILVERIO GRULLON | R. STUMBRIS</t>
+        </is>
+      </c>
+      <c r="D777" t="n">
+        <v>4</v>
+      </c>
+      <c r="E777" t="n">
+        <v>35</v>
+      </c>
+      <c r="F777" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G777" t="n">
+        <v>2</v>
+      </c>
+      <c r="H777" t="n">
+        <v>0</v>
+      </c>
+      <c r="I777" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J777" t="n">
+        <v>0</v>
+      </c>
+      <c r="K777" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L777" t="n">
+        <v>0</v>
+      </c>
+      <c r="M777" t="n">
+        <v>0</v>
+      </c>
+      <c r="N777" t="n">
+        <v>1</v>
+      </c>
+      <c r="O777" t="n">
+        <v>2</v>
+      </c>
+      <c r="P777" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q777" t="n">
+        <v>1</v>
+      </c>
+      <c r="R777" t="n">
+        <v>1</v>
+      </c>
+      <c r="S777" t="n">
+        <v>0</v>
+      </c>
+      <c r="T777" t="n">
+        <v>0</v>
+      </c>
+      <c r="U777" t="n">
+        <v>1</v>
+      </c>
+      <c r="V777" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W777" t="n">
+        <v>34</v>
+      </c>
+      <c r="X777" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2486560</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>J. GRANGER | M. NIANG | O. SILVERIO GRULLON | R. STUMBRIS | S. GARCIA CALVO</t>
+        </is>
+      </c>
+      <c r="D778" t="n">
+        <v>5</v>
+      </c>
+      <c r="E778" t="n">
+        <v>84</v>
+      </c>
+      <c r="F778" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G778" t="n">
+        <v>6</v>
+      </c>
+      <c r="H778" t="n">
+        <v>4</v>
+      </c>
+      <c r="I778" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J778" t="n">
+        <v>2</v>
+      </c>
+      <c r="K778" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L778" t="n">
+        <v>200</v>
+      </c>
+      <c r="M778" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="N778" t="n">
+        <v>0</v>
+      </c>
+      <c r="O778" t="n">
+        <v>6</v>
+      </c>
+      <c r="P778" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q778" t="n">
+        <v>0</v>
+      </c>
+      <c r="R778" t="n">
+        <v>3</v>
+      </c>
+      <c r="S778" t="n">
+        <v>0</v>
+      </c>
+      <c r="T778" t="n">
+        <v>0</v>
+      </c>
+      <c r="U778" t="n">
+        <v>1</v>
+      </c>
+      <c r="V778" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W778" t="n">
+        <v>34</v>
+      </c>
+      <c r="X778" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES vs FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2486561</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>A. FAURE RIBES | D. DUSCAK | F. NWAOKORIE | M. TOWNES VILLAR | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D779" t="n">
+        <v>5</v>
+      </c>
+      <c r="E779" t="n">
+        <v>22</v>
+      </c>
+      <c r="F779" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G779" t="n">
+        <v>0</v>
+      </c>
+      <c r="H779" t="n">
+        <v>2</v>
+      </c>
+      <c r="I779" t="n">
+        <v>1</v>
+      </c>
+      <c r="J779" t="n">
+        <v>2</v>
+      </c>
+      <c r="K779" t="n">
+        <v>0</v>
+      </c>
+      <c r="L779" t="n">
+        <v>100</v>
+      </c>
+      <c r="M779" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N779" t="n">
+        <v>1</v>
+      </c>
+      <c r="O779" t="n">
+        <v>0</v>
+      </c>
+      <c r="P779" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q779" t="n">
+        <v>0</v>
+      </c>
+      <c r="R779" t="n">
+        <v>2</v>
+      </c>
+      <c r="S779" t="n">
+        <v>0</v>
+      </c>
+      <c r="T779" t="n">
+        <v>0</v>
+      </c>
+      <c r="U779" t="n">
+        <v>0</v>
+      </c>
+      <c r="V779" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W779" t="n">
+        <v>34</v>
+      </c>
+      <c r="X779" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2486561</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>D. DUSCAK | F. NWAOKORIE | M. TOWNES VILLAR | R. COSIALLS BORRAS | R. LOBACO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="D780" t="n">
+        <v>5</v>
+      </c>
+      <c r="E780" t="n">
+        <v>260</v>
+      </c>
+      <c r="F780" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="G780" t="n">
+        <v>10</v>
+      </c>
+      <c r="H780" t="n">
+        <v>8</v>
+      </c>
+      <c r="I780" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="J780" t="n">
+        <v>6</v>
+      </c>
+      <c r="K780" t="n">
+        <v>173.61</v>
+      </c>
+      <c r="L780" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="M780" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="N780" t="n">
+        <v>7</v>
+      </c>
+      <c r="O780" t="n">
+        <v>4</v>
+      </c>
+      <c r="P780" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q780" t="n">
+        <v>3</v>
+      </c>
+      <c r="R780" t="n">
+        <v>8</v>
+      </c>
+      <c r="S780" t="n">
+        <v>0</v>
+      </c>
+      <c r="T780" t="n">
+        <v>0</v>
+      </c>
+      <c r="U780" t="n">
+        <v>2</v>
+      </c>
+      <c r="V780" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W780" t="n">
+        <v>34</v>
+      </c>
+      <c r="X780" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2486561</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>C. JÜRGENS | C. OKANU | I. VAZQUEZ PEREZ | M. FERNANDEZ CARBALLO | S. MC DONNELL</t>
+        </is>
+      </c>
+      <c r="D781" t="n">
+        <v>5</v>
+      </c>
+      <c r="E781" t="n">
+        <v>91</v>
+      </c>
+      <c r="F781" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G781" t="n">
+        <v>4</v>
+      </c>
+      <c r="H781" t="n">
+        <v>5</v>
+      </c>
+      <c r="I781" t="n">
+        <v>4</v>
+      </c>
+      <c r="J781" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K781" t="n">
+        <v>100</v>
+      </c>
+      <c r="L781" t="n">
+        <v>181.16</v>
+      </c>
+      <c r="M781" t="n">
+        <v>-81.16</v>
+      </c>
+      <c r="N781" t="n">
+        <v>5</v>
+      </c>
+      <c r="O781" t="n">
+        <v>0</v>
+      </c>
+      <c r="P781" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q781" t="n">
+        <v>1</v>
+      </c>
+      <c r="R781" t="n">
+        <v>2</v>
+      </c>
+      <c r="S781" t="n">
+        <v>4</v>
+      </c>
+      <c r="T781" t="n">
+        <v>0</v>
+      </c>
+      <c r="U781" t="n">
+        <v>1</v>
+      </c>
+      <c r="V781" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W781" t="n">
+        <v>34</v>
+      </c>
+      <c r="X781" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2486561</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>C. OKANU | G. KALSCHEUR | I. VAZQUEZ PEREZ | M. FERNANDEZ CARBALLO | S. MC DONNELL</t>
+        </is>
+      </c>
+      <c r="D782" t="n">
+        <v>5</v>
+      </c>
+      <c r="E782" t="n">
+        <v>191</v>
+      </c>
+      <c r="F782" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="G782" t="n">
+        <v>6</v>
+      </c>
+      <c r="H782" t="n">
+        <v>5</v>
+      </c>
+      <c r="I782" t="n">
+        <v>4</v>
+      </c>
+      <c r="J782" t="n">
+        <v>4</v>
+      </c>
+      <c r="K782" t="n">
+        <v>150</v>
+      </c>
+      <c r="L782" t="n">
+        <v>125</v>
+      </c>
+      <c r="M782" t="n">
+        <v>25</v>
+      </c>
+      <c r="N782" t="n">
+        <v>5</v>
+      </c>
+      <c r="O782" t="n">
+        <v>0</v>
+      </c>
+      <c r="P782" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q782" t="n">
+        <v>1</v>
+      </c>
+      <c r="R782" t="n">
+        <v>6</v>
+      </c>
+      <c r="S782" t="n">
+        <v>0</v>
+      </c>
+      <c r="T782" t="n">
+        <v>0</v>
+      </c>
+      <c r="U782" t="n">
+        <v>2</v>
+      </c>
+      <c r="V782" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="W782" t="n">
+        <v>34</v>
+      </c>
+      <c r="X782" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO vs CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
